--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239C5FF3-3507-E041-93FB-6103465F4F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16078511-71B9-D640-9378-1F8CE9F92D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2322,9 +2322,6 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2334,6 +2331,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2341,12 +2347,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12801,12 +12801,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
-    <v>18.965</v>
-    <v>2.2305000000000001</v>
-    <v>-0.93</v>
-    <v>-1.0204999999999999E-2</v>
-    <v>-0.97219999999999995</v>
-    <v>-1.0778000000000001E-2</v>
+    <v>23.75</v>
+    <v>2.2740999999999998</v>
+    <v>4.13</v>
+    <v>4.5053000000000003E-2</v>
+    <v>-0.01</v>
+    <v>-1.0439999999999999E-4</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12814,25 +12814,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>97.9</v>
+    <v>95.94</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46234.999976365623</v>
+    <v>46269.899596041403</v>
     <v>0</v>
-    <v>90.13</v>
-    <v>454968800000</v>
+    <v>91.87</v>
+    <v>506309610200</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>96.72</v>
+    <v>92.45</v>
     <v>0</v>
-    <v>91.13</v>
-    <v>90.2</v>
-    <v>89.227800000000002</v>
-    <v>5044000000</v>
+    <v>91.67</v>
+    <v>95.8</v>
+    <v>95.79</v>
+    <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>109039502</v>
-    <v>116427519</v>
+    <v>97334975</v>
+    <v>97208231</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -12854,19 +12854,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>47.47</v>
+    <v>48.06</v>
     <v>39.47</v>
-    <v>0.82</v>
-    <v>1.7585E-2</v>
+    <v>-0.34</v>
+    <v>-7.0889999999999998E-3</v>
     <v>US</v>
-    <v>47.47</v>
+    <v>47.68</v>
     <v>Index</v>
     <v>3</v>
-    <v>46.82</v>
+    <v>47.32</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>46.84</v>
-    <v>46.63</v>
-    <v>47.45</v>
+    <v>47.66</v>
+    <v>47.96</v>
+    <v>47.62</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13088,9 +13088,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13664,18 +13664,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+      <c r="B2" s="234" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="235"/>
+      <c r="E2" s="234" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="235"/>
+      <c r="H2" s="234" t="s">
         <v>328</v>
       </c>
-      <c r="I2" s="236"/>
+      <c r="I2" s="235"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="184" t="s">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>454968.8</v>
+        <v>483215.2</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.512071631124799</v>
+        <v>-10.384946881958557</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>482969.8</v>
+        <v>511216.19999999995</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>42.692258950864286</v>
+        <v>42.202208590617651</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>243</v>
@@ -13755,14 +13755,14 @@
       </c>
       <c r="C6" s="207" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>89.227800000000002</v>
+        <v>95.79</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC150</f>
-        <v>-42.748815165876771</v>
+        <v>-45.402843601895725</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -13770,7 +13770,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-17.696116197488866</v>
+        <v>-17.532615973282802</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13779,14 +13779,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-0.93</v>
+        <v>4.13</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC151</f>
-        <v>7.7326825291064667</v>
+        <v>8.2127603801374676</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13794,7 +13794,7 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>15.805632990485584</v>
+        <v>15.755776643767003</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13803,14 +13803,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.97219999999999995</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC161</f>
-        <v>-2.4715980524378817E-2</v>
+        <v>-2.3271205044874416E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B11</f>
@@ -13818,7 +13818,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.82477125287709985</v>
+        <v>-0.83553469056610641</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13827,14 +13827,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0204999999999999E-2</v>
+        <v>4.5053000000000003E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC162</f>
-        <v>-2.3392461197339249E-2</v>
+        <v>-2.202505219206681E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.0778000000000001E-2</v>
+        <v>-1.0439999999999999E-4</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>293</v>
@@ -13882,7 +13882,7 @@
       </c>
       <c r="C12" s="208" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>18.965</v>
+        <v>23.75</v>
       </c>
       <c r="E12" s="184" t="s">
         <v>97</v>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2305000000000001</v>
+        <v>2.2740999999999998</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>99</v>
@@ -13914,7 +13914,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>116427519</v>
+        <v>97208231</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>100</v>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-2.7254616140711188E-2</v>
+        <v>-2.5661444424761471E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13943,10 +13943,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="236" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="236"/>
       <c r="E17" s="183" t="s">
         <v>296</v>
       </c>
@@ -14019,14 +14019,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="236" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="236"/>
+      <c r="E25" s="234" t="s">
         <v>381</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="235"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14040,7 +14040,7 @@
       </c>
       <c r="F26" s="222" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.45</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14055,7 +14055,7 @@
       </c>
       <c r="F27" s="223">
         <f ca="1">F26/1000</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14075,15 +14075,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="234" t="s">
+      <c r="B33" s="237" t="s">
         <v>351</v>
       </c>
-      <c r="C33" s="234"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="234"/>
-      <c r="G33" s="234"/>
-      <c r="H33" s="234"/>
+      <c r="C33" s="237"/>
+      <c r="D33" s="237"/>
+      <c r="E33" s="237"/>
+      <c r="F33" s="237"/>
+      <c r="G33" s="237"/>
+      <c r="H33" s="237"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14102,24 +14102,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="234"/>
-      <c r="C39" s="234"/>
-      <c r="D39" s="234"/>
-      <c r="E39" s="234"/>
-      <c r="F39" s="234"/>
-      <c r="G39" s="234"/>
-      <c r="H39" s="234"/>
+      <c r="B39" s="237"/>
+      <c r="C39" s="237"/>
+      <c r="D39" s="237"/>
+      <c r="E39" s="237"/>
+      <c r="F39" s="237"/>
+      <c r="G39" s="237"/>
+      <c r="H39" s="237"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="234" t="s">
+      <c r="B42" s="237" t="s">
         <v>354</v>
       </c>
-      <c r="C42" s="234"/>
-      <c r="D42" s="234"/>
-      <c r="E42" s="234"/>
-      <c r="F42" s="234"/>
-      <c r="G42" s="234"/>
-      <c r="H42" s="234"/>
+      <c r="C42" s="237"/>
+      <c r="D42" s="237"/>
+      <c r="E42" s="237"/>
+      <c r="F42" s="237"/>
+      <c r="G42" s="237"/>
+      <c r="H42" s="237"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14170,24 +14170,24 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="234"/>
-      <c r="C52" s="234"/>
-      <c r="D52" s="234"/>
-      <c r="E52" s="234"/>
-      <c r="F52" s="234"/>
-      <c r="G52" s="234"/>
-      <c r="H52" s="234"/>
+      <c r="B52" s="237"/>
+      <c r="C52" s="237"/>
+      <c r="D52" s="237"/>
+      <c r="E52" s="237"/>
+      <c r="F52" s="237"/>
+      <c r="G52" s="237"/>
+      <c r="H52" s="237"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="234" t="s">
+      <c r="B55" s="237" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="234"/>
-      <c r="D55" s="234"/>
-      <c r="E55" s="234"/>
-      <c r="F55" s="234"/>
-      <c r="G55" s="234"/>
-      <c r="H55" s="234"/>
+      <c r="C55" s="237"/>
+      <c r="D55" s="237"/>
+      <c r="E55" s="237"/>
+      <c r="F55" s="237"/>
+      <c r="G55" s="237"/>
+      <c r="H55" s="237"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14202,28 +14202,28 @@
       </c>
     </row>
     <row r="62" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="234"/>
-      <c r="C62" s="234"/>
-      <c r="D62" s="234"/>
-      <c r="E62" s="234"/>
-      <c r="F62" s="234"/>
-      <c r="G62" s="234"/>
-      <c r="H62" s="234"/>
+      <c r="B62" s="237"/>
+      <c r="C62" s="237"/>
+      <c r="D62" s="237"/>
+      <c r="E62" s="237"/>
+      <c r="F62" s="237"/>
+      <c r="G62" s="237"/>
+      <c r="H62" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B52:H52"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14293,36 +14293,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="234" t="s">
+      <c r="S2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234"/>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="234" t="s">
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
+      <c r="AA2" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="234"/>
+      <c r="AB2" s="237"/>
+      <c r="AC2" s="237"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15715,35 +15715,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="P2" s="234" t="s">
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
+      <c r="P2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="234"/>
-      <c r="S2" s="234"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234" t="s">
+      <c r="Q2" s="237"/>
+      <c r="R2" s="237"/>
+      <c r="S2" s="237"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="237"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -17150,20 +17150,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="246"/>
       <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
       <c r="R3" s="248"/>
@@ -18556,6 +18556,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18563,12 +18569,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18606,20 +18606,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
       <c r="S2" s="248"/>
       <c r="T2" s="248"/>
       <c r="U2" s="248"/>
@@ -19628,16 +19628,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19700,10 +19700,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="237" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="237"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19729,7 +19729,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>454968.8</v>
+        <v>483215.2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.7450000000000006E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2305000000000001</v>
+        <v>2.2740999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19788,10 +19788,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="237" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="234"/>
+      <c r="C15" s="237"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.9973135817630579E-2</v>
+        <v>9.4682513720786551E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19808,7 +19808,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90002686418236943</v>
+        <v>0.9053174862792136</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14782250000000002</v>
+        <v>0.14995449999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13746703265917032</v>
+        <v>0.13994518540326395</v>
       </c>
     </row>
   </sheetData>
@@ -19880,20 +19880,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="246"/>
       <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
       <c r="R3" s="248"/>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-31355.584616868127</v>
+        <v>-30707.755962473158</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20140,23 +20140,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8134.5072001711078</v>
+        <v>-8116.8234101099024</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5775.8304312245127</v>
+        <v>-5750.7453093893491</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4258.5004696878123</v>
+        <v>-4230.7878493503404</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4090.3821474179017</v>
+        <v>-4054.9292659967323</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1896.4292160979398</v>
+        <v>-1875.9051927323635</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20175,14 +20175,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-16467.239842794213</v>
+        <v>-15952.481045020277</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="234" t="s">
+      <c r="B13" s="237" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="234"/>
+      <c r="C13" s="237"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20198,14 +20198,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13746703265917032</v>
+        <v>0.13994518540326395</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="234" t="s">
+      <c r="B18" s="237" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="234"/>
+      <c r="C18" s="237"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20213,7 +20213,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-24155.649464599275</v>
+        <v>-24029.191027578687</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-16467.239842794213</v>
+        <v>-15952.481045020277</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-40622.889307393489</v>
+        <v>-39981.672072598965</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-53022.889307393489</v>
+        <v>-52381.672072598965</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="C26" s="141">
         <f ca="1">C24/C25</f>
-        <v>-10.512071631124799</v>
+        <v>-10.384946881958557</v>
       </c>
     </row>
   </sheetData>
@@ -20319,20 +20319,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -21264,10 +21264,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="234" t="s">
+      <c r="B37" s="237" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="234"/>
+      <c r="C37" s="237"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13746703265917032</v>
+        <v>0.13994518540326395</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21311,7 +21311,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>227739.75414815947</v>
+        <v>225267.94013107542</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>215339.75414815947</v>
+        <v>212867.94013107545</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21356,14 +21356,14 @@
       </c>
       <c r="C47" s="141">
         <f ca="1">C45/C46</f>
-        <v>42.692258950864286</v>
+        <v>42.202208590617651</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="234" t="s">
+      <c r="B49" s="237" t="s">
         <v>205</v>
       </c>
-      <c r="C49" s="234"/>
+      <c r="C49" s="237"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21419,10 +21419,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="234" t="s">
+      <c r="B57" s="237" t="s">
         <v>322</v>
       </c>
-      <c r="C57" s="234"/>
+      <c r="C57" s="237"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="C59" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13746703265917032</v>
+        <v>0.13994518540326395</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="C62" s="63">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>-76859.210100133845</v>
+        <v>-76034.514969238458</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21492,7 +21492,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>-89259.210100133845</v>
+        <v>-88434.514969238458</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21510,7 +21510,7 @@
       </c>
       <c r="C67" s="141">
         <f ca="1">C65/C66</f>
-        <v>-17.696116197488866</v>
+        <v>-17.532615973282802</v>
       </c>
     </row>
   </sheetData>
@@ -21562,10 +21562,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="237" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="234"/>
+      <c r="C4" s="237"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.512071631124799</v>
+        <v>-10.384946881958557</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21583,7 +21583,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C47</f>
-        <v>42.692258950864286</v>
+        <v>42.202208590617651</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C67</f>
-        <v>-17.696116197488866</v>
+        <v>-17.532615973282802</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="C9" s="141">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>15.805632990485584</v>
+        <v>15.755776643767003</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21628,7 +21628,7 @@
       </c>
       <c r="C11" s="153">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.82477125287709985</v>
+        <v>-0.83553469056610641</v>
       </c>
     </row>
   </sheetData>
@@ -21684,20 +21684,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
+      <c r="I2" s="237"/>
+      <c r="J2" s="237"/>
+      <c r="K2" s="237"/>
+      <c r="L2" s="237"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22060,10 +22060,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="234" t="s">
+      <c r="B20" s="237" t="s">
         <v>405</v>
       </c>
-      <c r="C20" s="234"/>
+      <c r="C20" s="237"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22164,20 +22164,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="234" t="s">
+      <c r="C3" s="237" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="234"/>
+      <c r="D3" s="237"/>
+      <c r="E3" s="237"/>
+      <c r="F3" s="237"/>
       <c r="G3" s="246"/>
       <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="234"/>
-      <c r="J3" s="234"/>
-      <c r="K3" s="234"/>
-      <c r="L3" s="234"/>
+      <c r="I3" s="237"/>
+      <c r="J3" s="237"/>
+      <c r="K3" s="237"/>
+      <c r="L3" s="237"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
       <c r="R3" s="248"/>
@@ -22352,7 +22352,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-964040.89169228077</v>
+        <v>-944123.12197827699</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22406,23 +22406,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13168.511488938682</v>
+        <v>-13139.884162555092</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19102.130728090644</v>
+        <v>-19019.167891433444</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27709.388313141331</v>
+        <v>-27529.066680310338</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-40195.002935423843</v>
+        <v>-39846.617718239992</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-58306.529278833121</v>
+        <v>-57675.509381477445</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22441,7 +22441,7 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-506292.34873897978</v>
+        <v>-490465.86881599115</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="C16" s="155">
         <f ca="1">C36</f>
-        <v>-134.25335279211089</v>
+        <v>-130.86362304718625</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13746703265917032</v>
+        <v>0.13994518540326395</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>454968.8</v>
+        <v>483215.2</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>467368.8</v>
+        <v>495615.19999999995</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22566,7 +22566,7 @@
       </c>
       <c r="C29" s="160">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-158481.56274442762</v>
+        <v>-157210.2458340163</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="C30" s="160">
         <f ca="1">L11</f>
-        <v>-506292.34873897978</v>
+        <v>-490465.86881599115</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22584,7 +22584,7 @@
       </c>
       <c r="C31" s="163">
         <f ca="1">C29+C30</f>
-        <v>-664773.91148340737</v>
+        <v>-647676.11465000745</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="C34" s="163">
         <f ca="1">C31+C32-C33</f>
-        <v>-677173.91148340737</v>
+        <v>-660076.11465000745</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22629,7 +22629,7 @@
       </c>
       <c r="C36" s="166">
         <f ca="1">C34/C35</f>
-        <v>-134.25335279211089</v>
+        <v>-130.86362304718625</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -23076,17 +23076,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -23431,7 +23431,7 @@
       <c r="R7" s="16"/>
       <c r="S7" s="16"/>
       <c r="T7" s="22">
-        <f t="shared" ref="T7:Z7" si="2">T5-T6</f>
+        <f t="shared" ref="T7:Y7" si="2">T5-T6</f>
         <v>1997</v>
       </c>
       <c r="U7" s="22">
@@ -23709,19 +23709,19 @@
         <v>20589</v>
       </c>
       <c r="T11" s="24">
-        <f t="shared" ref="T11:U11" si="5">SUM(T8:T10)</f>
+        <f t="shared" ref="T11" si="5">SUM(T8:T10)</f>
         <v>11054</v>
       </c>
       <c r="U11" s="24">
-        <f t="shared" ref="U11:V11" si="6">SUM(U8:U10)</f>
+        <f t="shared" ref="U11" si="6">SUM(U8:U10)</f>
         <v>5172</v>
       </c>
       <c r="V11" s="24">
-        <f t="shared" ref="V11:W11" si="7">SUM(V8:V10)</f>
+        <f t="shared" ref="V11" si="7">SUM(V8:V10)</f>
         <v>4973</v>
       </c>
       <c r="W11" s="24">
-        <f t="shared" ref="W11:X11" si="8">SUM(W8:W10)</f>
+        <f t="shared" ref="W11" si="8">SUM(W8:W10)</f>
         <v>6718</v>
       </c>
       <c r="X11" s="24">
@@ -23737,7 +23737,7 @@
         <v>8483</v>
       </c>
       <c r="AA11" s="24">
-        <f t="shared" ref="Z11:AA11" si="10">SUM(AA8:AA10)</f>
+        <f t="shared" ref="AA11" si="10">SUM(AA8:AA10)</f>
         <v>4713</v>
       </c>
       <c r="AC11" s="24">
@@ -24322,7 +24322,7 @@
         <v>5083</v>
       </c>
       <c r="AA20" s="25">
-        <f t="shared" ref="T20:AA20" si="13">AA19*AA$85</f>
+        <f t="shared" ref="AA20" si="13">AA19*AA$85</f>
         <v>5104</v>
       </c>
       <c r="AC20" s="25">
@@ -24481,7 +24481,7 @@
         <v>5083</v>
       </c>
       <c r="AA22" s="25">
-        <f t="shared" ref="T22:AA22" si="16">AA21*AA$85</f>
+        <f t="shared" ref="AA22" si="16">AA21*AA$85</f>
         <v>5104</v>
       </c>
       <c r="AC22" s="25">
@@ -24610,7 +24610,7 @@
         <v>-0.73</v>
       </c>
       <c r="AA24" s="64">
-        <f t="shared" ref="T24:AA24" si="18">AA23/AA$85</f>
+        <f t="shared" ref="AA24" si="18">AA23/AA$85</f>
         <v>-2.16</v>
       </c>
       <c r="AC24" s="64">
@@ -24742,7 +24742,7 @@
         <v>-0.73</v>
       </c>
       <c r="AA26" s="65">
-        <f t="shared" ref="T26:AA26" si="20">AA25/AA$85</f>
+        <f t="shared" ref="AA26" si="20">AA25/AA$85</f>
         <v>-2.16</v>
       </c>
       <c r="AB26" s="1"/>
@@ -25243,7 +25243,7 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="35">
-        <f t="shared" ref="T36:Z36" si="23">T37-T32</f>
+        <f t="shared" ref="T36:Y36" si="23">T37-T32</f>
         <v>147405</v>
       </c>
       <c r="U36" s="35">
@@ -25727,7 +25727,7 @@
         <v>80343</v>
       </c>
       <c r="AA43" s="22">
-        <f t="shared" ref="T43:AA43" si="27">AA40+AA42</f>
+        <f t="shared" ref="AA43" si="27">AA40+AA42</f>
         <v>99296</v>
       </c>
       <c r="AB43" s="1"/>
@@ -27076,7 +27076,7 @@
         <v>-3728</v>
       </c>
       <c r="AA69" s="63">
-        <f t="shared" ref="T69:AC69" si="33">AA5-AA6-AA11+AA13+AA14+AA16-AA17</f>
+        <f t="shared" ref="AA69:AC69" si="33">AA5-AA6-AA11+AA13+AA14+AA16-AA17</f>
         <v>-11033</v>
       </c>
       <c r="AC69" s="63">
@@ -27152,7 +27152,7 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="40">
-        <f t="shared" ref="T70:Z70" si="35">T18-T69</f>
+        <f t="shared" ref="T70:Y70" si="35">T18-T69</f>
         <v>0</v>
       </c>
       <c r="U70" s="40">
@@ -27287,7 +27287,7 @@
         <v>0</v>
       </c>
       <c r="AA71" s="42">
-        <f t="shared" ref="T71:AA71" si="39">AA37-(AA43+AA112)</f>
+        <f t="shared" ref="AA71" si="39">AA37-(AA43+AA112)</f>
         <v>0</v>
       </c>
       <c r="AB71" s="16"/>
@@ -27412,19 +27412,19 @@
         <v>4995</v>
       </c>
       <c r="T75" s="25">
-        <f t="shared" ref="T75:U75" si="41">T74*T85</f>
+        <f t="shared" ref="T75" si="41">T74*T85</f>
         <v>4313</v>
       </c>
       <c r="U75" s="25">
-        <f t="shared" ref="U75:V75" si="42">U74*U85</f>
+        <f t="shared" ref="U75" si="42">U74*U85</f>
         <v>4330</v>
       </c>
       <c r="V75" s="25">
-        <f t="shared" ref="V75:W75" si="43">V74*V85</f>
+        <f t="shared" ref="V75" si="43">V74*V85</f>
         <v>4362</v>
       </c>
       <c r="W75" s="25">
-        <f t="shared" ref="W75:X75" si="44">W74*W85</f>
+        <f t="shared" ref="W75" si="44">W74*W85</f>
         <v>4377</v>
       </c>
       <c r="X75" s="25">
@@ -27440,7 +27440,7 @@
         <v>5026</v>
       </c>
       <c r="AA75" s="25">
-        <f t="shared" ref="Z75:AA75" si="46">AA74*AA85</f>
+        <f t="shared" ref="AA75" si="46">AA74*AA85</f>
         <v>5044</v>
       </c>
       <c r="AC75" s="24">
@@ -27541,7 +27541,7 @@
         <v>0</v>
       </c>
       <c r="T77" s="25">
-        <f t="shared" ref="T77:Z77" si="48">T76*T85</f>
+        <f t="shared" ref="T77:Y77" si="48">T76*T85</f>
         <v>0</v>
       </c>
       <c r="U77" s="25">
@@ -27612,7 +27612,7 @@
         <v>4995</v>
       </c>
       <c r="T78" s="25">
-        <f t="shared" ref="T78:Z78" si="51">T75+T77</f>
+        <f t="shared" ref="T78:Y78" si="51">T75+T77</f>
         <v>4313</v>
       </c>
       <c r="U78" s="25">
@@ -27830,19 +27830,19 @@
         <v>0</v>
       </c>
       <c r="T82" s="45">
-        <f t="shared" ref="T82:U82" si="55">T81/T85</f>
+        <f t="shared" ref="T82" si="55">T81/T85</f>
         <v>0.13</v>
       </c>
       <c r="U82" s="45">
-        <f t="shared" ref="U82:V82" si="56">U81/U85</f>
+        <f t="shared" ref="U82" si="56">U81/U85</f>
         <v>0</v>
       </c>
       <c r="V82" s="45">
-        <f t="shared" ref="V82:W82" si="57">V81/V85</f>
+        <f t="shared" ref="V82" si="57">V81/V85</f>
         <v>0</v>
       </c>
       <c r="W82" s="45">
-        <f t="shared" ref="W82:X82" si="58">W81/W85</f>
+        <f t="shared" ref="W82" si="58">W81/W85</f>
         <v>0</v>
       </c>
       <c r="X82" s="45">
@@ -27858,7 +27858,7 @@
         <v>0</v>
       </c>
       <c r="AA82" s="45">
-        <f t="shared" ref="Z82:AA82" si="60">AA81/AA85</f>
+        <f t="shared" ref="AA82" si="60">AA81/AA85</f>
         <v>0</v>
       </c>
       <c r="AC82" s="71">
@@ -27959,7 +27959,7 @@
         <v>0</v>
       </c>
       <c r="AA83" s="46">
-        <f t="shared" ref="T83:AA83" si="63">IF(AND(AA15&gt;0,AA16&lt;0),-(AA16)/AA15,0)</f>
+        <f t="shared" ref="AA83" si="63">IF(AND(AA15&gt;0,AA16&lt;0),-(AA16)/AA15,0)</f>
         <v>0</v>
       </c>
       <c r="AC83" s="46">
@@ -28170,7 +28170,7 @@
         <v>-7.0937545707181514E-3</v>
       </c>
       <c r="AA89" s="48">
-        <f t="shared" ref="T89:AA96" si="72">IF(Z5=0,
+        <f t="shared" ref="AA89:AA96" si="72">IF(Z5=0,
 IF(AA5=0,0,IF(AA5&gt;0,1,-1)),
 (AA5-Z5)/ABS(Z5)
 )</f>
@@ -28771,7 +28771,7 @@
         <v>-12.674556213017752</v>
       </c>
       <c r="AA97" s="52">
-        <f t="shared" ref="T97:AA97" si="80">IF(Z15=0,
+        <f t="shared" ref="AA97" si="80">IF(Z15=0,
 IF(AA15=0,0,IF(AA15&gt;0,1,-1)),
 (AA15-Z15)/ABS(Z15)
 )</f>
@@ -28884,7 +28884,7 @@
         <v>-5.3079526226734348</v>
       </c>
       <c r="AA98" s="52">
-        <f t="shared" ref="T98:AA98" si="88">IF(Z18=0,
+        <f t="shared" ref="AA98" si="88">IF(Z18=0,
 IF(AA18=0,0,IF(AA18&gt;0,1,-1)),
 (AA18-Z18)/ABS(Z18)
 )</f>
@@ -28972,7 +28972,7 @@
         <v>0.39382779700964865</v>
       </c>
       <c r="AA101" s="50">
-        <f t="shared" ref="T101:AA101" si="90">AA7/AA5</f>
+        <f t="shared" ref="AA101" si="90">AA7/AA5</f>
         <v>0.40358382936507936</v>
       </c>
       <c r="AC101" s="50">
@@ -29043,7 +29043,7 @@
         <v>-0.23097886130956766</v>
       </c>
       <c r="AA102" s="50">
-        <f t="shared" ref="T102:AA102" si="92">AA12/AA5</f>
+        <f t="shared" ref="AA102" si="92">AA12/AA5</f>
         <v>0.11135912698412699</v>
       </c>
       <c r="AC102" s="50">
@@ -29117,7 +29117,7 @@
         <v>-0.31531266111806733</v>
       </c>
       <c r="AA103" s="55">
-        <f t="shared" ref="T103:AA103" si="94">AA111/AA5</f>
+        <f t="shared" ref="AA103" si="94">AA111/AA5</f>
         <v>-0.67261904761904767</v>
       </c>
       <c r="AB103" s="1"/>
@@ -29235,7 +29235,7 @@
         <v>0</v>
       </c>
       <c r="AA106" s="80">
-        <f t="shared" ref="T106:AA106" si="97">IF(AND(AA83&gt;=0,AA12&gt;=0),AA83,0)</f>
+        <f t="shared" ref="AA106" si="97">IF(AND(AA83&gt;=0,AA12&gt;=0),AA83,0)</f>
         <v>0</v>
       </c>
       <c r="AC106" s="80">
@@ -29306,7 +29306,7 @@
         <v>41270</v>
       </c>
       <c r="AA107" s="25">
-        <f t="shared" ref="T107:AA107" si="100">AA29+AA34</f>
+        <f t="shared" ref="AA107" si="100">AA29+AA34</f>
         <v>38137</v>
       </c>
       <c r="AC107" s="25">
@@ -29397,7 +29397,7 @@
         <v>45031</v>
       </c>
       <c r="AA108" s="25">
-        <f t="shared" ref="T108:AA108" si="102">AA39+AA41</f>
+        <f t="shared" ref="AA108" si="102">AA39+AA41</f>
         <v>50537</v>
       </c>
       <c r="AC108" s="25">
@@ -29515,7 +29515,7 @@
         <v>-3636</v>
       </c>
       <c r="AA110" s="125">
-        <f t="shared" ref="T110:AA110" si="104">AA60+AA61</f>
+        <f t="shared" ref="AA110" si="104">AA60+AA61</f>
         <v>-2556</v>
       </c>
       <c r="AC110" s="125">
@@ -29586,7 +29586,7 @@
         <v>-4281</v>
       </c>
       <c r="AA111" s="125">
-        <f t="shared" ref="T111:AA111" si="106">AA17+AA18</f>
+        <f t="shared" ref="AA111" si="106">AA17+AA18</f>
         <v>-10848</v>
       </c>
       <c r="AC111" s="125">
@@ -29657,7 +29657,7 @@
         <v>124989</v>
       </c>
       <c r="AA112" s="125">
-        <f t="shared" ref="T112:AA112" si="108">AA49+AA48</f>
+        <f t="shared" ref="AA112" si="108">AA49+AA48</f>
         <v>103143</v>
       </c>
       <c r="AC112" s="125">
@@ -29745,7 +29745,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29811,12 +29811,12 @@
         <v>43.23</v>
       </c>
       <c r="AA117" s="64">
-        <f t="shared" ref="T117:AA117" si="110">AA116/AA85</f>
+        <f t="shared" ref="AA117" si="110">AA116/AA85</f>
         <v>128.32</v>
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30206,7 +30206,7 @@
         <v>16128</v>
       </c>
       <c r="AA131" s="25">
-        <f t="shared" ref="T131:AA131" si="120">AB5</f>
+        <f t="shared" ref="AA131" si="120">AB5</f>
         <v>0</v>
       </c>
       <c r="AC131" s="49"/>
@@ -30231,7 +30231,7 @@
       <c r="P132" s="49"/>
       <c r="Q132" s="49"/>
       <c r="T132" s="227" t="str">
-        <f t="shared" ref="T132:Z132" si="121">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
+        <f t="shared" ref="T132:Y132" si="121">IF(T131&gt;T130, "BEAT", IF(T131&lt;T129, "MISSED", "MET"))</f>
         <v>MET</v>
       </c>
       <c r="U132" s="227" t="str">
@@ -30402,7 +30402,7 @@
         <v>0.40358382936507936</v>
       </c>
       <c r="AA135" s="73">
-        <f t="shared" ref="T135:AA135" si="129">AB101</f>
+        <f t="shared" ref="AA135" si="129">AB101</f>
         <v>0</v>
       </c>
       <c r="AC135" s="49"/>
@@ -30427,7 +30427,7 @@
       <c r="P136" s="49"/>
       <c r="Q136" s="49"/>
       <c r="T136" s="227" t="str">
-        <f t="shared" ref="T136:Z136" si="130">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
+        <f t="shared" ref="T136:Y136" si="130">IF(T135&gt;T134, "BEAT", IF(T135&lt;T133, "MISSED", "MET"))</f>
         <v>BEAT</v>
       </c>
       <c r="U136" s="227" t="str">
@@ -30592,7 +30592,7 @@
         <v>26.952935110849229</v>
       </c>
       <c r="AA141" s="117">
-        <f t="shared" ref="T141:AA141" si="133">AA30/AA5*90</f>
+        <f t="shared" ref="AA141" si="133">AA30/AA5*90</f>
         <v>22.505580357142854</v>
       </c>
       <c r="AC141" s="117">
@@ -30653,7 +30653,7 @@
         <v>551.09234507897929</v>
       </c>
       <c r="AA142" s="117">
-        <f t="shared" ref="T142:AA142" si="135">AA31/AA6*365</f>
+        <f t="shared" ref="AA142" si="135">AA31/AA6*365</f>
         <v>474.01808919846138</v>
       </c>
       <c r="AC142" s="117">
@@ -30714,7 +30714,7 @@
         <v>78.287970838396106</v>
       </c>
       <c r="AA143" s="117">
-        <f t="shared" ref="T143:AA143" si="137">AA38/AA6*90</f>
+        <f t="shared" ref="AA143" si="137">AA38/AA6*90</f>
         <v>81.925356066119136</v>
       </c>
       <c r="AC143" s="117">
@@ -30747,19 +30747,19 @@
         <v>44.890025490651112</v>
       </c>
       <c r="T144" s="117">
-        <f t="shared" ref="T144:U144" si="139">T141+T142-T143</f>
+        <f t="shared" ref="T144" si="139">T141+T142-T143</f>
         <v>322.90541880567213</v>
       </c>
       <c r="U144" s="117">
-        <f t="shared" ref="U144:V144" si="140">U141+U142-U143</f>
+        <f t="shared" ref="U144" si="140">U141+U142-U143</f>
         <v>404.87276502961197</v>
       </c>
       <c r="V144" s="117">
-        <f t="shared" ref="V144:W144" si="141">V141+V142-V143</f>
+        <f t="shared" ref="V144" si="141">V141+V142-V143</f>
         <v>459.78433741227212</v>
       </c>
       <c r="W144" s="117">
-        <f t="shared" ref="W144:X144" si="142">W141+W142-W143</f>
+        <f t="shared" ref="W144" si="142">W141+W142-W143</f>
         <v>359.18853823960967</v>
       </c>
       <c r="X144" s="117">
@@ -30775,7 +30775,7 @@
         <v>499.75730935143241</v>
       </c>
       <c r="AA144" s="117">
-        <f t="shared" ref="Z144:AA144" si="144">AA141+AA142-AA143</f>
+        <f t="shared" ref="AA144" si="144">AA141+AA142-AA143</f>
         <v>414.59831348948507</v>
       </c>
       <c r="AC144" s="117">
@@ -30836,7 +30836,7 @@
         <v>0.40424978005996731</v>
       </c>
       <c r="AA145" s="117">
-        <f t="shared" ref="T145:AA145" si="147">AA108/AA49</f>
+        <f t="shared" ref="AA145" si="147">AA108/AA49</f>
         <v>0.57728861575015422</v>
       </c>
       <c r="AC145" s="117">
@@ -30897,7 +30897,7 @@
         <v>3.3763039301937268E-2</v>
       </c>
       <c r="AA146" s="178">
-        <f t="shared" ref="T146:AA146" si="149">(AA108-AA107)/AA49</f>
+        <f t="shared" ref="AA146" si="149">(AA108-AA107)/AA49</f>
         <v>0.14164629549244934</v>
       </c>
       <c r="AC146" s="178">
@@ -30958,7 +30958,7 @@
         <v>1.686293472196392</v>
       </c>
       <c r="AA147" s="117">
-        <f t="shared" ref="T147:AA147" si="151">(AA107+AA30)/AA40</f>
+        <f t="shared" ref="AA147" si="151">(AA107+AA30)/AA40</f>
         <v>1.1822259601906364</v>
       </c>
       <c r="AC147" s="117">
@@ -31019,7 +31019,7 @@
         <v>2.3119583410823878</v>
       </c>
       <c r="AA148" s="117">
-        <f t="shared" ref="T148:AA148" si="153">AA32/AA40</f>
+        <f t="shared" ref="AA148" si="153">AA32/AA40</f>
         <v>1.6039529015979814</v>
       </c>
       <c r="AC148" s="117">
@@ -31080,7 +31080,7 @@
         <v>N/A</v>
       </c>
       <c r="AA149" s="180">
-        <f t="shared" ref="T149:AA149" si="155">IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
+        <f t="shared" ref="AA149" si="155">IF(AA13&gt;=0,"N/A",IF(AA12&lt;=0,"N/A",AA12/-AA13))</f>
         <v>46.051282051282051</v>
       </c>
       <c r="AC149" s="180" t="str">
@@ -31122,7 +31122,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-42.748815165876771</v>
+        <v>-45.402843601895725</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31159,7 +31159,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.7326825291064667</v>
+        <v>8.2127603801374676</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31220,7 +31220,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.1971487971487971</v>
+        <v>5.5198099198099193</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31281,7 +31281,7 @@
       </c>
       <c r="AC153" s="142">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>454968.8</v>
+        <v>483215.2</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31337,12 +31337,12 @@
         <v>234629.97999999998</v>
       </c>
       <c r="AA154" s="142">
-        <f t="shared" ref="T154:AA154" si="157">AA153+AA108-AA107+AA48+AA45</f>
+        <f t="shared" ref="AA154" si="157">AA153+AA108-AA107+AA48+AA45</f>
         <v>675247.08</v>
       </c>
       <c r="AC154" s="142">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>482969.8</v>
+        <v>511216.19999999995</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31379,7 +31379,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="182">
         <f ca="1">AC154/AC5</f>
-        <v>8.4684001963809781</v>
+        <v>8.9636730256697987</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31416,7 +31416,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="182">
         <f ca="1">AC154/AC12</f>
-        <v>-6272.335064935065</v>
+        <v>-6639.1714285714279</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31472,7 +31472,7 @@
         <v>-3161</v>
       </c>
       <c r="AA157" s="63">
-        <f t="shared" ref="T157:AA157" si="159">AA59-AA54+AA110+AA65</f>
+        <f t="shared" ref="AA157" si="159">AA59-AA54+AA110+AA65</f>
         <v>3764</v>
       </c>
       <c r="AC157" s="63">
@@ -31551,7 +31551,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-40.459653179190752</v>
+        <v>-42.971560693641621</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31588,7 +31588,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-85.739357358423575</v>
+        <v>-90.753807917628251</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31625,7 +31625,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-2.4715980524378817E-2</v>
+        <v>-2.3271205044874416E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31662,7 +31662,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-2.3392461197339249E-2</v>
+        <v>-2.202505219206681E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31773,7 +31773,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.514526710402999E-3</v>
+        <v>3.3090846479994834E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32051,7 +32051,7 @@
         <v>8.2113012335853561</v>
       </c>
       <c r="AA172" s="71">
-        <f t="shared" ref="T172:AA172" si="166">AA107/AA75</f>
+        <f t="shared" ref="AA172" si="166">AA107/AA75</f>
         <v>7.5608643933386199</v>
       </c>
       <c r="AC172" s="71">
@@ -32084,7 +32084,7 @@
         <v>0.25100546560791998</v>
       </c>
       <c r="T173" s="153" t="e">
-        <f t="shared" ref="T173:Y173" si="167">T54/T59</f>
+        <f t="shared" ref="T173:X173" si="167">T54/T59</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U173" s="153" t="e">
@@ -32145,7 +32145,7 @@
         <v>4.6052258149963103E-2</v>
       </c>
       <c r="T174" s="153">
-        <f t="shared" ref="T174:Y174" si="168">T54/T5</f>
+        <f t="shared" ref="T174:X174" si="168">T54/T5</f>
         <v>0</v>
       </c>
       <c r="U174" s="153">
@@ -32234,7 +32234,7 @@
         <v>-0.74830879426979702</v>
       </c>
       <c r="AA175" s="71">
-        <f t="shared" ref="T175:AA175" si="170">(AA107-AA108)/AA75</f>
+        <f t="shared" ref="AA175" si="170">(AA107-AA108)/AA75</f>
         <v>-2.4583663758921492</v>
       </c>
       <c r="AC175" s="71">
@@ -32276,7 +32276,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="153">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-2.7254616140711188E-2</v>
+        <v>-2.5661444424761471E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -32332,7 +32332,7 @@
         <v>0.2678058481255064</v>
       </c>
       <c r="AA177" s="153">
-        <f t="shared" ref="T177:AA177" si="172">-AA110/AA5</f>
+        <f t="shared" ref="AA177" si="172">-AA110/AA5</f>
         <v>0.15848214285714285</v>
       </c>
       <c r="AC177" s="153">
@@ -32365,7 +32365,7 @@
         <v>1.5103640301124059</v>
       </c>
       <c r="T178" s="153" t="e">
-        <f t="shared" ref="T178:Y178" si="173">-(T110/T59)</f>
+        <f t="shared" ref="T178:X178" si="173">-(T110/T59)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U178" s="153" t="e">
@@ -32426,7 +32426,7 @@
         <v>1.2511532547411583</v>
       </c>
       <c r="T179" s="153" t="e">
-        <f t="shared" ref="T179:Y179" si="174">-T110/T53</f>
+        <f t="shared" ref="T179:X179" si="174">-T110/T53</f>
         <v>#DIV/0!</v>
       </c>
       <c r="U179" s="153" t="e">
@@ -33386,7 +33386,7 @@
         <v>-5.687782253142927E-2</v>
       </c>
       <c r="AA201" s="80">
-        <f t="shared" ref="T201:AA205" si="192">IF(Z187=0,
+        <f t="shared" ref="AA201:AA205" si="192">IF(Z187=0,
 IF(AA187=0,0,IF(AA187&gt;0,1,-1)),
 (AA187-Z187)/ABS(Z187)
 )</f>
@@ -33960,7 +33960,7 @@
         <v>170</v>
       </c>
       <c r="AA220" s="61">
-        <f t="shared" ref="T220:AA220" si="197">AA190+AA219</f>
+        <f t="shared" ref="AA220" si="197">AA190+AA219</f>
         <v>1344</v>
       </c>
       <c r="AC220" s="63">
@@ -34022,15 +34022,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="234" t="s">
+      <c r="B4" s="237" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="E4" s="234" t="s">
+      <c r="C4" s="237"/>
+      <c r="E4" s="237" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
+      <c r="F4" s="237"/>
+      <c r="G4" s="237"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -34054,7 +34054,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>454968.8</v>
+        <v>483215.2</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34074,7 +34074,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>482969.8</v>
+        <v>511216.19999999995</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -34094,7 +34094,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC150</f>
-        <v>-42.748815165876771</v>
+        <v>-45.402843601895725</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -34114,7 +34114,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>7.7326825291064667</v>
+        <v>8.2127603801374676</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -34134,7 +34134,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>5.1971487971487971</v>
+        <v>5.5198099198099193</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34154,7 +34154,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC155</f>
-        <v>8.4684001963809781</v>
+        <v>8.9636730256697987</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34163,18 +34163,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>-6272.335064935065</v>
+        <v>-6639.1714285714279</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="234" t="s">
+      <c r="B15" s="237" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="234"/>
-      <c r="E15" s="234" t="s">
+      <c r="C15" s="237"/>
+      <c r="E15" s="237" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="234"/>
+      <c r="F15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34225,14 +34225,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="234" t="s">
+      <c r="B21" s="237" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="234"/>
-      <c r="E21" s="234" t="s">
+      <c r="C21" s="237"/>
+      <c r="E21" s="237" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="234"/>
+      <c r="F21" s="237"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34301,14 +34301,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="234" t="s">
+      <c r="B29" s="237" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="234"/>
-      <c r="E29" s="234" t="s">
+      <c r="C29" s="237"/>
+      <c r="E29" s="237" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="234"/>
+      <c r="F29" s="237"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34384,14 +34384,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="234" t="s">
+      <c r="B37" s="237" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="234"/>
-      <c r="E37" s="234" t="s">
+      <c r="C37" s="237"/>
+      <c r="E37" s="237" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="234"/>
+      <c r="F37" s="237"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34399,7 +34399,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC162</f>
-        <v>-2.3392461197339249E-2</v>
+        <v>-2.202505219206681E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -34415,7 +34415,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC161</f>
-        <v>-2.4715980524378817E-2</v>
+        <v>-2.3271205044874416E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -34456,18 +34456,18 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC165</f>
-        <v>3.514526710402999E-3</v>
+        <v>3.3090846479994834E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="234" t="s">
+      <c r="B45" s="237" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="234"/>
-      <c r="E45" s="234" t="s">
+      <c r="C45" s="237"/>
+      <c r="E45" s="237" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="234"/>
+      <c r="F45" s="237"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34500,18 +34500,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC176</f>
-        <v>-2.7254616140711188E-2</v>
+        <v>-2.5661444424761471E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="234" t="s">
+      <c r="B51" s="237" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="234"/>
-      <c r="E51" s="234" t="s">
+      <c r="C51" s="237"/>
+      <c r="E51" s="237" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="234"/>
+      <c r="F51" s="237"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34679,7 +34679,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>90.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34708,7 +34708,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>454968.8</v>
+        <v>483215.2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34737,7 +34737,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>482969.8</v>
+        <v>511216.19999999995</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34766,7 +34766,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC150</f>
-        <v>-42.748815165876771</v>
+        <v>-45.402843601895725</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34795,7 +34795,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>7.7326825291064667</v>
+        <v>8.2127603801374676</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34824,7 +34824,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>5.1971487971487971</v>
+        <v>5.5198099198099193</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34853,7 +34853,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC155</f>
-        <v>8.4684001963809781</v>
+        <v>8.9636730256697987</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34882,7 +34882,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>-6272.335064935065</v>
+        <v>-6639.1714285714279</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35655,7 +35655,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC162</f>
-        <v>-2.3392461197339249E-2</v>
+        <v>-2.202505219206681E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35684,7 +35684,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>-2.4715980524378817E-2</v>
+        <v>-2.3271205044874416E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35771,7 +35771,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC165</f>
-        <v>3.514526710402999E-3</v>
+        <v>3.3090846479994834E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36007,7 +36007,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC176</f>
-        <v>-2.7254616140711188E-2</v>
+        <v>-2.5661444424761471E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36545,14 +36545,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="240" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="241"/>
+      <c r="F3" s="242" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="241"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36619,19 +36619,19 @@
       <c r="B7" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="241">
+      <c r="C7" s="238">
         <f>Statement!AA89</f>
         <v>0.18789128673491934</v>
       </c>
-      <c r="D7" s="242"/>
-      <c r="F7" s="241">
+      <c r="D7" s="239"/>
+      <c r="F7" s="238">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.25421883505715842</v>
       </c>
-      <c r="G7" s="242"/>
+      <c r="G7" s="239"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -36658,19 +36658,19 @@
       <c r="B9" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="241">
+      <c r="C9" s="238">
         <f>Statement!AA90</f>
         <v>0.16877278250303768</v>
       </c>
-      <c r="D9" s="242"/>
-      <c r="F9" s="241">
+      <c r="D9" s="239"/>
+      <c r="F9" s="238">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>3.2413867124610925E-2</v>
       </c>
-      <c r="G9" s="242"/>
+      <c r="G9" s="239"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -36697,19 +36697,19 @@
       <c r="B11" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="241">
+      <c r="C11" s="238">
         <f>Statement!AA91</f>
         <v>0.21731812231157657</v>
       </c>
-      <c r="D11" s="242"/>
-      <c r="F11" s="241">
+      <c r="D11" s="239"/>
+      <c r="F11" s="238">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.83766233766233766</v>
       </c>
-      <c r="G11" s="242"/>
+      <c r="G11" s="239"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -36736,19 +36736,19 @@
       <c r="B13" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="241">
+      <c r="C13" s="238">
         <f>Statement!AA95</f>
         <v>-0.44441824826122833</v>
       </c>
-      <c r="D13" s="242"/>
-      <c r="F13" s="241">
+      <c r="D13" s="239"/>
+      <c r="F13" s="238">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-0.29845192021434952</v>
       </c>
-      <c r="G13" s="242"/>
+      <c r="G13" s="239"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -36775,19 +36775,19 @@
       <c r="B15" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="241">
+      <c r="C15" s="238">
         <f>Statement!AA96</f>
         <v>1.572704081632653</v>
       </c>
-      <c r="D15" s="242"/>
-      <c r="F15" s="241">
+      <c r="D15" s="239"/>
+      <c r="F15" s="238">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5654911838790933</v>
       </c>
-      <c r="G15" s="242"/>
+      <c r="G15" s="239"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -36814,19 +36814,19 @@
       <c r="B17" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="241">
+      <c r="C17" s="238">
         <f>Statement!AA98</f>
         <v>-1.9594957081545064</v>
       </c>
-      <c r="D17" s="242"/>
-      <c r="F17" s="241">
+      <c r="D17" s="239"/>
+      <c r="F17" s="238">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-2.781014393420151</v>
       </c>
-      <c r="G17" s="242"/>
+      <c r="G17" s="239"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -36853,22 +36853,22 @@
       <c r="B19" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="241">
+      <c r="C19" s="238">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.1314184536690932E-3</v>
       </c>
-      <c r="D19" s="242"/>
-      <c r="F19" s="241">
+      <c r="D19" s="239"/>
+      <c r="F19" s="238">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.16823071641107806</v>
       </c>
-      <c r="G19" s="242"/>
+      <c r="G19" s="239"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -36895,22 +36895,22 @@
       <c r="B21" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="241">
+      <c r="C21" s="238">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-1.9589041095890414</v>
       </c>
-      <c r="D21" s="242"/>
-      <c r="F21" s="241">
+      <c r="D21" s="239"/>
+      <c r="F21" s="238">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.2238805970149254</v>
       </c>
-      <c r="G21" s="242"/>
+      <c r="G21" s="239"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36958,22 +36958,22 @@
       <c r="B25" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="241">
+      <c r="C25" s="238">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14882878219231266</v>
       </c>
-      <c r="D25" s="242"/>
-      <c r="F25" s="241">
+      <c r="D25" s="239"/>
+      <c r="F25" s="238">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.12781095159446068</v>
       </c>
-      <c r="G25" s="242"/>
+      <c r="G25" s="239"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37000,22 +37000,22 @@
       <c r="B27" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="241">
+      <c r="C27" s="238">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.23950910530482977</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="F27" s="241">
+      <c r="D27" s="239"/>
+      <c r="F27" s="238">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.58974358974358976</v>
       </c>
-      <c r="G27" s="242"/>
+      <c r="G27" s="239"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37042,22 +37042,22 @@
       <c r="B29" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="241">
+      <c r="C29" s="238">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18467798732295171</v>
       </c>
-      <c r="D29" s="242"/>
-      <c r="F29" s="241">
+      <c r="D29" s="239"/>
+      <c r="F29" s="238">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28187976291278577</v>
       </c>
-      <c r="G29" s="242"/>
+      <c r="G29" s="239"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37084,22 +37084,22 @@
       <c r="B31" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="241">
+      <c r="C31" s="238">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>6.3456926766279287E-2</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="F31" s="241">
+      <c r="D31" s="239"/>
+      <c r="F31" s="238">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.30518451437627347</v>
       </c>
-      <c r="G31" s="242"/>
+      <c r="G31" s="239"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -37126,25 +37126,37 @@
       <c r="B33" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C33" s="241">
+      <c r="C33" s="238">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.11624203821656051</v>
       </c>
-      <c r="D33" s="242"/>
-      <c r="F33" s="241">
+      <c r="D33" s="239"/>
+      <c r="F33" s="238">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33428300094966762</v>
       </c>
-      <c r="G33" s="242"/>
+      <c r="G33" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -37161,18 +37173,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16078511-71B9-D640-9378-1F8CE9F92D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8A4BB0-EEE5-9B47-8B33-F7A3B38A3668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="4" activeTab="13" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -132,7 +132,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -142,12 +163,21 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2322,6 +2352,9 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2331,15 +2364,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2347,6 +2371,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -12575,7 +12605,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="C12">
-            <v>4.4999999999999998E-2</v>
+            <v>4.3999999999999997E-2</v>
           </cell>
         </row>
       </sheetData>
@@ -12783,7 +12813,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12801,12 +12831,10 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
-    <v>23.75</v>
-    <v>2.2740999999999998</v>
-    <v>4.13</v>
-    <v>4.5053000000000003E-2</v>
-    <v>-0.01</v>
-    <v>-1.0439999999999999E-4</v>
+    <v>28.73</v>
+    <v>2.2724000000000002</v>
+    <v>1.2304999999999999</v>
+    <v>1.0104E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12814,35 +12842,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>95.94</v>
+    <v>123.23</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46269.899596041403</v>
+    <v>46287.768220289065</v>
     <v>0</v>
-    <v>91.87</v>
-    <v>506309610200</v>
+    <v>120.075</v>
+    <v>650118980224</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>92.45</v>
+    <v>120.16</v>
     <v>0</v>
-    <v>91.67</v>
-    <v>95.8</v>
-    <v>95.79</v>
+    <v>121.78</v>
+    <v>123.01049999999999</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>97334975</v>
-    <v>97208231</v>
+    <v>65460673</v>
+    <v>102259506</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12854,30 +12896,30 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>48.06</v>
+    <v>50.16</v>
     <v>39.47</v>
-    <v>-0.34</v>
-    <v>-7.0889999999999998E-3</v>
+    <v>-0.35</v>
+    <v>-7.0030000000000005E-3</v>
     <v>US</v>
-    <v>47.68</v>
+    <v>49.76</v>
     <v>Index</v>
-    <v>3</v>
-    <v>47.32</v>
+    <v>6</v>
+    <v>49.51</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>47.66</v>
-    <v>47.96</v>
-    <v>47.62</v>
+    <v>49.53</v>
+    <v>49.98</v>
+    <v>49.63</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12899,8 +12941,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12921,7 +12961,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12931,6 +12970,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12966,7 +13010,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -12977,16 +13021,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13080,19 +13121,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13164,9 +13199,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13174,9 +13206,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13664,18 +13693,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="234" t="s">
+      <c r="B2" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="E2" s="234" t="s">
+      <c r="C2" s="236"/>
+      <c r="E2" s="235" t="s">
         <v>287</v>
       </c>
-      <c r="F2" s="235"/>
-      <c r="H2" s="234" t="s">
+      <c r="F2" s="236"/>
+      <c r="H2" s="235" t="s">
         <v>328</v>
       </c>
-      <c r="I2" s="235"/>
+      <c r="I2" s="236"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="184" t="s">
@@ -13690,7 +13719,7 @@
       </c>
       <c r="F3" s="186">
         <f ca="1">Statement!AC153</f>
-        <v>483215.2</v>
+        <v>620464.96199999994</v>
       </c>
       <c r="H3" s="184" t="str">
         <f>'AVG target price'!B5</f>
@@ -13698,7 +13727,7 @@
       </c>
       <c r="I3" s="210">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.384946881958557</v>
+        <v>-10.298865501047842</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13714,7 +13743,7 @@
       </c>
       <c r="F4" s="187">
         <f ca="1">Statement!AC154</f>
-        <v>511216.19999999995</v>
+        <v>648465.96199999994</v>
       </c>
       <c r="H4" s="184" t="str">
         <f>'AVG target price'!B6</f>
@@ -13722,7 +13751,7 @@
       </c>
       <c r="I4" s="210">
         <f ca="1">'AVG target price'!C6</f>
-        <v>42.202208590617651</v>
+        <v>41.863100153571963</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13731,7 +13760,7 @@
       </c>
       <c r="C5" s="207" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
       <c r="E5" s="184" t="s">
         <v>243</v>
@@ -13753,16 +13782,16 @@
       <c r="B6" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="207" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>95.79</v>
+      <c r="C6" s="207" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="184" t="s">
         <v>237</v>
       </c>
       <c r="F6" s="189">
         <f ca="1">Statement!AC150</f>
-        <v>-45.402843601895725</v>
+        <v>-58.298815165876768</v>
       </c>
       <c r="H6" s="184" t="str">
         <f>'AVG target price'!B8</f>
@@ -13770,7 +13799,7 @@
       </c>
       <c r="I6" s="210">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-17.532615973282802</v>
+        <v>-17.419475957511299</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13779,14 +13808,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>4.13</v>
+        <v>1.2304999999999999</v>
       </c>
       <c r="E7" s="185" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="190">
         <f ca="1">Statement!AC151</f>
-        <v>8.2127603801374676</v>
+        <v>10.545467231115865</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -13794,23 +13823,23 @@
       </c>
       <c r="I7" s="211">
         <f ca="1">'AVG target price'!C9</f>
-        <v>15.755776643767003</v>
+        <v>15.720804883676134</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.01</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="184" t="s">
         <v>265</v>
       </c>
       <c r="F8" s="191">
         <f ca="1">Statement!AC161</f>
-        <v>-2.3271205044874416E-2</v>
+        <v>-1.8123505256046998E-2</v>
       </c>
       <c r="H8" s="183" t="str">
         <f>'AVG target price'!B11</f>
@@ -13818,7 +13847,7 @@
       </c>
       <c r="I8" s="212">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.83553469056610641</v>
+        <v>-0.87219948798130131</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13827,23 +13856,23 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.5053000000000003E-2</v>
+        <v>1.0104E-2</v>
       </c>
       <c r="E9" s="184" t="s">
         <v>288</v>
       </c>
       <c r="F9" s="191">
         <f ca="1">Statement!AC162</f>
-        <v>-2.202505219206681E-2</v>
+        <v>-1.7153007263607582E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="184" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-1.0439999999999999E-4</v>
+      <c r="C10" s="72" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="184" t="s">
         <v>293</v>
@@ -13882,7 +13911,7 @@
       </c>
       <c r="C12" s="208" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>23.75</v>
+        <v>28.73</v>
       </c>
       <c r="E12" s="184" t="s">
         <v>97</v>
@@ -13898,7 +13927,7 @@
       </c>
       <c r="C13" s="208" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2740999999999998</v>
+        <v>2.2724000000000002</v>
       </c>
       <c r="E13" s="184" t="s">
         <v>99</v>
@@ -13914,7 +13943,7 @@
       </c>
       <c r="C14" s="209" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>97208231</v>
+        <v>102259506</v>
       </c>
       <c r="E14" s="185" t="s">
         <v>100</v>
@@ -13930,7 +13959,7 @@
       </c>
       <c r="F15" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-2.5661444424761471E-2</v>
+        <v>-1.9985012465538708E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13943,10 +13972,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="236" t="s">
+      <c r="B17" s="237" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="236"/>
+      <c r="C17" s="237"/>
       <c r="E17" s="183" t="s">
         <v>296</v>
       </c>
@@ -14019,14 +14048,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="236" t="s">
+      <c r="B25" s="237" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="236"/>
-      <c r="E25" s="234" t="s">
+      <c r="C25" s="237"/>
+      <c r="E25" s="235" t="s">
         <v>381</v>
       </c>
-      <c r="F25" s="235"/>
+      <c r="F25" s="236"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="183" t="s">
@@ -14035,12 +14064,12 @@
       <c r="C26" s="169">
         <v>0.21</v>
       </c>
-      <c r="E26" s="184" t="e" vm="2">
+      <c r="E26" s="184" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="222" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>47.62</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14055,7 +14084,7 @@
       </c>
       <c r="F27" s="223">
         <f ca="1">F26/1000</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14075,15 +14104,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="237" t="s">
+      <c r="B33" s="234" t="s">
         <v>351</v>
       </c>
-      <c r="C33" s="237"/>
-      <c r="D33" s="237"/>
-      <c r="E33" s="237"/>
-      <c r="F33" s="237"/>
-      <c r="G33" s="237"/>
-      <c r="H33" s="237"/>
+      <c r="C33" s="234"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="234"/>
+      <c r="G33" s="234"/>
+      <c r="H33" s="234"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14102,24 +14131,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="237"/>
-      <c r="C39" s="237"/>
-      <c r="D39" s="237"/>
-      <c r="E39" s="237"/>
-      <c r="F39" s="237"/>
-      <c r="G39" s="237"/>
-      <c r="H39" s="237"/>
+      <c r="B39" s="234"/>
+      <c r="C39" s="234"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="237" t="s">
+      <c r="B42" s="234" t="s">
         <v>354</v>
       </c>
-      <c r="C42" s="237"/>
-      <c r="D42" s="237"/>
-      <c r="E42" s="237"/>
-      <c r="F42" s="237"/>
-      <c r="G42" s="237"/>
-      <c r="H42" s="237"/>
+      <c r="C42" s="234"/>
+      <c r="D42" s="234"/>
+      <c r="E42" s="234"/>
+      <c r="F42" s="234"/>
+      <c r="G42" s="234"/>
+      <c r="H42" s="234"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14170,24 +14199,24 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="237"/>
-      <c r="C52" s="237"/>
-      <c r="D52" s="237"/>
-      <c r="E52" s="237"/>
-      <c r="F52" s="237"/>
-      <c r="G52" s="237"/>
-      <c r="H52" s="237"/>
+      <c r="B52" s="234"/>
+      <c r="C52" s="234"/>
+      <c r="D52" s="234"/>
+      <c r="E52" s="234"/>
+      <c r="F52" s="234"/>
+      <c r="G52" s="234"/>
+      <c r="H52" s="234"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="237" t="s">
+      <c r="B55" s="234" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="237"/>
-      <c r="D55" s="237"/>
-      <c r="E55" s="237"/>
-      <c r="F55" s="237"/>
-      <c r="G55" s="237"/>
-      <c r="H55" s="237"/>
+      <c r="C55" s="234"/>
+      <c r="D55" s="234"/>
+      <c r="E55" s="234"/>
+      <c r="F55" s="234"/>
+      <c r="G55" s="234"/>
+      <c r="H55" s="234"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14202,28 +14231,28 @@
       </c>
     </row>
     <row r="62" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="237"/>
-      <c r="C62" s="237"/>
-      <c r="D62" s="237"/>
-      <c r="E62" s="237"/>
-      <c r="F62" s="237"/>
-      <c r="G62" s="237"/>
-      <c r="H62" s="237"/>
+      <c r="B62" s="234"/>
+      <c r="C62" s="234"/>
+      <c r="D62" s="234"/>
+      <c r="E62" s="234"/>
+      <c r="F62" s="234"/>
+      <c r="G62" s="234"/>
+      <c r="H62" s="234"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B55:H55"/>
     <mergeCell ref="B62:H62"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14293,36 +14322,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="237" t="s">
+      <c r="S2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
-      <c r="AA2" s="237" t="s">
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
+      <c r="AA2" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="237"/>
-      <c r="AC2" s="237"/>
+      <c r="AB2" s="234"/>
+      <c r="AC2" s="234"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15715,35 +15744,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="P2" s="237" t="s">
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
+      <c r="P2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="237"/>
-      <c r="R2" s="237"/>
-      <c r="S2" s="237"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237" t="s">
+      <c r="Q2" s="234"/>
+      <c r="R2" s="234"/>
+      <c r="S2" s="234"/>
+      <c r="T2" s="234"/>
+      <c r="U2" s="234"/>
+      <c r="V2" s="234"/>
+      <c r="W2" s="234"/>
+      <c r="X2" s="234" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="237"/>
+      <c r="Y2" s="234"/>
+      <c r="Z2" s="234"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -17150,20 +17179,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
       <c r="G3" s="246"/>
       <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
       <c r="R3" s="248"/>
@@ -18556,12 +18585,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18569,6 +18592,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18606,20 +18635,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
       <c r="S2" s="248"/>
       <c r="T2" s="248"/>
       <c r="U2" s="248"/>
@@ -19082,24 +19111,24 @@
         <v>71</v>
       </c>
       <c r="C15" s="128">
-        <f>-Statement!M83</f>
-        <v>-8.4550522969174771E-2</v>
+        <f>Statement!M83</f>
+        <v>8.4550522969174771E-2</v>
       </c>
       <c r="D15" s="128">
-        <f>-Statement!N83</f>
+        <f>Statement!N83</f>
         <v>0</v>
       </c>
       <c r="E15" s="128">
-        <f>-Statement!O83</f>
+        <f>Statement!O83</f>
         <v>0</v>
       </c>
       <c r="F15" s="128">
-        <f>-Statement!P83</f>
+        <f>Statement!P83</f>
         <v>0</v>
       </c>
       <c r="G15" s="129">
-        <f>-Statement!Q83</f>
-        <v>-0.98330122029543998</v>
+        <f>Statement!Q83</f>
+        <v>0.98330122029543998</v>
       </c>
       <c r="H15" s="128">
         <f>Overview!$C$26</f>
@@ -19393,7 +19422,7 @@
       </c>
       <c r="C27" s="125">
         <f>C10*(1-C15)</f>
-        <v>21101.014974888265</v>
+        <v>17810.985025111735</v>
       </c>
       <c r="D27" s="125">
         <f t="shared" ref="D27:L27" si="6">D10*(1-D15)</f>
@@ -19409,7 +19438,7 @@
       </c>
       <c r="G27" s="130">
         <f t="shared" si="6"/>
-        <v>-4391.0289017341047</v>
+        <v>-36.971098265895883</v>
       </c>
       <c r="H27" s="125">
         <f t="shared" si="6"/>
@@ -19438,7 +19467,7 @@
       </c>
       <c r="C28" s="93">
         <f>C27+C20-C21+C22</f>
-        <v>8752.0149748882686</v>
+        <v>5461.985025111735</v>
       </c>
       <c r="D28" s="93">
         <f t="shared" ref="D28:L28" si="7">D27+D20-D21+D22</f>
@@ -19454,7 +19483,7 @@
       </c>
       <c r="G28" s="126">
         <f t="shared" si="7"/>
-        <v>-9078.0289017341056</v>
+        <v>-4723.9710982658962</v>
       </c>
       <c r="H28" s="93">
         <f t="shared" si="7"/>
@@ -19628,16 +19657,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19700,10 +19729,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="234" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="234"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19720,7 +19749,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19729,7 +19758,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>483215.2</v>
+        <v>620464.96199999994</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19747,7 +19776,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.7619999999999996E-2</v>
+        <v>4.9630000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19756,7 +19785,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2740999999999998</v>
+        <v>2.2724000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19765,7 +19794,7 @@
       </c>
       <c r="C11" s="134">
         <f>[1]Sheet1!$C$12</f>
-        <v>4.4999999999999998E-2</v>
+        <v>4.3999999999999997E-2</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19788,10 +19817,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="234" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="237"/>
+      <c r="C15" s="234"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19799,7 +19828,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.4682513720786551E-2</v>
+        <v>7.531572612599903E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19808,7 +19837,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9053174862792136</v>
+        <v>0.92468427387400098</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19826,7 +19855,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.14995449999999999</v>
+        <v>0.14961560000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19835,7 +19864,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.13994518540326395</v>
+        <v>0.14167916017003718</v>
       </c>
     </row>
   </sheetData>
@@ -19880,20 +19909,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
       <c r="G3" s="246"/>
       <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
       <c r="R3" s="248"/>
@@ -20000,7 +20029,7 @@
       </c>
       <c r="C7" s="111">
         <f>'FCF &amp; Other'!C28</f>
-        <v>8752.0149748882686</v>
+        <v>5461.985025111735</v>
       </c>
       <c r="D7" s="111">
         <f>'FCF &amp; Other'!D28</f>
@@ -20016,7 +20045,7 @@
       </c>
       <c r="G7" s="112">
         <f>'FCF &amp; Other'!G28</f>
-        <v>-9078.0289017341056</v>
+        <v>-4723.9710982658962</v>
       </c>
       <c r="H7" s="111">
         <f>'FCF &amp; Other'!H28</f>
@@ -20086,7 +20115,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-30707.755962473158</v>
+        <v>-30270.158645818847</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20140,23 +20169,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8116.8234101099024</v>
+        <v>-8104.4956323326605</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5750.7453093893491</v>
+        <v>-5733.290186850114</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4230.7878493503404</v>
+        <v>-4211.5400345128865</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4054.9292659967323</v>
+        <v>-4030.3509319045907</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1875.9051927323635</v>
+        <v>-1861.7028371175511</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20175,14 +20204,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-15952.481045020277</v>
+        <v>-15606.09796456752</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="237" t="s">
+      <c r="B13" s="234" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="237"/>
+      <c r="C13" s="234"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20198,14 +20227,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13994518540326395</v>
+        <v>0.14167916017003718</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="237" t="s">
+      <c r="B18" s="234" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="237"/>
+      <c r="C18" s="234"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20213,7 +20242,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-24029.191027578687</v>
+        <v>-23941.379622717803</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20222,7 +20251,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-15952.481045020277</v>
+        <v>-15606.09796456752</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20231,7 +20260,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-39981.672072598965</v>
+        <v>-39547.477587285321</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20258,7 +20287,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-52381.672072598965</v>
+        <v>-51947.477587285321</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20276,7 +20305,7 @@
       </c>
       <c r="C26" s="141">
         <f ca="1">C24/C25</f>
-        <v>-10.384946881958557</v>
+        <v>-10.298865501047842</v>
       </c>
     </row>
   </sheetData>
@@ -20319,20 +20348,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20494,7 +20523,7 @@
       </c>
       <c r="C8" s="91">
         <f>'FCF &amp; Other'!C28</f>
-        <v>8752.0149748882686</v>
+        <v>5461.985025111735</v>
       </c>
       <c r="D8" s="91">
         <f>'FCF &amp; Other'!D28</f>
@@ -20510,7 +20539,7 @@
       </c>
       <c r="G8" s="92">
         <f>'FCF &amp; Other'!G28</f>
-        <v>-9078.0289017341056</v>
+        <v>-4723.9710982658962</v>
       </c>
       <c r="H8" s="91">
         <f>'FCF &amp; Other'!H28</f>
@@ -20700,7 +20729,7 @@
 IF(D8=0,0,IF(D8&gt;0,1,-1)),
 (D8-C8)/ABS(C8)
 )</f>
-        <v>-2.5976892224385746</v>
+        <v>-3.5600582820554241</v>
       </c>
       <c r="E14" s="94">
         <f t="shared" ref="E14:L14" si="3">IF(D8=0,
@@ -20715,11 +20744,11 @@
       </c>
       <c r="G14" s="95">
         <f t="shared" si="3"/>
-        <v>0.6076910586977482</v>
+        <v>0.79585258866612385</v>
       </c>
       <c r="H14" s="94">
         <f t="shared" si="3"/>
-        <v>-1.9244801628226501E-2</v>
+        <v>-0.95867704832483724</v>
       </c>
       <c r="I14" s="94">
         <f t="shared" si="3"/>
@@ -21232,7 +21261,7 @@
       </c>
       <c r="C34" s="148">
         <f>C32/C8</f>
-        <v>24.365577596914751</v>
+        <v>39.042197849240281</v>
       </c>
       <c r="D34" s="148">
         <f t="shared" ref="D34:G34" si="13">D32/D8</f>
@@ -21248,7 +21277,7 @@
       </c>
       <c r="G34" s="149">
         <f t="shared" si="13"/>
-        <v>-18.136426065855499</v>
+        <v>-34.852668777003771</v>
       </c>
       <c r="H34" s="136"/>
       <c r="I34" s="136"/>
@@ -21264,10 +21293,10 @@
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="234" t="s">
         <v>200</v>
       </c>
-      <c r="C37" s="237"/>
+      <c r="C37" s="234"/>
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
@@ -21285,7 +21314,7 @@
       </c>
       <c r="C39" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13994518540326395</v>
+        <v>0.14167916017003718</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21311,7 +21340,7 @@
       </c>
       <c r="C42" s="24">
         <f ca="1">C41/(1+C39)^5-G30+G31</f>
-        <v>225267.94013107542</v>
+        <v>223557.47717461697</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
@@ -21338,7 +21367,7 @@
       </c>
       <c r="C45" s="24">
         <f ca="1">C42+C43-C44</f>
-        <v>212867.94013107545</v>
+        <v>211157.47717461697</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21356,14 +21385,14 @@
       </c>
       <c r="C47" s="141">
         <f ca="1">C45/C46</f>
-        <v>42.202208590617651</v>
+        <v>41.863100153571963</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="237" t="s">
+      <c r="B49" s="234" t="s">
         <v>205</v>
       </c>
-      <c r="C49" s="237"/>
+      <c r="C49" s="234"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B50" s="1" t="s">
@@ -21419,10 +21448,10 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="237" t="s">
+      <c r="B57" s="234" t="s">
         <v>322</v>
       </c>
-      <c r="C57" s="237"/>
+      <c r="C57" s="234"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B58" s="1" t="s">
@@ -21439,7 +21468,7 @@
       </c>
       <c r="C59" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13994518540326395</v>
+        <v>0.14167916017003718</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21465,7 +21494,7 @@
       </c>
       <c r="C62" s="63">
         <f ca="1">C61/(1+C59)^5-G30+G31</f>
-        <v>-76034.514969238458</v>
+        <v>-75463.836729686984</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21492,7 +21521,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C62+C63-C64</f>
-        <v>-88434.514969238458</v>
+        <v>-87863.836729686984</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21510,7 +21539,7 @@
       </c>
       <c r="C67" s="141">
         <f ca="1">C65/C66</f>
-        <v>-17.532615973282802</v>
+        <v>-17.419475957511299</v>
       </c>
     </row>
   </sheetData>
@@ -21562,10 +21591,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="234" t="s">
         <v>210</v>
       </c>
-      <c r="C4" s="237"/>
+      <c r="C4" s="234"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21574,7 +21603,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.384946881958557</v>
+        <v>-10.298865501047842</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21583,7 +21612,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C47</f>
-        <v>42.202208590617651</v>
+        <v>41.863100153571963</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21601,7 +21630,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C67</f>
-        <v>-17.532615973282802</v>
+        <v>-17.419475957511299</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21610,7 +21639,7 @@
       </c>
       <c r="C9" s="141">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>15.755776643767003</v>
+        <v>15.720804883676134</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21619,7 +21648,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21628,7 +21657,7 @@
       </c>
       <c r="C11" s="153">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.83553469056610641</v>
+        <v>-0.87219948798130131</v>
       </c>
     </row>
   </sheetData>
@@ -21684,20 +21713,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="237" t="s">
+      <c r="C2" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
       <c r="G2" s="246"/>
       <c r="H2" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22060,10 +22089,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="237" t="s">
+      <c r="B20" s="234" t="s">
         <v>405</v>
       </c>
-      <c r="C20" s="237"/>
+      <c r="C20" s="234"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22164,20 +22193,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="237" t="s">
+      <c r="C3" s="234" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
+      <c r="D3" s="234"/>
+      <c r="E3" s="234"/>
+      <c r="F3" s="234"/>
       <c r="G3" s="246"/>
       <c r="H3" s="247" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
+      <c r="I3" s="234"/>
+      <c r="J3" s="234"/>
+      <c r="K3" s="234"/>
+      <c r="L3" s="234"/>
       <c r="P3" s="248"/>
       <c r="Q3" s="248"/>
       <c r="R3" s="248"/>
@@ -22284,7 +22313,7 @@
       </c>
       <c r="C7" s="111">
         <f>'FCF &amp; Other'!C28</f>
-        <v>8752.0149748882686</v>
+        <v>5461.985025111735</v>
       </c>
       <c r="D7" s="111">
         <f>'FCF &amp; Other'!D28</f>
@@ -22300,27 +22329,27 @@
       </c>
       <c r="G7" s="112">
         <f>'FCF &amp; Other'!G28</f>
-        <v>-9078.0289017341056</v>
+        <v>-4723.9710982658962</v>
       </c>
       <c r="H7" s="125">
         <f>G7*(1+$C$17)</f>
-        <v>-14978.747687861274</v>
+        <v>-7794.5523121387287</v>
       </c>
       <c r="I7" s="125">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>-24714.9336849711</v>
+        <v>-12861.011315028902</v>
       </c>
       <c r="J7" s="125">
         <f t="shared" si="0"/>
-        <v>-40779.640580202315</v>
+        <v>-21220.668669797687</v>
       </c>
       <c r="K7" s="125">
         <f t="shared" si="0"/>
-        <v>-67286.40695733382</v>
+        <v>-35014.10330516618</v>
       </c>
       <c r="L7" s="125">
         <f t="shared" si="0"/>
-        <v>-111022.5714796008</v>
+        <v>-57773.270453524194</v>
       </c>
       <c r="N7" s="90"/>
       <c r="O7" s="16"/>
@@ -22352,7 +22381,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-944123.12197827699</v>
+        <v>-484296.04363020218</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22406,23 +22435,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-13139.884162555092</v>
+        <v>-6827.2703786393358</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-19019.167891433444</v>
+        <v>-9867.0419131388371</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-27529.066680310338</v>
+        <v>-14260.240288746543</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-39846.617718239992</v>
+        <v>-20609.464810522964</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-57675.509381477445</v>
+        <v>-29785.615892557966</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22441,7 +22470,7 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-490465.86881599115</v>
+        <v>-249683.90781094792</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22457,7 +22486,7 @@
       </c>
       <c r="C15" s="155">
         <f ca="1">Overview!C5</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22466,7 +22495,7 @@
       </c>
       <c r="C16" s="155">
         <f ca="1">C36</f>
-        <v>-130.86362304718625</v>
+        <v>-68.087537885518145</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22505,7 +22534,7 @@
       </c>
       <c r="C21" s="225">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.13994518540326395</v>
+        <v>0.14167916017003718</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22523,7 +22552,7 @@
       </c>
       <c r="C23" s="160">
         <f ca="1">C15*C22</f>
-        <v>483215.2</v>
+        <v>620464.96199999994</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22550,7 +22579,7 @@
       </c>
       <c r="C26" s="161">
         <f ca="1">C23+C25-C24</f>
-        <v>495615.19999999995</v>
+        <v>632864.96199999994</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22566,7 +22595,7 @@
       </c>
       <c r="C29" s="160">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-157210.2458340163</v>
+        <v>-81349.633283605654</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22575,7 +22604,7 @@
       </c>
       <c r="C30" s="160">
         <f ca="1">L11</f>
-        <v>-490465.86881599115</v>
+        <v>-249683.90781094792</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22584,7 +22613,7 @@
       </c>
       <c r="C31" s="163">
         <f ca="1">C29+C30</f>
-        <v>-647676.11465000745</v>
+        <v>-331033.54109455354</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22611,7 +22640,7 @@
       </c>
       <c r="C34" s="163">
         <f ca="1">C31+C32-C33</f>
-        <v>-660076.11465000745</v>
+        <v>-343433.54109455354</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.2">
@@ -22629,7 +22658,7 @@
       </c>
       <c r="C36" s="166">
         <f ca="1">C34/C35</f>
-        <v>-130.86362304718625</v>
+        <v>-68.087537885518145</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.2">
@@ -22694,7 +22723,7 @@
       </c>
       <c r="C41" s="111">
         <f>C7</f>
-        <v>8752.0149748882686</v>
+        <v>5461.985025111735</v>
       </c>
       <c r="D41" s="111">
         <f t="shared" si="2"/>
@@ -22710,27 +22739,27 @@
       </c>
       <c r="G41" s="112">
         <f t="shared" si="2"/>
-        <v>-9078.0289017341056</v>
+        <v>-4723.9710982658962</v>
       </c>
       <c r="H41" s="142">
         <f t="shared" si="2"/>
-        <v>-14978.747687861274</v>
+        <v>-7794.5523121387287</v>
       </c>
       <c r="I41" s="142">
         <f t="shared" si="2"/>
-        <v>-24714.9336849711</v>
+        <v>-12861.011315028902</v>
       </c>
       <c r="J41" s="142">
         <f t="shared" si="2"/>
-        <v>-40779.640580202315</v>
+        <v>-21220.668669797687</v>
       </c>
       <c r="K41" s="142">
         <f t="shared" si="2"/>
-        <v>-67286.40695733382</v>
+        <v>-35014.10330516618</v>
       </c>
       <c r="L41" s="142">
         <f t="shared" si="2"/>
-        <v>-111022.5714796008</v>
+        <v>-57773.270453524194</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.2">
@@ -22759,23 +22788,23 @@
       </c>
       <c r="H42" s="142">
         <f>H41/H43</f>
-        <v>-13617.043352601157</v>
+        <v>-7085.9566473988434</v>
       </c>
       <c r="I42" s="142">
         <f t="shared" ref="I42:L42" si="3">I41/I43</f>
-        <v>-22468.121531791909</v>
+        <v>-11691.828468208092</v>
       </c>
       <c r="J42" s="142">
         <f t="shared" si="3"/>
-        <v>-37072.400527456644</v>
+        <v>-19291.516972543352</v>
       </c>
       <c r="K42" s="142">
         <f t="shared" si="3"/>
-        <v>-61169.460870303468</v>
+        <v>-31831.003004696526</v>
       </c>
       <c r="L42" s="142">
         <f t="shared" si="3"/>
-        <v>-100929.61043600072</v>
+        <v>-52521.154957749262</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.2">
@@ -22784,7 +22813,7 @@
       </c>
       <c r="C43" s="94">
         <f>C41/C42</f>
-        <v>0.4498362959954908</v>
+        <v>0.28073525005714101</v>
       </c>
       <c r="D43" s="94">
         <f t="shared" ref="D43:G43" si="4">D41/D42</f>
@@ -22800,7 +22829,7 @@
       </c>
       <c r="G43" s="95">
         <f t="shared" si="4"/>
-        <v>4.1002840567904721</v>
+        <v>2.133681616199592</v>
       </c>
       <c r="H43" s="167">
         <v>1.1000000000000001</v>
@@ -22844,23 +22873,23 @@
       </c>
       <c r="H44" s="142">
         <f>H41/H45</f>
-        <v>-1497874.7687861274</v>
+        <v>-779455.2312138729</v>
       </c>
       <c r="I44" s="142">
         <f t="shared" ref="I44:L44" si="5">I41/I45</f>
-        <v>-1235746.684248555</v>
+        <v>-643050.56575144501</v>
       </c>
       <c r="J44" s="142">
         <f t="shared" si="5"/>
-        <v>-970943.82333815028</v>
+        <v>-505254.01594756398</v>
       </c>
       <c r="K44" s="142">
         <f t="shared" si="5"/>
-        <v>-961234.38510476879</v>
+        <v>-500201.47578808822</v>
       </c>
       <c r="L44" s="142">
         <f t="shared" si="5"/>
-        <v>-740150.47653067205</v>
+        <v>-385155.13635682798</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.2">
@@ -22869,7 +22898,7 @@
       </c>
       <c r="C45" s="94">
         <f>C41/C44</f>
-        <v>0.11075135370125871</v>
+        <v>6.9118053061243856E-2</v>
       </c>
       <c r="D45" s="94">
         <f t="shared" ref="D45:G45" si="6">D41/D44</f>
@@ -22885,7 +22914,7 @@
       </c>
       <c r="G45" s="95">
         <f t="shared" si="6"/>
-        <v>-0.17175995500225352</v>
+        <v>-8.9379431598317904E-2</v>
       </c>
       <c r="H45" s="167">
         <v>0.01</v>
@@ -22910,7 +22939,7 @@
       <c r="C46" s="136"/>
       <c r="D46" s="94">
         <f>D41/C41-1</f>
-        <v>-2.597689222438575</v>
+        <v>-3.5600582820554241</v>
       </c>
       <c r="E46" s="94">
         <f t="shared" ref="E46:L47" si="7">E41/D41-1</f>
@@ -22922,7 +22951,7 @@
       </c>
       <c r="G46" s="95">
         <f t="shared" si="7"/>
-        <v>-0.6076910586977482</v>
+        <v>-0.79585258866612374</v>
       </c>
       <c r="H46" s="168">
         <f t="shared" si="7"/>
@@ -22938,7 +22967,7 @@
       </c>
       <c r="K46" s="168">
         <f t="shared" si="7"/>
-        <v>0.65000000000000013</v>
+        <v>0.64999999999999969</v>
       </c>
       <c r="L46" s="168">
         <f t="shared" si="7"/>
@@ -22968,19 +22997,19 @@
       </c>
       <c r="H47" s="168">
         <f t="shared" si="7"/>
-        <v>5.1504260851857078</v>
+        <v>2.2005224242993875</v>
       </c>
       <c r="I47" s="168">
         <f t="shared" si="7"/>
-        <v>0.64999999999999991</v>
+        <v>0.65000000000000013</v>
       </c>
       <c r="J47" s="168">
         <f t="shared" si="7"/>
-        <v>0.64999999999999969</v>
+        <v>0.64999999999999991</v>
       </c>
       <c r="K47" s="168">
         <f t="shared" si="7"/>
-        <v>0.65000000000000013</v>
+        <v>0.64999999999999969</v>
       </c>
       <c r="L47" s="168">
         <f t="shared" si="7"/>
@@ -23010,7 +23039,7 @@
       </c>
       <c r="H48" s="168">
         <f t="shared" si="8"/>
-        <v>-29.340392575371833</v>
+        <v>-15.747606213722454</v>
       </c>
       <c r="I48" s="168">
         <f t="shared" si="8"/>
@@ -23018,11 +23047,11 @@
       </c>
       <c r="J48" s="168">
         <f t="shared" si="8"/>
-        <v>-0.2142857142857143</v>
+        <v>-0.21428571428571419</v>
       </c>
       <c r="K48" s="168">
         <f t="shared" si="8"/>
-        <v>-1.0000000000000009E-2</v>
+        <v>-1.0000000000000231E-2</v>
       </c>
       <c r="L48" s="168">
         <f t="shared" si="8"/>
@@ -23059,7 +23088,7 @@
       </c>
       <c r="I49" s="168">
         <f t="shared" si="9"/>
-        <v>1.8181818181818181E-2</v>
+        <v>1.8181818181818184E-2</v>
       </c>
       <c r="J49" s="168">
         <f t="shared" si="9"/>
@@ -23067,26 +23096,26 @@
       </c>
       <c r="K49" s="168">
         <f t="shared" si="9"/>
-        <v>6.363636363636363E-2</v>
+        <v>6.3636363636363644E-2</v>
       </c>
       <c r="L49" s="168">
         <f t="shared" si="9"/>
-        <v>0.13636363636363633</v>
+        <v>0.13636363636363635</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C39:L39"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C39:L39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29745,7 +29774,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29816,7 +29845,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31122,7 +31151,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-45.402843601895725</v>
+        <v>-58.298815165876768</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31159,7 +31188,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>8.2127603801374676</v>
+        <v>10.545467231115865</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31220,7 +31249,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.5198099198099193</v>
+        <v>7.0876260766260764</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31281,7 +31310,7 @@
       </c>
       <c r="AC153" s="142">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>483215.2</v>
+        <v>620464.96199999994</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31342,7 +31371,7 @@
       </c>
       <c r="AC154" s="142">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>511216.19999999995</v>
+        <v>648465.96199999994</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31379,7 +31408,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="182">
         <f ca="1">AC154/AC5</f>
-        <v>8.9636730256697987</v>
+        <v>11.370212547341842</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31416,7 +31445,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="182">
         <f ca="1">AC154/AC12</f>
-        <v>-6639.1714285714279</v>
+        <v>-8421.6358701298686</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31551,7 +31580,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-42.971560693641621</v>
+        <v>-55.176964161849703</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31588,7 +31617,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-90.753807917628251</v>
+        <v>-115.11911272856381</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31625,7 +31654,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-2.3271205044874416E-2</v>
+        <v>-1.8123505256046998E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31662,7 +31691,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-2.202505219206681E-2</v>
+        <v>-1.7153007263607582E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31773,7 +31802,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="153">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.3090846479994834E-3</v>
+        <v>2.57709959132229E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32276,7 +32305,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="153">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-2.5661444424761471E-2</v>
+        <v>-1.9985012465538708E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34022,15 +34051,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="237" t="s">
+      <c r="B4" s="234" t="s">
         <v>233</v>
       </c>
-      <c r="C4" s="237"/>
-      <c r="E4" s="237" t="s">
+      <c r="C4" s="234"/>
+      <c r="E4" s="234" t="s">
         <v>240</v>
       </c>
-      <c r="F4" s="237"/>
-      <c r="G4" s="237"/>
+      <c r="F4" s="234"/>
+      <c r="G4" s="234"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34038,7 +34067,7 @@
       </c>
       <c r="C5" s="171">
         <f ca="1">Overview!C5</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -34054,7 +34083,7 @@
       </c>
       <c r="C6" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>483215.2</v>
+        <v>620464.96199999994</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34074,7 +34103,7 @@
       </c>
       <c r="C7" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>511216.19999999995</v>
+        <v>648465.96199999994</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -34094,7 +34123,7 @@
       </c>
       <c r="C8" s="173">
         <f ca="1">Statement!AC150</f>
-        <v>-45.402843601895725</v>
+        <v>-58.298815165876768</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>243</v>
@@ -34114,7 +34143,7 @@
       </c>
       <c r="C9" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>8.2127603801374676</v>
+        <v>10.545467231115865</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>244</v>
@@ -34134,7 +34163,7 @@
       </c>
       <c r="C10" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>5.5198099198099193</v>
+        <v>7.0876260766260764</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34154,7 +34183,7 @@
       </c>
       <c r="C11" s="173">
         <f ca="1">Statement!AC155</f>
-        <v>8.9636730256697987</v>
+        <v>11.370212547341842</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34163,18 +34192,18 @@
       </c>
       <c r="C12" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>-6639.1714285714279</v>
+        <v>-8421.6358701298686</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="237" t="s">
+      <c r="B15" s="234" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="237"/>
-      <c r="E15" s="237" t="s">
+      <c r="C15" s="234"/>
+      <c r="E15" s="234" t="s">
         <v>246</v>
       </c>
-      <c r="F15" s="237"/>
+      <c r="F15" s="234"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34225,14 +34254,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="237" t="s">
+      <c r="B21" s="234" t="s">
         <v>245</v>
       </c>
-      <c r="C21" s="237"/>
-      <c r="E21" s="237" t="s">
+      <c r="C21" s="234"/>
+      <c r="E21" s="234" t="s">
         <v>249</v>
       </c>
-      <c r="F21" s="237"/>
+      <c r="F21" s="234"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34301,14 +34330,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="237" t="s">
+      <c r="B29" s="234" t="s">
         <v>250</v>
       </c>
-      <c r="C29" s="237"/>
-      <c r="E29" s="237" t="s">
+      <c r="C29" s="234"/>
+      <c r="E29" s="234" t="s">
         <v>256</v>
       </c>
-      <c r="F29" s="237"/>
+      <c r="F29" s="234"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34384,14 +34413,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="237" t="s">
+      <c r="B37" s="234" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="237"/>
-      <c r="E37" s="237" t="s">
+      <c r="C37" s="234"/>
+      <c r="E37" s="234" t="s">
         <v>271</v>
       </c>
-      <c r="F37" s="237"/>
+      <c r="F37" s="234"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34399,7 +34428,7 @@
       </c>
       <c r="C38" s="174">
         <f ca="1">Statement!AC162</f>
-        <v>-2.202505219206681E-2</v>
+        <v>-1.7153007263607582E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>270</v>
@@ -34415,7 +34444,7 @@
       </c>
       <c r="C39" s="214">
         <f ca="1">Statement!AC161</f>
-        <v>-2.3271205044874416E-2</v>
+        <v>-1.8123505256046998E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>272</v>
@@ -34456,18 +34485,18 @@
       </c>
       <c r="C42" s="174">
         <f ca="1">Statement!AC165</f>
-        <v>3.3090846479994834E-3</v>
+        <v>2.57709959132229E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="237" t="s">
+      <c r="B45" s="234" t="s">
         <v>279</v>
       </c>
-      <c r="C45" s="237"/>
-      <c r="E45" s="237" t="s">
+      <c r="C45" s="234"/>
+      <c r="E45" s="234" t="s">
         <v>285</v>
       </c>
-      <c r="F45" s="237"/>
+      <c r="F45" s="234"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34500,18 +34529,18 @@
       </c>
       <c r="F48" s="174">
         <f ca="1">Statement!AC176</f>
-        <v>-2.5661444424761471E-2</v>
+        <v>-1.9985012465538708E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="237" t="s">
+      <c r="B51" s="234" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="237"/>
-      <c r="E51" s="237" t="s">
+      <c r="C51" s="234"/>
+      <c r="E51" s="234" t="s">
         <v>303</v>
       </c>
-      <c r="F51" s="237"/>
+      <c r="F51" s="234"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34679,7 +34708,7 @@
       </c>
       <c r="I6" s="171">
         <f ca="1">Statement!AC116</f>
-        <v>95.8</v>
+        <v>123.01049999999999</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34708,7 +34737,7 @@
       </c>
       <c r="I7" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>483215.2</v>
+        <v>620464.96199999994</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34737,7 +34766,7 @@
       </c>
       <c r="I8" s="172">
         <f ca="1">Statement!AC154</f>
-        <v>511216.19999999995</v>
+        <v>648465.96199999994</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34766,7 +34795,7 @@
       </c>
       <c r="I9" s="173">
         <f ca="1">Statement!AC150</f>
-        <v>-45.402843601895725</v>
+        <v>-58.298815165876768</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34795,7 +34824,7 @@
       </c>
       <c r="I10" s="173">
         <f ca="1">Statement!AC151</f>
-        <v>8.2127603801374676</v>
+        <v>10.545467231115865</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34824,7 +34853,7 @@
       </c>
       <c r="I11" s="173">
         <f ca="1">Statement!AC152</f>
-        <v>5.5198099198099193</v>
+        <v>7.0876260766260764</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34853,7 +34882,7 @@
       </c>
       <c r="I12" s="173">
         <f ca="1">Statement!AC155</f>
-        <v>8.9636730256697987</v>
+        <v>11.370212547341842</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34882,7 +34911,7 @@
       </c>
       <c r="I13" s="173">
         <f ca="1">Statement!AC156</f>
-        <v>-6639.1714285714279</v>
+        <v>-8421.6358701298686</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35655,7 +35684,7 @@
       </c>
       <c r="I51" s="174">
         <f ca="1">Statement!AC162</f>
-        <v>-2.202505219206681E-2</v>
+        <v>-1.7153007263607582E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35684,7 +35713,7 @@
       </c>
       <c r="I52" s="174">
         <f ca="1">Statement!AC161</f>
-        <v>-2.3271205044874416E-2</v>
+        <v>-1.8123505256046998E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35771,7 +35800,7 @@
       </c>
       <c r="I55" s="174">
         <f ca="1">Statement!AC165</f>
-        <v>3.3090846479994834E-3</v>
+        <v>2.57709959132229E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36007,7 +36036,7 @@
       </c>
       <c r="I68" s="195">
         <f ca="1">Statement!AC176</f>
-        <v>-2.5661444424761471E-2</v>
+        <v>-1.9985012465538708E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36545,14 +36574,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="238" t="s">
         <v>313</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="F3" s="242" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>314</v>
       </c>
-      <c r="G3" s="241"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36619,19 +36648,19 @@
       <c r="B7" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C7" s="238">
+      <c r="C7" s="241">
         <f>Statement!AA89</f>
         <v>0.18789128673491934</v>
       </c>
-      <c r="D7" s="239"/>
-      <c r="F7" s="238">
+      <c r="D7" s="242"/>
+      <c r="F7" s="241">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.25421883505715842</v>
       </c>
-      <c r="G7" s="239"/>
+      <c r="G7" s="242"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="206" t="s">
@@ -36658,19 +36687,19 @@
       <c r="B9" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C9" s="238">
+      <c r="C9" s="241">
         <f>Statement!AA90</f>
         <v>0.16877278250303768</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="F9" s="238">
+      <c r="D9" s="242"/>
+      <c r="F9" s="241">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>3.2413867124610925E-2</v>
       </c>
-      <c r="G9" s="239"/>
+      <c r="G9" s="242"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="206" t="s">
@@ -36697,19 +36726,19 @@
       <c r="B11" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="241">
         <f>Statement!AA91</f>
         <v>0.21731812231157657</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="F11" s="238">
+      <c r="D11" s="242"/>
+      <c r="F11" s="241">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.83766233766233766</v>
       </c>
-      <c r="G11" s="239"/>
+      <c r="G11" s="242"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="206" t="s">
@@ -36736,19 +36765,19 @@
       <c r="B13" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="238">
+      <c r="C13" s="241">
         <f>Statement!AA95</f>
         <v>-0.44441824826122833</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="F13" s="238">
+      <c r="D13" s="242"/>
+      <c r="F13" s="241">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-0.29845192021434952</v>
       </c>
-      <c r="G13" s="239"/>
+      <c r="G13" s="242"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="206" t="s">
@@ -36775,19 +36804,19 @@
       <c r="B15" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C15" s="238">
+      <c r="C15" s="241">
         <f>Statement!AA96</f>
         <v>1.572704081632653</v>
       </c>
-      <c r="D15" s="239"/>
-      <c r="F15" s="238">
+      <c r="D15" s="242"/>
+      <c r="F15" s="241">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5654911838790933</v>
       </c>
-      <c r="G15" s="239"/>
+      <c r="G15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="206" t="s">
@@ -36814,19 +36843,19 @@
       <c r="B17" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C17" s="238">
+      <c r="C17" s="241">
         <f>Statement!AA98</f>
         <v>-1.9594957081545064</v>
       </c>
-      <c r="D17" s="239"/>
-      <c r="F17" s="238">
+      <c r="D17" s="242"/>
+      <c r="F17" s="241">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-2.781014393420151</v>
       </c>
-      <c r="G17" s="239"/>
+      <c r="G17" s="242"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="206" t="s">
@@ -36853,22 +36882,22 @@
       <c r="B19" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C19" s="238">
+      <c r="C19" s="241">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.1314184536690932E-3</v>
       </c>
-      <c r="D19" s="239"/>
-      <c r="F19" s="238">
+      <c r="D19" s="242"/>
+      <c r="F19" s="241">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.16823071641107806</v>
       </c>
-      <c r="G19" s="239"/>
+      <c r="G19" s="242"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="206" t="s">
@@ -36895,22 +36924,22 @@
       <c r="B21" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C21" s="238">
+      <c r="C21" s="241">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-1.9589041095890414</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="F21" s="238">
+      <c r="D21" s="242"/>
+      <c r="F21" s="241">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.2238805970149254</v>
       </c>
-      <c r="G21" s="239"/>
+      <c r="G21" s="242"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36958,22 +36987,22 @@
       <c r="B25" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C25" s="238">
+      <c r="C25" s="241">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14882878219231266</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="F25" s="238">
+      <c r="D25" s="242"/>
+      <c r="F25" s="241">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.12781095159446068</v>
       </c>
-      <c r="G25" s="239"/>
+      <c r="G25" s="242"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37000,22 +37029,22 @@
       <c r="B27" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C27" s="238">
+      <c r="C27" s="241">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.23950910530482977</v>
       </c>
-      <c r="D27" s="239"/>
-      <c r="F27" s="238">
+      <c r="D27" s="242"/>
+      <c r="F27" s="241">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.58974358974358976</v>
       </c>
-      <c r="G27" s="239"/>
+      <c r="G27" s="242"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37042,22 +37071,22 @@
       <c r="B29" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C29" s="238">
+      <c r="C29" s="241">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18467798732295171</v>
       </c>
-      <c r="D29" s="239"/>
-      <c r="F29" s="238">
+      <c r="D29" s="242"/>
+      <c r="F29" s="241">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28187976291278577</v>
       </c>
-      <c r="G29" s="239"/>
+      <c r="G29" s="242"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37084,22 +37113,22 @@
       <c r="B31" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C31" s="238">
+      <c r="C31" s="241">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>6.3456926766279287E-2</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="F31" s="238">
+      <c r="D31" s="242"/>
+      <c r="F31" s="241">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.30518451437627347</v>
       </c>
-      <c r="G31" s="239"/>
+      <c r="G31" s="242"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -37126,37 +37155,25 @@
       <c r="B33" s="205" t="s">
         <v>315</v>
       </c>
-      <c r="C33" s="238">
+      <c r="C33" s="241">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.11624203821656051</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="F33" s="238">
+      <c r="D33" s="242"/>
+      <c r="F33" s="241">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33428300094966762</v>
       </c>
-      <c r="G33" s="239"/>
+      <c r="G33" s="242"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -37173,6 +37190,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0729C0D6-CBA2-1A43-ADDE-1A21A04DD434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3DAF6D-9276-F34B-8401-C9416840322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -132,28 +132,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -163,21 +142,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2333,10 +2303,42 @@
     <xf numFmtId="39" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2348,36 +2350,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2387,8 +2359,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12796,7 +12766,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12816,8 +12786,10 @@
     <v>142.35</v>
     <v>31.21</v>
     <v>2.2450000000000001</v>
-    <v>-2.82</v>
-    <v>-2.2136999999999997E-2</v>
+    <v>-4.3899999999999997</v>
+    <v>-3.4460999999999999E-2</v>
+    <v>1.2800000000000001E-2</v>
+    <v>1.0410000000000001E-4</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12828,46 +12800,32 @@
     <v>126.93</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.729591770316</v>
+    <v>46290.840666435157</v>
     <v>0</v>
     <v>122.84</v>
-    <v>658361045330</v>
+    <v>650063487000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
     <v>126.8</v>
     <v>0</v>
     <v>127.39</v>
-    <v>124.57</v>
+    <v>123</v>
+    <v>123.0128</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>59063150</v>
+    <v>96039166</v>
     <v>101957193</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12886,7 +12844,7 @@
     <v>US</v>
     <v>51.81</v>
     <v>Index</v>
-    <v>6</v>
+    <v>3</v>
     <v>50.87</v>
     <v>10 Y TSY YLD NDX</v>
     <v>51.21</v>
@@ -12896,13 +12854,13 @@
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12924,6 +12882,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12944,6 +12904,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12953,11 +12914,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -12993,7 +12949,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13004,13 +12960,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13104,13 +13063,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13182,6 +13147,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13189,6 +13157,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13676,18 +13647,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>320</v>
       </c>
-      <c r="I2" s="236"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="180" t="s">
@@ -13702,7 +13673,7 @@
       </c>
       <c r="F3" s="182">
         <f ca="1">Statement!AC153</f>
-        <v>628331.07999999996</v>
+        <v>620412</v>
       </c>
       <c r="H3" s="180" t="str">
         <f>'AVG target price'!B5</f>
@@ -13710,7 +13681,7 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.160073722659385</v>
+        <v>-10.16454346822564</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13726,7 +13697,7 @@
       </c>
       <c r="F4" s="183">
         <f ca="1">Statement!AC154</f>
-        <v>656332.07999999996</v>
+        <v>648413</v>
       </c>
       <c r="H4" s="180" t="str">
         <f>'AVG target price'!B6</f>
@@ -13734,7 +13705,7 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.95038368034578</v>
+        <v>37.098113117913257</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13743,7 +13714,7 @@
       </c>
       <c r="C5" s="203" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
       <c r="E5" s="180" t="s">
         <v>238</v>
@@ -13765,16 +13736,16 @@
       <c r="B6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="203" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="203" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>123.0128</v>
       </c>
       <c r="E6" s="180" t="s">
         <v>232</v>
       </c>
       <c r="F6" s="185">
         <f ca="1">Statement!AC150</f>
-        <v>-59.037914691943115</v>
+        <v>-58.293838862559234</v>
       </c>
       <c r="H6" s="180" t="str">
         <f>'AVG target price'!B8</f>
@@ -13782,7 +13753,7 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.58603546568752</v>
+        <v>-21.462668364326252</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13791,14 +13762,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.82</v>
+        <v>-4.3899999999999997</v>
       </c>
       <c r="E7" s="181" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="186">
         <f ca="1">Statement!AC151</f>
-        <v>10.679160339809229</v>
+        <v>10.544567085145182</v>
       </c>
       <c r="H7" s="179" t="str">
         <f>'AVG target price'!B9</f>
@@ -13806,23 +13777,23 @@
       </c>
       <c r="I7" s="207">
         <f ca="1">'AVG target price'!C9</f>
-        <v>13.48568383292265</v>
+        <v>13.552340531263269</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>1.2800000000000001E-2</v>
       </c>
       <c r="E8" s="180" t="s">
         <v>260</v>
       </c>
       <c r="F8" s="187">
         <f ca="1">Statement!AC161</f>
-        <v>-1.7896615905105315E-2</v>
+        <v>-1.8125052384544465E-2</v>
       </c>
       <c r="H8" s="179" t="str">
         <f>'AVG target price'!B11</f>
@@ -13830,7 +13801,7 @@
       </c>
       <c r="I8" s="208">
         <f ca="1">'AVG target price'!C11</f>
-        <v>-0.89174212223711447</v>
+        <v>-0.88981836966452632</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13839,23 +13810,23 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.2136999999999997E-2</v>
+        <v>-3.4460999999999999E-2</v>
       </c>
       <c r="E9" s="180" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="187">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6938267640683957E-2</v>
+        <v>-1.7154471544715451E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="72" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>1.0410000000000001E-4</v>
       </c>
       <c r="E10" s="180" t="s">
         <v>288</v>
@@ -13942,7 +13913,7 @@
       </c>
       <c r="F15" s="187">
         <f ca="1">Statement!AC176</f>
-        <v>-1.9734818783753307E-2</v>
+        <v>-1.9986718503188203E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13955,10 +13926,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="235" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="179" t="s">
         <v>291</v>
       </c>
@@ -14031,14 +14002,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="235" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>373</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="179" t="s">
@@ -14047,7 +14018,7 @@
       <c r="C26" s="165">
         <v>0.21</v>
       </c>
-      <c r="E26" s="180" t="e" vm="5">
+      <c r="E26" s="180" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="218" cm="1">
@@ -14087,15 +14058,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="231" t="s">
+      <c r="B33" s="232" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="231"/>
-      <c r="D33" s="231"/>
-      <c r="E33" s="231"/>
-      <c r="F33" s="231"/>
-      <c r="G33" s="231"/>
-      <c r="H33" s="231"/>
+      <c r="C33" s="232"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14114,24 +14085,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="231"/>
-      <c r="C39" s="231"/>
-      <c r="D39" s="231"/>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="231"/>
-      <c r="H39" s="231"/>
+      <c r="B39" s="232"/>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="232"/>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="231" t="s">
+      <c r="B42" s="232" t="s">
         <v>346</v>
       </c>
-      <c r="C42" s="231"/>
-      <c r="D42" s="231"/>
-      <c r="E42" s="231"/>
-      <c r="F42" s="231"/>
-      <c r="G42" s="231"/>
-      <c r="H42" s="231"/>
+      <c r="C42" s="232"/>
+      <c r="D42" s="232"/>
+      <c r="E42" s="232"/>
+      <c r="F42" s="232"/>
+      <c r="G42" s="232"/>
+      <c r="H42" s="232"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14182,24 +14153,24 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="231"/>
-      <c r="C52" s="231"/>
-      <c r="D52" s="231"/>
-      <c r="E52" s="231"/>
-      <c r="F52" s="231"/>
-      <c r="G52" s="231"/>
-      <c r="H52" s="231"/>
+      <c r="B52" s="232"/>
+      <c r="C52" s="232"/>
+      <c r="D52" s="232"/>
+      <c r="E52" s="232"/>
+      <c r="F52" s="232"/>
+      <c r="G52" s="232"/>
+      <c r="H52" s="232"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="231" t="s">
+      <c r="B55" s="232" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="231"/>
-      <c r="D55" s="231"/>
-      <c r="E55" s="231"/>
-      <c r="F55" s="231"/>
-      <c r="G55" s="231"/>
-      <c r="H55" s="231"/>
+      <c r="C55" s="232"/>
+      <c r="D55" s="232"/>
+      <c r="E55" s="232"/>
+      <c r="F55" s="232"/>
+      <c r="G55" s="232"/>
+      <c r="H55" s="232"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14214,28 +14185,28 @@
       </c>
     </row>
     <row r="62" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="231"/>
-      <c r="C62" s="231"/>
-      <c r="D62" s="231"/>
-      <c r="E62" s="231"/>
-      <c r="F62" s="231"/>
-      <c r="G62" s="231"/>
-      <c r="H62" s="231"/>
+      <c r="B62" s="232"/>
+      <c r="C62" s="232"/>
+      <c r="D62" s="232"/>
+      <c r="E62" s="232"/>
+      <c r="F62" s="232"/>
+      <c r="G62" s="232"/>
+      <c r="H62" s="232"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B55:H55"/>
     <mergeCell ref="B62:H62"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B42:H42"/>
     <mergeCell ref="B52:H52"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E25:F25"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14305,36 +14276,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="233" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="231" t="s">
+      <c r="S2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231"/>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="231"/>
-      <c r="AA2" s="231" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="231"/>
-      <c r="AC2" s="231"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14345,32 +14316,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="230" t="s">
+      <c r="C4" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="243" t="s">
+      <c r="S4" s="242" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
-      <c r="AA4" s="244"/>
-      <c r="AB4" s="244"/>
-      <c r="AC4" s="244"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
+      <c r="AA4" s="243"/>
+      <c r="AB4" s="243"/>
+      <c r="AC4" s="243"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15064,33 +15035,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="230" t="s">
+      <c r="C13" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="230"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="230"/>
-      <c r="G13" s="230"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="230"/>
-      <c r="J13" s="230"/>
-      <c r="K13" s="230"/>
-      <c r="L13" s="230"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="243" t="s">
+      <c r="S13" s="242" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="244"/>
-      <c r="U13" s="244"/>
-      <c r="V13" s="244"/>
-      <c r="W13" s="244"/>
-      <c r="X13" s="244"/>
-      <c r="Y13" s="244"/>
-      <c r="Z13" s="244"/>
-      <c r="AA13" s="244"/>
-      <c r="AB13" s="244"/>
-      <c r="AC13" s="244"/>
+      <c r="T13" s="243"/>
+      <c r="U13" s="243"/>
+      <c r="V13" s="243"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="243"/>
+      <c r="Y13" s="243"/>
+      <c r="Z13" s="243"/>
+      <c r="AA13" s="243"/>
+      <c r="AB13" s="243"/>
+      <c r="AC13" s="243"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15727,35 +15698,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="233" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
-      <c r="P2" s="231" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="231"/>
-      <c r="R2" s="231"/>
-      <c r="S2" s="231"/>
-      <c r="T2" s="231"/>
-      <c r="U2" s="231"/>
-      <c r="V2" s="231"/>
-      <c r="W2" s="231"/>
-      <c r="X2" s="231" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="231"/>
-      <c r="Z2" s="231"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15764,31 +15735,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="230" t="s">
+      <c r="C4" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
-      <c r="P4" s="244" t="s">
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="P4" s="243" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="244"/>
-      <c r="R4" s="244"/>
-      <c r="S4" s="244"/>
-      <c r="T4" s="244"/>
-      <c r="U4" s="244"/>
-      <c r="V4" s="244"/>
-      <c r="W4" s="244"/>
-      <c r="X4" s="244"/>
-      <c r="Y4" s="244"/>
-      <c r="Z4" s="244"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15983,32 +15954,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="230" t="s">
+      <c r="C9" s="241" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="230"/>
-      <c r="E9" s="230"/>
-      <c r="F9" s="230"/>
-      <c r="G9" s="230"/>
-      <c r="H9" s="230"/>
-      <c r="I9" s="230"/>
-      <c r="J9" s="230"/>
-      <c r="K9" s="230"/>
-      <c r="L9" s="230"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="244" t="s">
+      <c r="P9" s="243" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="244"/>
-      <c r="R9" s="244"/>
-      <c r="S9" s="244"/>
-      <c r="T9" s="244"/>
-      <c r="U9" s="244"/>
-      <c r="V9" s="244"/>
-      <c r="W9" s="244"/>
-      <c r="X9" s="244"/>
-      <c r="Y9" s="244"/>
-      <c r="Z9" s="244"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
+      <c r="U9" s="243"/>
+      <c r="V9" s="243"/>
+      <c r="W9" s="243"/>
+      <c r="X9" s="243"/>
+      <c r="Y9" s="243"/>
+      <c r="Z9" s="243"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16578,31 +16549,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="230" t="s">
+      <c r="C18" s="241" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="230"/>
-      <c r="E18" s="230"/>
-      <c r="F18" s="230"/>
-      <c r="G18" s="230"/>
-      <c r="H18" s="230"/>
-      <c r="I18" s="230"/>
-      <c r="J18" s="230"/>
-      <c r="K18" s="230"/>
-      <c r="L18" s="230"/>
-      <c r="P18" s="244" t="s">
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
+      <c r="P18" s="243" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="244"/>
-      <c r="R18" s="244"/>
-      <c r="S18" s="244"/>
-      <c r="T18" s="244"/>
-      <c r="U18" s="244"/>
-      <c r="V18" s="244"/>
-      <c r="W18" s="244"/>
-      <c r="X18" s="244"/>
-      <c r="Y18" s="244"/>
-      <c r="Z18" s="244"/>
+      <c r="Q18" s="243"/>
+      <c r="R18" s="243"/>
+      <c r="S18" s="243"/>
+      <c r="T18" s="243"/>
+      <c r="U18" s="243"/>
+      <c r="V18" s="243"/>
+      <c r="W18" s="243"/>
+      <c r="X18" s="243"/>
+      <c r="Y18" s="243"/>
+      <c r="Z18" s="243"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17162,60 +17133,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="231" t="s">
+      <c r="C3" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="232"/>
-      <c r="H3" s="233" t="s">
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="P3" s="234"/>
-      <c r="Q3" s="234"/>
-      <c r="R3" s="234"/>
-      <c r="S3" s="234"/>
-      <c r="T3" s="234"/>
-      <c r="U3" s="234"/>
-      <c r="V3" s="234"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="234"/>
-      <c r="Y3" s="234"/>
-      <c r="Z3" s="234"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="230" t="s">
+      <c r="C5" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="230"/>
-      <c r="E5" s="230"/>
-      <c r="F5" s="230"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="230"/>
-      <c r="L5" s="230"/>
-      <c r="P5" s="234"/>
-      <c r="Q5" s="234"/>
-      <c r="R5" s="234"/>
-      <c r="S5" s="234"/>
-      <c r="T5" s="234"/>
-      <c r="U5" s="234"/>
-      <c r="V5" s="234"/>
-      <c r="W5" s="234"/>
-      <c r="X5" s="234"/>
-      <c r="Y5" s="234"/>
-      <c r="Z5" s="234"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17401,30 +17372,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="230" t="s">
+      <c r="C11" s="241" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="230"/>
-      <c r="E11" s="230"/>
-      <c r="F11" s="230"/>
-      <c r="G11" s="230"/>
-      <c r="H11" s="230"/>
-      <c r="I11" s="230"/>
-      <c r="J11" s="230"/>
-      <c r="K11" s="230"/>
-      <c r="L11" s="230"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="234"/>
-      <c r="Q11" s="234"/>
-      <c r="R11" s="234"/>
-      <c r="S11" s="234"/>
-      <c r="T11" s="234"/>
-      <c r="U11" s="234"/>
-      <c r="V11" s="234"/>
-      <c r="W11" s="234"/>
-      <c r="X11" s="234"/>
-      <c r="Y11" s="234"/>
-      <c r="Z11" s="234"/>
+      <c r="P11" s="246"/>
+      <c r="Q11" s="246"/>
+      <c r="R11" s="246"/>
+      <c r="S11" s="246"/>
+      <c r="T11" s="246"/>
+      <c r="U11" s="246"/>
+      <c r="V11" s="246"/>
+      <c r="W11" s="246"/>
+      <c r="X11" s="246"/>
+      <c r="Y11" s="246"/>
+      <c r="Z11" s="246"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17666,18 +17637,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="230" t="s">
+      <c r="C18" s="241" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="230"/>
-      <c r="E18" s="230"/>
-      <c r="F18" s="230"/>
-      <c r="G18" s="230"/>
-      <c r="H18" s="230"/>
-      <c r="I18" s="230"/>
-      <c r="J18" s="230"/>
-      <c r="K18" s="230"/>
-      <c r="L18" s="230"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17890,23 +17861,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="234"/>
-      <c r="C25" s="234"/>
+      <c r="B25" s="246"/>
+      <c r="C25" s="246"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="230" t="s">
+      <c r="C26" s="241" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="230"/>
-      <c r="E26" s="230"/>
-      <c r="F26" s="230"/>
-      <c r="G26" s="230"/>
-      <c r="H26" s="230"/>
-      <c r="I26" s="230"/>
-      <c r="J26" s="230"/>
-      <c r="K26" s="230"/>
-      <c r="L26" s="230"/>
+      <c r="D26" s="241"/>
+      <c r="E26" s="241"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="241"/>
+      <c r="H26" s="241"/>
+      <c r="I26" s="241"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="241"/>
+      <c r="L26" s="241"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18098,18 +18069,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="230" t="s">
+      <c r="C33" s="241" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="230"/>
-      <c r="E33" s="230"/>
-      <c r="F33" s="230"/>
-      <c r="G33" s="230"/>
-      <c r="H33" s="230"/>
-      <c r="I33" s="230"/>
-      <c r="J33" s="230"/>
-      <c r="K33" s="230"/>
-      <c r="L33" s="230"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="241"/>
+      <c r="F33" s="241"/>
+      <c r="G33" s="241"/>
+      <c r="H33" s="241"/>
+      <c r="I33" s="241"/>
+      <c r="J33" s="241"/>
+      <c r="K33" s="241"/>
+      <c r="L33" s="241"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18293,18 +18264,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="230" t="s">
+      <c r="C40" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="230"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
+      <c r="D40" s="241"/>
+      <c r="E40" s="241"/>
+      <c r="F40" s="241"/>
+      <c r="G40" s="241"/>
+      <c r="H40" s="241"/>
+      <c r="I40" s="241"/>
+      <c r="J40" s="241"/>
+      <c r="K40" s="241"/>
+      <c r="L40" s="241"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18568,12 +18539,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18581,6 +18546,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18618,60 +18589,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="233" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
-      <c r="S2" s="234"/>
-      <c r="T2" s="234"/>
-      <c r="U2" s="234"/>
-      <c r="V2" s="234"/>
-      <c r="W2" s="234"/>
-      <c r="X2" s="234"/>
-      <c r="Y2" s="234"/>
-      <c r="Z2" s="234"/>
-      <c r="AA2" s="234"/>
-      <c r="AB2" s="234"/>
-      <c r="AC2" s="234"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
+      <c r="X2" s="246"/>
+      <c r="Y2" s="246"/>
+      <c r="Z2" s="246"/>
+      <c r="AA2" s="246"/>
+      <c r="AB2" s="246"/>
+      <c r="AC2" s="246"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="230" t="s">
+      <c r="C4" s="241" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
-      <c r="S4" s="234"/>
-      <c r="T4" s="234"/>
-      <c r="U4" s="234"/>
-      <c r="V4" s="234"/>
-      <c r="W4" s="234"/>
-      <c r="X4" s="234"/>
-      <c r="Y4" s="234"/>
-      <c r="Z4" s="234"/>
-      <c r="AA4" s="234"/>
-      <c r="AB4" s="234"/>
-      <c r="AC4" s="234"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
+      <c r="X4" s="246"/>
+      <c r="Y4" s="246"/>
+      <c r="Z4" s="246"/>
+      <c r="AA4" s="246"/>
+      <c r="AB4" s="246"/>
+      <c r="AC4" s="246"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19034,18 +19005,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="230" t="s">
+      <c r="C13" s="241" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="230"/>
-      <c r="E13" s="230"/>
-      <c r="F13" s="230"/>
-      <c r="G13" s="230"/>
-      <c r="H13" s="230"/>
-      <c r="I13" s="230"/>
-      <c r="J13" s="230"/>
-      <c r="K13" s="230"/>
-      <c r="L13" s="230"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19138,18 +19109,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="230" t="s">
+      <c r="C18" s="241" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="230"/>
-      <c r="E18" s="230"/>
-      <c r="F18" s="230"/>
-      <c r="G18" s="230"/>
-      <c r="H18" s="230"/>
-      <c r="I18" s="230"/>
-      <c r="J18" s="230"/>
-      <c r="K18" s="230"/>
-      <c r="L18" s="230"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19341,18 +19312,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="230" t="s">
+      <c r="C25" s="241" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="230"/>
-      <c r="E25" s="230"/>
-      <c r="F25" s="230"/>
-      <c r="G25" s="230"/>
-      <c r="H25" s="230"/>
-      <c r="I25" s="230"/>
-      <c r="J25" s="230"/>
-      <c r="K25" s="230"/>
-      <c r="L25" s="230"/>
+      <c r="D25" s="241"/>
+      <c r="E25" s="241"/>
+      <c r="F25" s="241"/>
+      <c r="G25" s="241"/>
+      <c r="H25" s="241"/>
+      <c r="I25" s="241"/>
+      <c r="J25" s="241"/>
+      <c r="K25" s="241"/>
+      <c r="L25" s="241"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19490,18 +19461,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="230" t="s">
+      <c r="C31" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="230"/>
-      <c r="E31" s="230"/>
-      <c r="F31" s="230"/>
-      <c r="G31" s="230"/>
-      <c r="H31" s="230"/>
-      <c r="I31" s="230"/>
-      <c r="J31" s="230"/>
-      <c r="K31" s="230"/>
-      <c r="L31" s="230"/>
+      <c r="D31" s="241"/>
+      <c r="E31" s="241"/>
+      <c r="F31" s="241"/>
+      <c r="G31" s="241"/>
+      <c r="H31" s="241"/>
+      <c r="I31" s="241"/>
+      <c r="J31" s="241"/>
+      <c r="K31" s="241"/>
+      <c r="L31" s="241"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19640,16 +19611,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19712,10 +19683,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="232" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="231"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19732,7 +19703,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19741,7 +19712,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>628331.07999999996</v>
+        <v>620412</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19800,10 +19771,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="231" t="s">
+      <c r="B15" s="232" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="231"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19811,7 +19782,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.4443034646731368E-2</v>
+        <v>7.5321671244759289E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19820,7 +19791,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92555696535326859</v>
+        <v>0.9246783287552407</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19847,7 +19818,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14457500282912109</v>
+        <v>0.14447975422871187</v>
       </c>
     </row>
   </sheetData>
@@ -19892,60 +19863,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="231" t="s">
+      <c r="C3" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="232"/>
-      <c r="H3" s="233" t="s">
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="P3" s="234"/>
-      <c r="Q3" s="234"/>
-      <c r="R3" s="234"/>
-      <c r="S3" s="234"/>
-      <c r="T3" s="234"/>
-      <c r="U3" s="234"/>
-      <c r="V3" s="234"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="234"/>
-      <c r="Y3" s="234"/>
-      <c r="Z3" s="234"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="230" t="s">
+      <c r="C5" s="241" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="230"/>
-      <c r="E5" s="230"/>
-      <c r="F5" s="230"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="230"/>
-      <c r="L5" s="230"/>
-      <c r="P5" s="234"/>
-      <c r="Q5" s="234"/>
-      <c r="R5" s="234"/>
-      <c r="S5" s="234"/>
-      <c r="T5" s="234"/>
-      <c r="U5" s="234"/>
-      <c r="V5" s="234"/>
-      <c r="W5" s="234"/>
-      <c r="X5" s="234"/>
-      <c r="Y5" s="234"/>
-      <c r="Z5" s="234"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20098,7 +20069,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-29566.505306761417</v>
+        <v>-29589.128811016464</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20152,23 +20123,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8083.9907775835545</v>
+        <v>-8084.6635625799163</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5704.3157581878513</v>
+        <v>-5705.2652738071865</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4179.6545046268784</v>
+        <v>-4180.6981387497526</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3989.717357642402</v>
+        <v>-3991.0456902243664</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1838.2706141965093</v>
+        <v>-1839.0356860508248</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20187,14 +20158,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-15051.462844856744</v>
+        <v>-15069.248902318086</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="231" t="s">
+      <c r="B13" s="232" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="231"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20210,14 +20181,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14457500282912109</v>
+        <v>0.14447975422871187</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="231" t="s">
+      <c r="B18" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="231"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20225,7 +20196,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23795.949012237197</v>
+        <v>-23800.708351412046</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20234,7 +20205,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-15051.462844856744</v>
+        <v>-15069.248902318086</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20243,7 +20214,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-38847.411857093939</v>
+        <v>-38869.957253730128</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20270,7 +20241,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-51247.411857093939</v>
+        <v>-51269.957253730128</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20283,12 +20254,12 @@
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="248" t="s">
+      <c r="B26" s="230" t="s">
         <v>187</v>
       </c>
-      <c r="C26" s="249">
+      <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-10.160073722659385</v>
+        <v>-10.16454346822564</v>
       </c>
     </row>
   </sheetData>
@@ -20331,37 +20302,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="233" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="230" t="s">
+      <c r="C4" s="241" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20557,23 +20528,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8083.9907775835545</v>
+        <v>-8084.6635625799163</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5704.3157581878513</v>
+        <v>-5705.2652738071865</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4179.6545046268784</v>
+        <v>-4180.6981387497526</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-3989.717357642402</v>
+        <v>-3991.0456902243664</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1838.2706141965093</v>
+        <v>-1839.0356860508248</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -20581,18 +20552,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="230" t="s">
+      <c r="C11" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="230"/>
-      <c r="E11" s="230"/>
-      <c r="F11" s="230"/>
-      <c r="G11" s="230"/>
-      <c r="H11" s="230"/>
-      <c r="I11" s="230"/>
-      <c r="J11" s="230"/>
-      <c r="K11" s="230"/>
-      <c r="L11" s="230"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
       <c r="N11" s="90"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20786,18 +20757,18 @@
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="230" t="s">
+      <c r="C17" s="241" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="230"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="230"/>
-      <c r="G17" s="230"/>
-      <c r="H17" s="230"/>
-      <c r="I17" s="230"/>
-      <c r="J17" s="230"/>
-      <c r="K17" s="230"/>
-      <c r="L17" s="230"/>
+      <c r="D17" s="241"/>
+      <c r="E17" s="241"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
       <c r="N17" s="90"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20931,18 +20902,18 @@
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="230" t="s">
+      <c r="C22" s="241" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="230"/>
-      <c r="E22" s="230"/>
-      <c r="F22" s="230"/>
-      <c r="G22" s="230"/>
-      <c r="H22" s="230"/>
-      <c r="I22" s="230"/>
-      <c r="J22" s="230"/>
-      <c r="K22" s="230"/>
-      <c r="L22" s="230"/>
+      <c r="D22" s="241"/>
+      <c r="E22" s="241"/>
+      <c r="F22" s="241"/>
+      <c r="G22" s="241"/>
+      <c r="H22" s="241"/>
+      <c r="I22" s="241"/>
+      <c r="J22" s="241"/>
+      <c r="K22" s="241"/>
+      <c r="L22" s="241"/>
       <c r="N22" s="90"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21026,18 +20997,18 @@
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="230" t="s">
+      <c r="C27" s="241" t="s">
         <v>195</v>
       </c>
-      <c r="D27" s="230"/>
-      <c r="E27" s="230"/>
-      <c r="F27" s="230"/>
-      <c r="G27" s="230"/>
-      <c r="H27" s="230"/>
-      <c r="I27" s="230"/>
-      <c r="J27" s="230"/>
-      <c r="K27" s="230"/>
-      <c r="L27" s="230"/>
+      <c r="D27" s="241"/>
+      <c r="E27" s="241"/>
+      <c r="F27" s="241"/>
+      <c r="G27" s="241"/>
+      <c r="H27" s="241"/>
+      <c r="I27" s="241"/>
+      <c r="J27" s="241"/>
+      <c r="K27" s="241"/>
+      <c r="L27" s="241"/>
       <c r="N27" s="90"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21307,10 +21278,10 @@
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="231" t="s">
+      <c r="B38" s="232" t="s">
         <v>200</v>
       </c>
-      <c r="C38" s="231"/>
+      <c r="C38" s="232"/>
       <c r="N38" s="90"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
@@ -21328,7 +21299,7 @@
       </c>
       <c r="C40" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14457500282912109</v>
+        <v>0.14447975422871187</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
@@ -21353,8 +21324,8 @@
         <v>410</v>
       </c>
       <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5-G31+G32</f>
-        <v>220735.41368170478</v>
+        <f ca="1">C42/(1+C40)^5</f>
+        <v>221484.5552321157</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
@@ -21363,7 +21334,7 @@
       </c>
       <c r="C44" s="93">
         <f ca="1">SUM(H9:K9)+C43</f>
-        <v>198777.73528366411</v>
+        <v>199522.88256675447</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21390,7 +21361,7 @@
       </c>
       <c r="C47" s="107">
         <f ca="1">C44+C45-C46</f>
-        <v>186377.73528366411</v>
+        <v>187122.88256675447</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.2">
@@ -21403,19 +21374,19 @@
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="248" t="s">
+      <c r="B49" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C49" s="249">
+      <c r="C49" s="231">
         <f ca="1">C47/C48</f>
-        <v>36.95038368034578</v>
+        <v>37.098113117913257</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="231" t="s">
+      <c r="B51" s="232" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="231"/>
+      <c r="C51" s="232"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B52" s="1" t="s">
@@ -21462,19 +21433,19 @@
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="248" t="s">
+      <c r="B57" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C57" s="249">
+      <c r="C57" s="231">
         <f>C56/(1+C53)^5</f>
         <v>48.738460839691712</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="231" t="s">
+      <c r="B59" s="232" t="s">
         <v>317</v>
       </c>
-      <c r="C59" s="231"/>
+      <c r="C59" s="232"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B60" s="1" t="s">
@@ -21491,7 +21462,7 @@
       </c>
       <c r="C61" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14457500282912109</v>
+        <v>0.14447975422871187</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.2">
@@ -21516,8 +21487,8 @@
         <v>410</v>
       </c>
       <c r="C64" s="63">
-        <f ca="1">C63/(1+C61)^5-G31+G32</f>
-        <v>-74522.284490887163</v>
+        <f ca="1">C63/(1+C61)^5</f>
+        <v>-73896.02656430038</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.2">
@@ -21526,7 +21497,7 @@
       </c>
       <c r="C65" s="93">
         <f ca="1">SUM(H9:K9)+C64</f>
-        <v>-96479.962888927854</v>
+        <v>-95857.699229661608</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21553,7 +21524,7 @@
       </c>
       <c r="C68" s="93">
         <f ca="1">C65+C66-C67</f>
-        <v>-108879.96288892785</v>
+        <v>-108257.69922966161</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.2">
@@ -21566,12 +21537,12 @@
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="248" t="s">
+      <c r="B70" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C70" s="249">
+      <c r="C70" s="231">
         <f ca="1">C68/C69</f>
-        <v>-21.58603546568752</v>
+        <v>-21.462668364326252</v>
       </c>
     </row>
   </sheetData>
@@ -21623,10 +21594,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="231"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21635,7 +21606,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.160073722659385</v>
+        <v>-10.16454346822564</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21644,7 +21615,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C49</f>
-        <v>36.95038368034578</v>
+        <v>37.098113117913257</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21662,16 +21633,16 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C70</f>
-        <v>-21.58603546568752</v>
+        <v>-21.462668364326252</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="248" t="s">
+      <c r="B9" s="230" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="249">
+      <c r="C9" s="231">
         <f ca="1">AVERAGE(C5:C8)</f>
-        <v>13.48568383292265</v>
+        <v>13.552340531263269</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21680,7 +21651,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C5</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21689,7 +21660,7 @@
       </c>
       <c r="C11" s="151">
         <f ca="1">(C9-C10)/C10</f>
-        <v>-0.89174212223711447</v>
+        <v>-0.88981836966452632</v>
       </c>
     </row>
   </sheetData>
@@ -21745,37 +21716,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="231" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="231"/>
-      <c r="E2" s="231"/>
-      <c r="F2" s="231"/>
-      <c r="G2" s="232"/>
-      <c r="H2" s="233" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="231"/>
-      <c r="J2" s="231"/>
-      <c r="K2" s="231"/>
-      <c r="L2" s="231"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="230" t="s">
+      <c r="C4" s="241" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="230"/>
-      <c r="E4" s="230"/>
-      <c r="F4" s="230"/>
-      <c r="G4" s="230"/>
-      <c r="H4" s="230"/>
-      <c r="I4" s="230"/>
-      <c r="J4" s="230"/>
-      <c r="K4" s="230"/>
-      <c r="L4" s="230"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21888,18 +21859,18 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="230" t="s">
+      <c r="C9" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="230"/>
-      <c r="E9" s="230"/>
-      <c r="F9" s="230"/>
-      <c r="G9" s="230"/>
-      <c r="H9" s="230"/>
-      <c r="I9" s="230"/>
-      <c r="J9" s="230"/>
-      <c r="K9" s="230"/>
-      <c r="L9" s="230"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22020,18 +21991,18 @@
       <c r="N13" s="90"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="230" t="s">
+      <c r="C14" s="241" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="230"/>
-      <c r="E14" s="230"/>
-      <c r="F14" s="230"/>
-      <c r="G14" s="230"/>
-      <c r="H14" s="230"/>
-      <c r="I14" s="230"/>
-      <c r="J14" s="230"/>
-      <c r="K14" s="230"/>
-      <c r="L14" s="230"/>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
       <c r="N14" s="90"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22121,10 +22092,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="231" t="s">
+      <c r="B20" s="232" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="231"/>
+      <c r="C20" s="232"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22171,10 +22142,10 @@
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B26" s="248" t="s">
+      <c r="B26" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C26" s="249">
+      <c r="C26" s="231">
         <f>C23/(C24-C25)</f>
         <v>0</v>
       </c>
@@ -22225,60 +22196,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="231" t="s">
+      <c r="C3" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="231"/>
-      <c r="E3" s="231"/>
-      <c r="F3" s="231"/>
-      <c r="G3" s="232"/>
-      <c r="H3" s="233" t="s">
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="231"/>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="P3" s="234"/>
-      <c r="Q3" s="234"/>
-      <c r="R3" s="234"/>
-      <c r="S3" s="234"/>
-      <c r="T3" s="234"/>
-      <c r="U3" s="234"/>
-      <c r="V3" s="234"/>
-      <c r="W3" s="234"/>
-      <c r="X3" s="234"/>
-      <c r="Y3" s="234"/>
-      <c r="Z3" s="234"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
+      <c r="P3" s="246"/>
+      <c r="Q3" s="246"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
+      <c r="X3" s="246"/>
+      <c r="Y3" s="246"/>
+      <c r="Z3" s="246"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="230" t="s">
+      <c r="C5" s="241" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="230"/>
-      <c r="E5" s="230"/>
-      <c r="F5" s="230"/>
-      <c r="G5" s="230"/>
-      <c r="H5" s="230"/>
-      <c r="I5" s="230"/>
-      <c r="J5" s="230"/>
-      <c r="K5" s="230"/>
-      <c r="L5" s="230"/>
-      <c r="P5" s="234"/>
-      <c r="Q5" s="234"/>
-      <c r="R5" s="234"/>
-      <c r="S5" s="234"/>
-      <c r="T5" s="234"/>
-      <c r="U5" s="234"/>
-      <c r="V5" s="234"/>
-      <c r="W5" s="234"/>
-      <c r="X5" s="234"/>
-      <c r="Y5" s="234"/>
-      <c r="Z5" s="234"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="246"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
+      <c r="X5" s="246"/>
+      <c r="Y5" s="246"/>
+      <c r="Z5" s="246"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22413,7 +22384,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-473038.20609522233</v>
+        <v>-473400.16236152302</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22467,23 +22438,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6809.9969795534789</v>
+        <v>-6810.5637372254214</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9817.1766712441367</v>
+        <v>-9818.8107958231867</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-14152.276143996089</v>
+        <v>-14155.809880644385</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20401.682353602617</v>
+        <v>-20408.474869705358</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-29410.72083545231</v>
+        <v>-29422.961315473349</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22502,15 +22473,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-240810.23135364283</v>
+        <v>-241094.79270533888</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="245" t="s">
+      <c r="B14" s="247" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="246"/>
+      <c r="C14" s="248"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22518,7 +22489,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22527,7 +22498,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-66.178050027258408</v>
+        <v>-66.239376150715813</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22537,20 +22508,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="247" t="s">
+      <c r="E17" s="249" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="245" t="s">
+      <c r="B19" s="247" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="246"/>
+      <c r="C19" s="248"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22566,7 +22537,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14457500282912109</v>
+        <v>0.14447975422871187</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22584,7 +22555,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>628331.07999999996</v>
+        <v>620412</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22611,15 +22582,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>640731.07999999996</v>
+        <v>632812</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="245" t="s">
+      <c r="B28" s="247" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="246"/>
+      <c r="C28" s="248"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -22627,7 +22598,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-80591.852983848628</v>
+        <v>-80616.620598871697</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22636,7 +22607,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-240810.23135364283</v>
+        <v>-241094.79270533888</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22645,7 +22616,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-321402.08433749143</v>
+        <v>-321711.41330421058</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22672,7 +22643,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-333802.08433749143</v>
+        <v>-334111.41330421058</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22690,21 +22661,21 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-66.178050027258408</v>
+        <v>-66.239376150715813</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29363,7 +29334,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29434,7 +29405,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30740,7 +30711,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-59.037914691943115</v>
+        <v>-58.293838862559234</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30777,7 +30748,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.679160339809229</v>
+        <v>10.544567085145182</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30838,7 +30809,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.1774814374814371</v>
+        <v>7.0870210870210872</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -30899,7 +30870,7 @@
       </c>
       <c r="AC153" s="140">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>628331.07999999996</v>
+        <v>620412</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -30960,7 +30931,7 @@
       </c>
       <c r="AC154" s="140">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>656332.07999999996</v>
+        <v>648413</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -30997,7 +30968,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="178">
         <f ca="1">AC154/AC5</f>
-        <v>11.508137186141113</v>
+        <v>11.369283910786926</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31034,7 +31005,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="178">
         <f ca="1">AC154/AC12</f>
-        <v>-8523.7932467532464</v>
+        <v>-8420.9480519480512</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31169,7 +31140,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-55.876485549132944</v>
+        <v>-55.172254335260114</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31206,7 +31177,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-116.51554766554233</v>
+        <v>-115.10971063376532</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31243,7 +31214,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-1.7896615905105315E-2</v>
+        <v>-1.8125052384544465E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31280,7 +31251,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-1.6938267640683957E-2</v>
+        <v>-1.7154471544715451E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31391,7 +31362,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="151">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>2.5448367125178659E-3</v>
+        <v>2.5773195876288659E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31894,7 +31865,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="151">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.9734818783753307E-2</v>
+        <v>-1.9986718503188203E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33640,15 +33611,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="231" t="s">
+      <c r="B4" s="232" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="231"/>
-      <c r="E4" s="231" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="231"/>
-      <c r="G4" s="231"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33656,7 +33627,7 @@
       </c>
       <c r="C5" s="167">
         <f ca="1">Overview!C5</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -33672,7 +33643,7 @@
       </c>
       <c r="C6" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>628331.07999999996</v>
+        <v>620412</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33692,7 +33663,7 @@
       </c>
       <c r="C7" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>656332.07999999996</v>
+        <v>648413</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33712,7 +33683,7 @@
       </c>
       <c r="C8" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-59.037914691943115</v>
+        <v>-58.293838862559234</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>238</v>
@@ -33732,7 +33703,7 @@
       </c>
       <c r="C9" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>10.679160339809229</v>
+        <v>10.544567085145182</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>239</v>
@@ -33752,7 +33723,7 @@
       </c>
       <c r="C10" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>7.1774814374814371</v>
+        <v>7.0870210870210872</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33772,7 +33743,7 @@
       </c>
       <c r="C11" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>11.508137186141113</v>
+        <v>11.369283910786926</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33781,18 +33752,18 @@
       </c>
       <c r="C12" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-8523.7932467532464</v>
+        <v>-8420.9480519480512</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="231" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="231"/>
-      <c r="E15" s="231" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="231"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33843,14 +33814,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="231" t="s">
+      <c r="B21" s="232" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="231"/>
-      <c r="E21" s="231" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="231"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33919,14 +33890,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="231" t="s">
+      <c r="B29" s="232" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="231"/>
-      <c r="E29" s="231" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="231"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34002,14 +33973,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="231" t="s">
+      <c r="B37" s="232" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="231"/>
-      <c r="E37" s="231" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="231"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34017,7 +33988,7 @@
       </c>
       <c r="C38" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6938267640683957E-2</v>
+        <v>-1.7154471544715451E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>265</v>
@@ -34033,7 +34004,7 @@
       </c>
       <c r="C39" s="210">
         <f ca="1">Statement!AC161</f>
-        <v>-1.7896615905105315E-2</v>
+        <v>-1.8125052384544465E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>267</v>
@@ -34074,18 +34045,18 @@
       </c>
       <c r="C42" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>2.5448367125178659E-3</v>
+        <v>2.5773195876288659E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="231" t="s">
+      <c r="B45" s="232" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="231"/>
-      <c r="E45" s="231" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>280</v>
       </c>
-      <c r="F45" s="231"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34118,18 +34089,18 @@
       </c>
       <c r="F48" s="170">
         <f ca="1">Statement!AC176</f>
-        <v>-1.9734818783753307E-2</v>
+        <v>-1.9986718503188203E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="231" t="s">
+      <c r="B51" s="232" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="231"/>
-      <c r="E51" s="231" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="231"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34297,7 +34268,7 @@
       </c>
       <c r="I6" s="167">
         <f ca="1">Statement!AC116</f>
-        <v>124.57</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34326,7 +34297,7 @@
       </c>
       <c r="I7" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>628331.07999999996</v>
+        <v>620412</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34355,7 +34326,7 @@
       </c>
       <c r="I8" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>656332.07999999996</v>
+        <v>648413</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34384,7 +34355,7 @@
       </c>
       <c r="I9" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-59.037914691943115</v>
+        <v>-58.293838862559234</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34413,7 +34384,7 @@
       </c>
       <c r="I10" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>10.679160339809229</v>
+        <v>10.544567085145182</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34442,7 +34413,7 @@
       </c>
       <c r="I11" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>7.1774814374814371</v>
+        <v>7.0870210870210872</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34471,7 +34442,7 @@
       </c>
       <c r="I12" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>11.508137186141113</v>
+        <v>11.369283910786926</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34500,7 +34471,7 @@
       </c>
       <c r="I13" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-8523.7932467532464</v>
+        <v>-8420.9480519480512</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35273,7 +35244,7 @@
       </c>
       <c r="I51" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-1.6938267640683957E-2</v>
+        <v>-1.7154471544715451E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35302,7 +35273,7 @@
       </c>
       <c r="I52" s="170">
         <f ca="1">Statement!AC161</f>
-        <v>-1.7896615905105315E-2</v>
+        <v>-1.8125052384544465E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35389,7 +35360,7 @@
       </c>
       <c r="I55" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>2.5448367125178659E-3</v>
+        <v>2.5773195876288659E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35625,7 +35596,7 @@
       </c>
       <c r="I68" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-1.9734818783753307E-2</v>
+        <v>-1.9986718503188203E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36163,14 +36134,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="236" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="F3" s="242" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="241"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36237,19 +36208,19 @@
       <c r="B7" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C7" s="238">
+      <c r="C7" s="239">
         <f>Statement!AA89</f>
         <v>0.18789128673491934</v>
       </c>
-      <c r="D7" s="239"/>
-      <c r="F7" s="238">
+      <c r="D7" s="240"/>
+      <c r="F7" s="239">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.25421883505715842</v>
       </c>
-      <c r="G7" s="239"/>
+      <c r="G7" s="240"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
@@ -36276,19 +36247,19 @@
       <c r="B9" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="238">
+      <c r="C9" s="239">
         <f>Statement!AA90</f>
         <v>0.16877278250303768</v>
       </c>
-      <c r="D9" s="239"/>
-      <c r="F9" s="238">
+      <c r="D9" s="240"/>
+      <c r="F9" s="239">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>3.2413867124610925E-2</v>
       </c>
-      <c r="G9" s="239"/>
+      <c r="G9" s="240"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
@@ -36315,19 +36286,19 @@
       <c r="B11" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C11" s="238">
+      <c r="C11" s="239">
         <f>Statement!AA91</f>
         <v>0.21731812231157657</v>
       </c>
-      <c r="D11" s="239"/>
-      <c r="F11" s="238">
+      <c r="D11" s="240"/>
+      <c r="F11" s="239">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.83766233766233766</v>
       </c>
-      <c r="G11" s="239"/>
+      <c r="G11" s="240"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="202" t="s">
@@ -36354,19 +36325,19 @@
       <c r="B13" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C13" s="238">
+      <c r="C13" s="239">
         <f>Statement!AA95</f>
         <v>-0.44441824826122833</v>
       </c>
-      <c r="D13" s="239"/>
-      <c r="F13" s="238">
+      <c r="D13" s="240"/>
+      <c r="F13" s="239">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-0.29845192021434952</v>
       </c>
-      <c r="G13" s="239"/>
+      <c r="G13" s="240"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="202" t="s">
@@ -36393,19 +36364,19 @@
       <c r="B15" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C15" s="238">
+      <c r="C15" s="239">
         <f>Statement!AA96</f>
         <v>1.572704081632653</v>
       </c>
-      <c r="D15" s="239"/>
-      <c r="F15" s="238">
+      <c r="D15" s="240"/>
+      <c r="F15" s="239">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5654911838790933</v>
       </c>
-      <c r="G15" s="239"/>
+      <c r="G15" s="240"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="202" t="s">
@@ -36432,19 +36403,19 @@
       <c r="B17" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C17" s="238">
+      <c r="C17" s="239">
         <f>Statement!AA98</f>
         <v>-1.9594957081545064</v>
       </c>
-      <c r="D17" s="239"/>
-      <c r="F17" s="238">
+      <c r="D17" s="240"/>
+      <c r="F17" s="239">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-2.781014393420151</v>
       </c>
-      <c r="G17" s="239"/>
+      <c r="G17" s="240"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="202" t="s">
@@ -36471,22 +36442,22 @@
       <c r="B19" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="238">
+      <c r="C19" s="239">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.1314184536690932E-3</v>
       </c>
-      <c r="D19" s="239"/>
-      <c r="F19" s="238">
+      <c r="D19" s="240"/>
+      <c r="F19" s="239">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.16823071641107806</v>
       </c>
-      <c r="G19" s="239"/>
+      <c r="G19" s="240"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="202" t="s">
@@ -36513,22 +36484,22 @@
       <c r="B21" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C21" s="238">
+      <c r="C21" s="239">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-1.9589041095890414</v>
       </c>
-      <c r="D21" s="239"/>
-      <c r="F21" s="238">
+      <c r="D21" s="240"/>
+      <c r="F21" s="239">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.2238805970149254</v>
       </c>
-      <c r="G21" s="239"/>
+      <c r="G21" s="240"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36576,22 +36547,22 @@
       <c r="B25" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="238">
+      <c r="C25" s="239">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14882878219231266</v>
       </c>
-      <c r="D25" s="239"/>
-      <c r="F25" s="238">
+      <c r="D25" s="240"/>
+      <c r="F25" s="239">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.12781095159446068</v>
       </c>
-      <c r="G25" s="239"/>
+      <c r="G25" s="240"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36618,22 +36589,22 @@
       <c r="B27" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C27" s="238">
+      <c r="C27" s="239">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.23950910530482977</v>
       </c>
-      <c r="D27" s="239"/>
-      <c r="F27" s="238">
+      <c r="D27" s="240"/>
+      <c r="F27" s="239">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.58974358974358976</v>
       </c>
-      <c r="G27" s="239"/>
+      <c r="G27" s="240"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36660,22 +36631,22 @@
       <c r="B29" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C29" s="238">
+      <c r="C29" s="239">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18467798732295171</v>
       </c>
-      <c r="D29" s="239"/>
-      <c r="F29" s="238">
+      <c r="D29" s="240"/>
+      <c r="F29" s="239">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28187976291278577</v>
       </c>
-      <c r="G29" s="239"/>
+      <c r="G29" s="240"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36702,22 +36673,22 @@
       <c r="B31" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C31" s="238">
+      <c r="C31" s="239">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>6.3456926766279287E-2</v>
       </c>
-      <c r="D31" s="239"/>
-      <c r="F31" s="238">
+      <c r="D31" s="240"/>
+      <c r="F31" s="239">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.30518451437627347</v>
       </c>
-      <c r="G31" s="239"/>
+      <c r="G31" s="240"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36744,37 +36715,25 @@
       <c r="B33" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C33" s="238">
+      <c r="C33" s="239">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.11624203821656051</v>
       </c>
-      <c r="D33" s="239"/>
-      <c r="F33" s="238">
+      <c r="D33" s="240"/>
+      <c r="F33" s="239">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33428300094966762</v>
       </c>
-      <c r="G33" s="239"/>
+      <c r="G33" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36791,6 +36750,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3DAF6D-9276-F34B-8401-C9416840322C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EADBBD-276F-C94D-BCEF-3B3773E4AAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="7" activeTab="17" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="418">
   <si>
     <t>Ticker</t>
   </si>
@@ -1393,6 +1393,21 @@
   </si>
   <si>
     <t>Year 5 FCFF</t>
+  </si>
+  <si>
+    <t>EV/Sales</t>
+  </si>
+  <si>
+    <t>EV/Sales valuation</t>
+  </si>
+  <si>
+    <t>Year 5 Sales</t>
+  </si>
+  <si>
+    <t>Applied EV/Sales ratio</t>
+  </si>
+  <si>
+    <t>EV/Sales price</t>
   </si>
 </sst>
 </file>
@@ -2305,7 +2320,16 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2317,6 +2341,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2326,38 +2356,23 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12785,11 +12800,11 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>31.21</v>
-    <v>2.2450000000000001</v>
+    <v>2.2642000000000002</v>
     <v>-4.3899999999999997</v>
     <v>-3.4460999999999999E-2</v>
-    <v>1.2800000000000001E-2</v>
-    <v>1.0410000000000001E-4</v>
+    <v>-5.2200000000000003E-2</v>
+    <v>-4.2439999999999996E-4</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12800,21 +12815,21 @@
     <v>126.93</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.840666435157</v>
+    <v>46290.999997858591</v>
     <v>0</v>
     <v>122.84</v>
     <v>650063487000</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>126.8</v>
+    <v>126.83</v>
     <v>0</v>
     <v>127.39</v>
     <v>123</v>
-    <v>123.0128</v>
+    <v>122.9478</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>96039166</v>
+    <v>97728428</v>
     <v>101957193</v>
     <v>1989</v>
   </rv>
@@ -12837,19 +12852,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>39.47</v>
-    <v>0.48</v>
-    <v>9.3860000000000002E-3</v>
+    <v>0.22</v>
+    <v>4.2620000000000002E-3</v>
     <v>US</v>
-    <v>51.81</v>
+    <v>52.3</v>
     <v>Index</v>
     <v>3</v>
-    <v>50.87</v>
+    <v>51.62</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.21</v>
-    <v>51.14</v>
+    <v>51.86</v>
     <v>51.62</v>
+    <v>51.84</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13071,9 +13086,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13647,18 +13662,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>320</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="237"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="180" t="s">
@@ -13681,7 +13696,7 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.16454346822564</v>
+        <v>-10.117821197205226</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13705,7 +13720,7 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>37.098113117913257</v>
+        <v>36.914651209075622</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13738,7 +13753,7 @@
       </c>
       <c r="C6" s="203" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>123.0128</v>
+        <v>122.9478</v>
       </c>
       <c r="E6" s="180" t="s">
         <v>232</v>
@@ -13753,7 +13768,7 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.462668364326252</v>
+        <v>-21.324314605788395</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13772,12 +13787,12 @@
         <v>10.544567085145182</v>
       </c>
       <c r="H7" s="179" t="str">
-        <f>'AVG target price'!B9</f>
+        <f>'AVG target price'!B10</f>
         <v>AVG price</v>
       </c>
       <c r="I7" s="207">
-        <f ca="1">'AVG target price'!C9</f>
-        <v>13.552340531263269</v>
+        <f ca="1">'AVG target price'!C10</f>
+        <v>19.089891296408641</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13786,7 +13801,7 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>1.2800000000000001E-2</v>
+        <v>-5.2200000000000003E-2</v>
       </c>
       <c r="E8" s="180" t="s">
         <v>260</v>
@@ -13796,12 +13811,12 @@
         <v>-1.8125052384544465E-2</v>
       </c>
       <c r="H8" s="179" t="str">
-        <f>'AVG target price'!B11</f>
+        <f>'AVG target price'!B12</f>
         <v>Upside/Downside</v>
       </c>
       <c r="I8" s="208">
-        <f ca="1">'AVG target price'!C11</f>
-        <v>-0.88981836966452632</v>
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.84479763173651512</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13826,7 +13841,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.0410000000000001E-4</v>
+        <v>-4.2439999999999996E-4</v>
       </c>
       <c r="E10" s="180" t="s">
         <v>288</v>
@@ -13881,7 +13896,7 @@
       </c>
       <c r="C13" s="204" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2450000000000001</v>
+        <v>2.2642000000000002</v>
       </c>
       <c r="E13" s="180" t="s">
         <v>99</v>
@@ -13926,10 +13941,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="238" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="179" t="s">
         <v>291</v>
       </c>
@@ -14002,14 +14017,14 @@
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="238" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>373</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="179" t="s">
@@ -14023,7 +14038,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.62</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14038,7 +14053,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14058,15 +14073,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="232" t="s">
+      <c r="B33" s="233" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="232"/>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="233"/>
+      <c r="E33" s="233"/>
+      <c r="F33" s="233"/>
+      <c r="G33" s="233"/>
+      <c r="H33" s="233"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14085,24 +14100,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="232"/>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="232"/>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="232" t="s">
+      <c r="B42" s="233" t="s">
         <v>346</v>
       </c>
-      <c r="C42" s="232"/>
-      <c r="D42" s="232"/>
-      <c r="E42" s="232"/>
-      <c r="F42" s="232"/>
-      <c r="G42" s="232"/>
-      <c r="H42" s="232"/>
+      <c r="C42" s="233"/>
+      <c r="D42" s="233"/>
+      <c r="E42" s="233"/>
+      <c r="F42" s="233"/>
+      <c r="G42" s="233"/>
+      <c r="H42" s="233"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14153,24 +14168,24 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="232"/>
-      <c r="C52" s="232"/>
-      <c r="D52" s="232"/>
-      <c r="E52" s="232"/>
-      <c r="F52" s="232"/>
-      <c r="G52" s="232"/>
-      <c r="H52" s="232"/>
+      <c r="B52" s="233"/>
+      <c r="C52" s="233"/>
+      <c r="D52" s="233"/>
+      <c r="E52" s="233"/>
+      <c r="F52" s="233"/>
+      <c r="G52" s="233"/>
+      <c r="H52" s="233"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="232" t="s">
+      <c r="B55" s="233" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="232"/>
-      <c r="D55" s="232"/>
-      <c r="E55" s="232"/>
-      <c r="F55" s="232"/>
-      <c r="G55" s="232"/>
-      <c r="H55" s="232"/>
+      <c r="C55" s="233"/>
+      <c r="D55" s="233"/>
+      <c r="E55" s="233"/>
+      <c r="F55" s="233"/>
+      <c r="G55" s="233"/>
+      <c r="H55" s="233"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14185,28 +14200,28 @@
       </c>
     </row>
     <row r="62" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="232"/>
-      <c r="C62" s="232"/>
-      <c r="D62" s="232"/>
-      <c r="E62" s="232"/>
-      <c r="F62" s="232"/>
-      <c r="G62" s="232"/>
-      <c r="H62" s="232"/>
+      <c r="B62" s="233"/>
+      <c r="C62" s="233"/>
+      <c r="D62" s="233"/>
+      <c r="E62" s="233"/>
+      <c r="F62" s="233"/>
+      <c r="G62" s="233"/>
+      <c r="H62" s="233"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B55:H55"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B52:H52"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B52:H52"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14276,36 +14291,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
+      <c r="AA2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="233"/>
+      <c r="AC2" s="233"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14316,32 +14331,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="242" t="s">
+      <c r="S4" s="244" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
+      <c r="X4" s="245"/>
+      <c r="Y4" s="245"/>
+      <c r="Z4" s="245"/>
+      <c r="AA4" s="245"/>
+      <c r="AB4" s="245"/>
+      <c r="AC4" s="245"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15035,33 +15050,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="232" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="232"/>
+      <c r="I13" s="232"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="232"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="242" t="s">
+      <c r="S13" s="244" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="243"/>
-      <c r="U13" s="243"/>
-      <c r="V13" s="243"/>
-      <c r="W13" s="243"/>
-      <c r="X13" s="243"/>
-      <c r="Y13" s="243"/>
-      <c r="Z13" s="243"/>
-      <c r="AA13" s="243"/>
-      <c r="AB13" s="243"/>
-      <c r="AC13" s="243"/>
+      <c r="T13" s="245"/>
+      <c r="U13" s="245"/>
+      <c r="V13" s="245"/>
+      <c r="W13" s="245"/>
+      <c r="X13" s="245"/>
+      <c r="Y13" s="245"/>
+      <c r="Z13" s="245"/>
+      <c r="AA13" s="245"/>
+      <c r="AB13" s="245"/>
+      <c r="AC13" s="245"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15698,35 +15713,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
+      <c r="P2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="233"/>
+      <c r="R2" s="233"/>
+      <c r="S2" s="233"/>
+      <c r="T2" s="233"/>
+      <c r="U2" s="233"/>
+      <c r="V2" s="233"/>
+      <c r="W2" s="233"/>
+      <c r="X2" s="233" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="233"/>
+      <c r="Z2" s="233"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15735,31 +15750,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="P4" s="243" t="s">
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
+      <c r="P4" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
+      <c r="Q4" s="245"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="245"/>
+      <c r="V4" s="245"/>
+      <c r="W4" s="245"/>
+      <c r="X4" s="245"/>
+      <c r="Y4" s="245"/>
+      <c r="Z4" s="245"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15954,32 +15969,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="232" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="243" t="s">
+      <c r="P9" s="245" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="243"/>
-      <c r="S9" s="243"/>
-      <c r="T9" s="243"/>
-      <c r="U9" s="243"/>
-      <c r="V9" s="243"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
+      <c r="Q9" s="245"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="245"/>
+      <c r="V9" s="245"/>
+      <c r="W9" s="245"/>
+      <c r="X9" s="245"/>
+      <c r="Y9" s="245"/>
+      <c r="Z9" s="245"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16549,31 +16564,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="232" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
-      <c r="P18" s="243" t="s">
+      <c r="D18" s="232"/>
+      <c r="E18" s="232"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="232"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="232"/>
+      <c r="P18" s="245" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="243"/>
-      <c r="R18" s="243"/>
-      <c r="S18" s="243"/>
-      <c r="T18" s="243"/>
-      <c r="U18" s="243"/>
-      <c r="V18" s="243"/>
-      <c r="W18" s="243"/>
-      <c r="X18" s="243"/>
-      <c r="Y18" s="243"/>
-      <c r="Z18" s="243"/>
+      <c r="Q18" s="245"/>
+      <c r="R18" s="245"/>
+      <c r="S18" s="245"/>
+      <c r="T18" s="245"/>
+      <c r="U18" s="245"/>
+      <c r="V18" s="245"/>
+      <c r="W18" s="245"/>
+      <c r="X18" s="245"/>
+      <c r="Y18" s="245"/>
+      <c r="Z18" s="245"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17133,20 +17148,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="234"/>
+      <c r="H3" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17164,18 +17179,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="232" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
       <c r="P5" s="246"/>
       <c r="Q5" s="246"/>
       <c r="R5" s="246"/>
@@ -17372,18 +17387,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="232" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="232"/>
+      <c r="E11" s="232"/>
+      <c r="F11" s="232"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="232"/>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="232"/>
+      <c r="L11" s="232"/>
       <c r="N11" s="90"/>
       <c r="P11" s="246"/>
       <c r="Q11" s="246"/>
@@ -17637,18 +17652,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="232" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="232"/>
+      <c r="E18" s="232"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="232"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="232"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17866,18 +17881,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="232" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="232"/>
+      <c r="E26" s="232"/>
+      <c r="F26" s="232"/>
+      <c r="G26" s="232"/>
+      <c r="H26" s="232"/>
+      <c r="I26" s="232"/>
+      <c r="J26" s="232"/>
+      <c r="K26" s="232"/>
+      <c r="L26" s="232"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18069,18 +18084,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="241" t="s">
+      <c r="C33" s="232" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="241"/>
-      <c r="J33" s="241"/>
-      <c r="K33" s="241"/>
-      <c r="L33" s="241"/>
+      <c r="D33" s="232"/>
+      <c r="E33" s="232"/>
+      <c r="F33" s="232"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="232"/>
+      <c r="I33" s="232"/>
+      <c r="J33" s="232"/>
+      <c r="K33" s="232"/>
+      <c r="L33" s="232"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18264,18 +18279,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="241" t="s">
+      <c r="C40" s="232" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="241"/>
-      <c r="E40" s="241"/>
-      <c r="F40" s="241"/>
-      <c r="G40" s="241"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="241"/>
-      <c r="J40" s="241"/>
-      <c r="K40" s="241"/>
-      <c r="L40" s="241"/>
+      <c r="D40" s="232"/>
+      <c r="E40" s="232"/>
+      <c r="F40" s="232"/>
+      <c r="G40" s="232"/>
+      <c r="H40" s="232"/>
+      <c r="I40" s="232"/>
+      <c r="J40" s="232"/>
+      <c r="K40" s="232"/>
+      <c r="L40" s="232"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18539,6 +18554,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18546,12 +18567,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18589,20 +18604,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -18620,18 +18635,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="232" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
       <c r="S4" s="246"/>
       <c r="T4" s="246"/>
       <c r="U4" s="246"/>
@@ -19005,18 +19020,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="232" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="232"/>
+      <c r="E13" s="232"/>
+      <c r="F13" s="232"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="232"/>
+      <c r="I13" s="232"/>
+      <c r="J13" s="232"/>
+      <c r="K13" s="232"/>
+      <c r="L13" s="232"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19109,18 +19124,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="232" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="232"/>
+      <c r="E18" s="232"/>
+      <c r="F18" s="232"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="232"/>
+      <c r="I18" s="232"/>
+      <c r="J18" s="232"/>
+      <c r="K18" s="232"/>
+      <c r="L18" s="232"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19312,18 +19327,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="241" t="s">
+      <c r="C25" s="232" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="241"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="241"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241"/>
-      <c r="L25" s="241"/>
+      <c r="D25" s="232"/>
+      <c r="E25" s="232"/>
+      <c r="F25" s="232"/>
+      <c r="G25" s="232"/>
+      <c r="H25" s="232"/>
+      <c r="I25" s="232"/>
+      <c r="J25" s="232"/>
+      <c r="K25" s="232"/>
+      <c r="L25" s="232"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19461,18 +19476,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="241" t="s">
+      <c r="C31" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="241"/>
-      <c r="E31" s="241"/>
-      <c r="F31" s="241"/>
-      <c r="G31" s="241"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="241"/>
-      <c r="J31" s="241"/>
-      <c r="K31" s="241"/>
-      <c r="L31" s="241"/>
+      <c r="D31" s="232"/>
+      <c r="E31" s="232"/>
+      <c r="F31" s="232"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="232"/>
+      <c r="I31" s="232"/>
+      <c r="J31" s="232"/>
+      <c r="K31" s="232"/>
+      <c r="L31" s="232"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19611,16 +19626,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19683,10 +19698,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="233" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="233"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19730,7 +19745,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>5.1619999999999999E-2</v>
+        <v>5.1840000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19739,7 +19754,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2450000000000001</v>
+        <v>2.2642000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19771,10 +19786,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="233" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="233"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19809,7 +19824,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.152645</v>
+        <v>0.153729</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19818,7 +19833,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14447975422871187</v>
+        <v>0.14548210553708257</v>
       </c>
     </row>
   </sheetData>
@@ -19863,20 +19878,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="234"/>
+      <c r="H3" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19894,18 +19909,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="232" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
       <c r="P5" s="246"/>
       <c r="Q5" s="246"/>
       <c r="R5" s="246"/>
@@ -20069,7 +20084,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-29589.128811016464</v>
+        <v>-29352.770791278683</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20123,23 +20138,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8084.6635625799163</v>
+        <v>-8077.5890975485418</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5705.2652738071865</v>
+        <v>-5695.2848855921911</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4180.6981387497526</v>
+        <v>-4169.7328105604902</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3991.0456902243664</v>
+        <v>-3977.0945963992685</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1839.0356860508248</v>
+        <v>-1831.0035370374044</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20158,14 +20173,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-15069.248902318086</v>
+        <v>-14883.585191565269</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="233" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="233"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20181,14 +20196,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14447975422871187</v>
+        <v>0.14548210553708257</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="233" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="233"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20196,7 +20211,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23800.708351412046</v>
+        <v>-23750.704927137893</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20205,7 +20220,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-15069.248902318086</v>
+        <v>-14883.585191565269</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20214,7 +20229,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-38869.957253730128</v>
+        <v>-38634.29011870316</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20241,7 +20256,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-51269.957253730128</v>
+        <v>-51034.29011870316</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20259,7 +20274,7 @@
       </c>
       <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-10.16454346822564</v>
+        <v>-10.117821197205226</v>
       </c>
     </row>
   </sheetData>
@@ -20280,7 +20295,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D33819-10E3-B843-9B8A-30FFCAB234A7}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="82" customWidth="1"/>
@@ -20302,37 +20317,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="232" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20528,23 +20543,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8084.6635625799163</v>
+        <v>-8077.5890975485418</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5705.2652738071865</v>
+        <v>-5695.2848855921911</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4180.6981387497526</v>
+        <v>-4169.7328105604902</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-3991.0456902243664</v>
+        <v>-3977.0945963992685</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1839.0356860508248</v>
+        <v>-1831.0035370374044</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -20552,18 +20567,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="232" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="232"/>
+      <c r="E11" s="232"/>
+      <c r="F11" s="232"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="232"/>
+      <c r="I11" s="232"/>
+      <c r="J11" s="232"/>
+      <c r="K11" s="232"/>
+      <c r="L11" s="232"/>
       <c r="N11" s="90"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20757,18 +20772,18 @@
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="241" t="s">
+      <c r="C17" s="232" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="241"/>
+      <c r="D17" s="232"/>
+      <c r="E17" s="232"/>
+      <c r="F17" s="232"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="232"/>
+      <c r="I17" s="232"/>
+      <c r="J17" s="232"/>
+      <c r="K17" s="232"/>
+      <c r="L17" s="232"/>
       <c r="N17" s="90"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20902,18 +20917,18 @@
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="241" t="s">
+      <c r="C22" s="232" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="241"/>
-      <c r="E22" s="241"/>
-      <c r="F22" s="241"/>
-      <c r="G22" s="241"/>
-      <c r="H22" s="241"/>
-      <c r="I22" s="241"/>
-      <c r="J22" s="241"/>
-      <c r="K22" s="241"/>
-      <c r="L22" s="241"/>
+      <c r="D22" s="232"/>
+      <c r="E22" s="232"/>
+      <c r="F22" s="232"/>
+      <c r="G22" s="232"/>
+      <c r="H22" s="232"/>
+      <c r="I22" s="232"/>
+      <c r="J22" s="232"/>
+      <c r="K22" s="232"/>
+      <c r="L22" s="232"/>
       <c r="N22" s="90"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -20997,18 +21012,18 @@
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="241" t="s">
+      <c r="C27" s="232" t="s">
         <v>195</v>
       </c>
-      <c r="D27" s="241"/>
-      <c r="E27" s="241"/>
-      <c r="F27" s="241"/>
-      <c r="G27" s="241"/>
-      <c r="H27" s="241"/>
-      <c r="I27" s="241"/>
-      <c r="J27" s="241"/>
-      <c r="K27" s="241"/>
-      <c r="L27" s="241"/>
+      <c r="D27" s="232"/>
+      <c r="E27" s="232"/>
+      <c r="F27" s="232"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="232"/>
+      <c r="I27" s="232"/>
+      <c r="J27" s="232"/>
+      <c r="K27" s="232"/>
+      <c r="L27" s="232"/>
       <c r="N27" s="90"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21272,291 +21287,427 @@
       <c r="N35" s="90"/>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="C36" s="146">
+        <f>C33/C6</f>
+        <v>2.6985207025713711</v>
+      </c>
+      <c r="D36" s="146">
+        <f t="shared" ref="D36:G36" si="14">D33/D6</f>
+        <v>1.8519346908998637</v>
+      </c>
+      <c r="E36" s="146">
+        <f t="shared" si="14"/>
+        <v>4.242384008261415</v>
+      </c>
+      <c r="F36" s="146">
+        <f t="shared" si="14"/>
+        <v>2.0611664563755863</v>
+      </c>
+      <c r="G36" s="147">
+        <f t="shared" si="14"/>
+        <v>3.1151117249730382</v>
+      </c>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="136"/>
+      <c r="K36" s="136"/>
+      <c r="L36" s="136"/>
       <c r="N36" s="90"/>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="N37" s="90"/>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B38" s="232" t="s">
+      <c r="N38" s="90"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39" s="233" t="s">
         <v>200</v>
       </c>
-      <c r="C38" s="232"/>
-      <c r="N38" s="90"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="233"/>
+      <c r="N39" s="90"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C39" s="63">
+      <c r="C40" s="63">
         <f>L7</f>
         <v>12425.560115163004</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B40" s="1" t="s">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B41" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C40" s="134">
+      <c r="C41" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14447975422871187</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B41" s="39" t="s">
+        <v>0.14548210553708257</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42" s="39" t="s">
         <v>202</v>
       </c>
-      <c r="C41" s="104">
+      <c r="C42" s="104">
         <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B42" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C42" s="24">
-        <f>(C39*C41)</f>
-        <v>434894.60403070512</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C43" s="24">
+        <f>(C40*C42)</f>
+        <v>434894.60403070512</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C43" s="24">
-        <f ca="1">C42/(1+C40)^5</f>
-        <v>221484.5552321157</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B44" s="16" t="s">
+      <c r="C44" s="24">
+        <f ca="1">C43/(1+C41)^5</f>
+        <v>220517.20208867794</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="C44" s="93">
-        <f ca="1">SUM(H9:K9)+C43</f>
-        <v>199522.88256675447</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="93">
+        <f ca="1">SUM(H9:K9)+C44</f>
+        <v>198597.50069857744</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C45" s="87">
+      <c r="C46" s="87">
         <f>Statement!AC107</f>
         <v>38137</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B46" s="1" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B47" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C46" s="87">
+      <c r="C47" s="87">
         <f>Statement!AC108</f>
         <v>50537</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B47" s="16" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B48" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C47" s="107">
-        <f ca="1">C44+C45-C46</f>
-        <v>187122.88256675447</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="107">
+        <f ca="1">C45+C46-C47</f>
+        <v>186197.50069857744</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B49" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="87">
+      <c r="C49" s="87">
         <f>Statement!AC78</f>
         <v>5044</v>
       </c>
     </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B49" s="230" t="s">
+    <row r="50" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B50" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C49" s="231">
-        <f ca="1">C47/C48</f>
-        <v>37.098113117913257</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="C50" s="231">
+        <f ca="1">C48/C49</f>
+        <v>36.914651209075622</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B52" s="233" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="232"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="233"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B53" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C52" s="63">
+      <c r="C53" s="63">
         <f>L6</f>
         <v>95581.231655099982</v>
       </c>
     </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B53" s="1" t="s">
+    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B54" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C53" s="134">
+      <c r="C54" s="134">
         <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
         <v>0.12</v>
       </c>
     </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B54" s="39" t="s">
+    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B55" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="C54" s="104">
+      <c r="C55" s="104">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B55" s="1" t="s">
+    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B56" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C56" s="24">
         <f>L19</f>
         <v>5563.9177776000006</v>
       </c>
     </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B56" s="1" t="s">
+    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B57" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C56" s="24">
-        <f>(C52*C54)/C55</f>
+      <c r="C57" s="24">
+        <f>(C53*C55)/C56</f>
         <v>85.8938211127996</v>
       </c>
     </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B57" s="230" t="s">
+    <row r="58" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B58" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C57" s="231">
-        <f>C56/(1+C53)^5</f>
+      <c r="C58" s="231">
+        <f>C57/(1+C54)^5</f>
         <v>48.738460839691712</v>
       </c>
     </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B59" s="232" t="s">
+    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B60" s="233" t="s">
         <v>317</v>
       </c>
-      <c r="C59" s="232"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="1" t="s">
+      <c r="C60" s="233"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B61" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C60" s="63">
+      <c r="C61" s="63">
         <f>L8</f>
         <v>-3611.026943369634</v>
       </c>
     </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B61" s="1" t="s">
+    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B62" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C61" s="134">
+      <c r="C62" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14447975422871187</v>
-      </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B62" s="39" t="s">
+        <v>0.14548210553708257</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B63" s="39" t="s">
         <v>390</v>
       </c>
-      <c r="C62" s="104">
+      <c r="C63" s="104">
         <v>40</v>
-      </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B63" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C63" s="63">
-        <f>(C60*C62)-G31+G32</f>
-        <v>-145098.07773478536</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B64" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C64" s="63">
+        <f>(C61*C63)</f>
+        <v>-144441.07773478536</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C64" s="63">
-        <f ca="1">C63/(1+C61)^5</f>
-        <v>-73896.02656430038</v>
-      </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B65" s="16" t="s">
+      <c r="C65" s="63">
+        <f ca="1">C64/(1+C62)^5</f>
+        <v>-73240.141481496175</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B66" s="16" t="s">
         <v>411</v>
       </c>
-      <c r="C65" s="93">
-        <f ca="1">SUM(H9:K9)+C64</f>
-        <v>-95857.699229661608</v>
-      </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B66" s="1" t="s">
+      <c r="C66" s="93">
+        <f ca="1">SUM(H9:K9)+C65</f>
+        <v>-95159.842871596658</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C66" s="87">
+      <c r="C67" s="87">
         <f>Statement!AC107</f>
         <v>38137</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B67" s="1" t="s">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C67" s="87">
+      <c r="C68" s="87">
         <f>Statement!AC108</f>
         <v>50537</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B68" s="16" t="s">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B69" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C68" s="93">
-        <f ca="1">C65+C66-C67</f>
-        <v>-108257.69922966161</v>
-      </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="93">
+        <f ca="1">C66+C67-C68</f>
+        <v>-107559.84287159666</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C69" s="87">
+      <c r="C70" s="87">
         <f>Statement!AC78</f>
         <v>5044</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B70" s="230" t="s">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B71" s="230" t="s">
         <v>204</v>
       </c>
-      <c r="C70" s="231">
-        <f ca="1">C68/C69</f>
-        <v>-21.462668364326252</v>
+      <c r="C71" s="231">
+        <f ca="1">C69/C70</f>
+        <v>-21.324314605788395</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B73" s="233" t="s">
+        <v>414</v>
+      </c>
+      <c r="C73" s="233"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C74" s="63">
+        <f>L6</f>
+        <v>95581.231655099982</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="134">
+        <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
+        <v>0.14548210553708257</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B76" s="39" t="s">
+        <v>416</v>
+      </c>
+      <c r="C76" s="104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C77" s="63">
+        <f>(C74*C76)</f>
+        <v>477906.15827549994</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C78" s="63">
+        <f ca="1">C77/(1+C75)^5</f>
+        <v>242326.59570184379</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B79" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="C79" s="93">
+        <f ca="1">SUM(H9:K9)+C78</f>
+        <v>220406.89431174329</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C80" s="87">
+        <f>Statement!AC107</f>
+        <v>38137</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C81" s="87">
+        <f>Statement!AC108</f>
+        <v>50537</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B82" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C82" s="93">
+        <f ca="1">C79+C80-C81</f>
+        <v>208006.89431174329</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C83" s="87">
+        <f>Statement!AC78</f>
+        <v>5044</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B84" s="230" t="s">
+        <v>204</v>
+      </c>
+      <c r="C84" s="231">
+        <f ca="1">C82/C83</f>
+        <v>41.238480236269488</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
     <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="C22:L22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21567,7 +21718,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69906138-34BE-DB43-85EE-BFBB58F201B2}">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="82" customWidth="1"/>
@@ -21594,10 +21745,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="233" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="233"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21606,7 +21757,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.16454346822564</v>
+        <v>-10.117821197205226</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21614,8 +21765,8 @@
         <v>211</v>
       </c>
       <c r="C6" s="132">
-        <f ca="1">Multiples!C49</f>
-        <v>37.098113117913257</v>
+        <f ca="1">Multiples!C50</f>
+        <v>36.914651209075622</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21623,7 +21774,7 @@
         <v>212</v>
       </c>
       <c r="C7" s="132">
-        <f>Multiples!C57</f>
+        <f>Multiples!C58</f>
         <v>48.738460839691712</v>
       </c>
     </row>
@@ -21632,35 +21783,44 @@
         <v>318</v>
       </c>
       <c r="C8" s="132">
-        <f ca="1">Multiples!C70</f>
-        <v>-21.462668364326252</v>
+        <f ca="1">Multiples!C71</f>
+        <v>-21.324314605788395</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="230" t="s">
+      <c r="B9" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" s="132">
+        <f ca="1">Multiples!C84</f>
+        <v>41.238480236269488</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B10" s="230" t="s">
         <v>213</v>
       </c>
-      <c r="C9" s="231">
-        <f ca="1">AVERAGE(C5:C8)</f>
-        <v>13.552340531263269</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="231">
+        <f ca="1">AVERAGE(C5:C9)</f>
+        <v>19.089891296408641</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="132">
+      <c r="C11" s="132">
         <f ca="1">Overview!C5</f>
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B12" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C11" s="151">
-        <f ca="1">(C9-C10)/C10</f>
-        <v>-0.88981836966452632</v>
+      <c r="C12" s="151">
+        <f ca="1">(C10-C11)/C11</f>
+        <v>-0.84479763173651512</v>
       </c>
     </row>
   </sheetData>
@@ -21716,37 +21876,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="232" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="232"/>
+      <c r="E4" s="232"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
+      <c r="H4" s="232"/>
+      <c r="I4" s="232"/>
+      <c r="J4" s="232"/>
+      <c r="K4" s="232"/>
+      <c r="L4" s="232"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -21859,18 +22019,18 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="232" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="232"/>
+      <c r="E9" s="232"/>
+      <c r="F9" s="232"/>
+      <c r="G9" s="232"/>
+      <c r="H9" s="232"/>
+      <c r="I9" s="232"/>
+      <c r="J9" s="232"/>
+      <c r="K9" s="232"/>
+      <c r="L9" s="232"/>
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21991,18 +22151,18 @@
       <c r="N13" s="90"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="232" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
-      <c r="K14" s="241"/>
-      <c r="L14" s="241"/>
+      <c r="D14" s="232"/>
+      <c r="E14" s="232"/>
+      <c r="F14" s="232"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="232"/>
+      <c r="I14" s="232"/>
+      <c r="J14" s="232"/>
+      <c r="K14" s="232"/>
+      <c r="L14" s="232"/>
       <c r="N14" s="90"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22092,10 +22252,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="233" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="232"/>
+      <c r="C20" s="233"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22196,20 +22356,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="233" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="233"/>
+      <c r="E3" s="233"/>
+      <c r="F3" s="233"/>
+      <c r="G3" s="234"/>
+      <c r="H3" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="233"/>
+      <c r="J3" s="233"/>
+      <c r="K3" s="233"/>
+      <c r="L3" s="233"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22227,18 +22387,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="232" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
+      <c r="D5" s="232"/>
+      <c r="E5" s="232"/>
+      <c r="F5" s="232"/>
+      <c r="G5" s="232"/>
+      <c r="H5" s="232"/>
+      <c r="I5" s="232"/>
+      <c r="J5" s="232"/>
+      <c r="K5" s="232"/>
+      <c r="L5" s="232"/>
       <c r="P5" s="246"/>
       <c r="Q5" s="246"/>
       <c r="R5" s="246"/>
@@ -22384,7 +22544,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-473400.16236152302</v>
+        <v>-469618.64092390455</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22438,23 +22598,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6810.5637372254214</v>
+        <v>-6804.6041701228451</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9818.8107958231867</v>
+        <v>-9801.6344615339112</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-14155.809880644385</v>
+        <v>-14118.681368617328</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20408.474869705358</v>
+        <v>-20337.135033022507</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-29422.961315473349</v>
+        <v>-29294.453961595143</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22473,15 +22633,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-241094.79270533888</v>
+        <v>-238124.33584003564</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="247" t="s">
+      <c r="B14" s="248" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="248"/>
+      <c r="C14" s="249"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22498,7 +22658,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-66.239376150715813</v>
+        <v>-65.59889865878813</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22508,20 +22668,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="249" t="s">
+      <c r="E17" s="247" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="247"/>
+      <c r="H17" s="247"/>
+      <c r="I17" s="247"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="248" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="248"/>
+      <c r="C19" s="249"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22537,7 +22697,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14447975422871187</v>
+        <v>0.14548210553708257</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22587,10 +22747,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="247" t="s">
+      <c r="B28" s="248" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="248"/>
+      <c r="C28" s="249"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -22598,7 +22758,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-80616.620598871697</v>
+        <v>-80356.508994891745</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22607,7 +22767,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-241094.79270533888</v>
+        <v>-238124.33584003564</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22616,7 +22776,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-321711.41330421058</v>
+        <v>-318480.84483492735</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22643,7 +22803,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-334111.41330421058</v>
+        <v>-330880.84483492735</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22661,21 +22821,21 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-66.239376150715813</v>
+        <v>-65.59889865878813</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33611,15 +33771,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="233" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="233"/>
+      <c r="E4" s="233" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33756,14 +33916,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="233" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="233"/>
+      <c r="E15" s="233" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="233"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33814,14 +33974,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="233" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="233"/>
+      <c r="E21" s="233" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="233"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -33890,14 +34050,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="233" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="233"/>
+      <c r="E29" s="233" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="233"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -33973,14 +34133,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="233" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="233"/>
+      <c r="E37" s="233" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="233"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34049,14 +34209,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="233" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="233"/>
+      <c r="E45" s="233" t="s">
         <v>280</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="233"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34093,14 +34253,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="233" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="233"/>
+      <c r="E51" s="233" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="233"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36134,14 +36294,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="241" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="242"/>
+      <c r="F3" s="243" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="242"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36734,6 +36894,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36750,18 +36922,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EADBBD-276F-C94D-BCEF-3B3773E4AAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDDD59E-CFA0-7548-8F8C-76B8FEA2D600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" firstSheet="8" activeTab="18" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="419">
   <si>
     <t>Ticker</t>
   </si>
@@ -1408,6 +1408,9 @@
   </si>
   <si>
     <t>EV/Sales price</t>
+  </si>
+  <si>
+    <t>Reverse DCF rate</t>
   </si>
 </sst>
 </file>
@@ -2320,16 +2323,7 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2341,12 +2335,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2356,23 +2344,38 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13662,18 +13665,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="236" t="s">
+      <c r="B2" s="233" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="E2" s="236" t="s">
+      <c r="C2" s="234"/>
+      <c r="E2" s="233" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="237"/>
-      <c r="H2" s="236" t="s">
+      <c r="F2" s="234"/>
+      <c r="H2" s="233" t="s">
         <v>320</v>
       </c>
-      <c r="I2" s="237"/>
+      <c r="I2" s="234"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="180" t="s">
@@ -13786,13 +13789,13 @@
         <f ca="1">Statement!AC151</f>
         <v>10.544567085145182</v>
       </c>
-      <c r="H7" s="179" t="str">
-        <f>'AVG target price'!B10</f>
-        <v>AVG price</v>
-      </c>
-      <c r="I7" s="207">
-        <f ca="1">'AVG target price'!C10</f>
-        <v>19.089891296408641</v>
+      <c r="H7" s="180" t="str">
+        <f>'AVG target price'!B9</f>
+        <v>EV/Sales price</v>
+      </c>
+      <c r="I7" s="206">
+        <f ca="1">'AVG target price'!C9</f>
+        <v>41.238480236269488</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13811,12 +13814,12 @@
         <v>-1.8125052384544465E-2</v>
       </c>
       <c r="H8" s="179" t="str">
-        <f>'AVG target price'!B12</f>
-        <v>Upside/Downside</v>
-      </c>
-      <c r="I8" s="208">
-        <f ca="1">'AVG target price'!C12</f>
-        <v>-0.84479763173651512</v>
+        <f>'AVG target price'!B10</f>
+        <v>AVG price</v>
+      </c>
+      <c r="I8" s="207">
+        <f ca="1">'AVG target price'!C10</f>
+        <v>19.089891296408641</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13834,6 +13837,14 @@
         <f ca="1">Statement!AC162</f>
         <v>-1.7154471544715451E-2</v>
       </c>
+      <c r="H9" s="179" t="str">
+        <f>'AVG target price'!B12</f>
+        <v>Upside/Downside</v>
+      </c>
+      <c r="I9" s="208">
+        <f ca="1">'AVG target price'!C12</f>
+        <v>-0.84479763173651512</v>
+      </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="180" t="s">
@@ -13850,13 +13861,6 @@
         <f ca="1">Statement!AC164</f>
         <v>0</v>
       </c>
-      <c r="H10" s="179" t="s">
-        <v>401</v>
-      </c>
-      <c r="I10" s="207">
-        <f>DDM!C26</f>
-        <v>0</v>
-      </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="180" t="s">
@@ -13873,6 +13877,13 @@
         <f ca="1">Statement!AC163</f>
         <v>0</v>
       </c>
+      <c r="H11" s="179" t="s">
+        <v>401</v>
+      </c>
+      <c r="I11" s="207">
+        <f>DDM!C26</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="180" t="s">
@@ -13905,6 +13916,13 @@
         <f>Statement!AC125</f>
         <v>-0.12784720477028169</v>
       </c>
+      <c r="H13" s="179" t="s">
+        <v>418</v>
+      </c>
+      <c r="I13" s="208">
+        <f>'Reverse DCF'!C17</f>
+        <v>0.65</v>
+      </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="181" t="s">
@@ -13941,10 +13959,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="238" t="s">
+      <c r="B17" s="235" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="235"/>
       <c r="E17" s="179" t="s">
         <v>291</v>
       </c>
@@ -13967,7 +13985,6 @@
         <f>Statement!AC144</f>
         <v>64.755312947057305</v>
       </c>
-      <c r="I18" s="50"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="179" t="s">
@@ -13983,6 +14000,7 @@
         <f>Statement!AC146</f>
         <v>0.14164629549244934</v>
       </c>
+      <c r="I19" s="50"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="179" t="s">
@@ -14006,7 +14024,6 @@
       <c r="C21" s="68" t="s">
         <v>363</v>
       </c>
-      <c r="I21" s="50"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="179" t="s">
@@ -14015,16 +14032,17 @@
       <c r="C22" s="68" t="s">
         <v>340</v>
       </c>
+      <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="235" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="E25" s="236" t="s">
+      <c r="C25" s="235"/>
+      <c r="E25" s="233" t="s">
         <v>373</v>
       </c>
-      <c r="F25" s="237"/>
+      <c r="F25" s="234"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="179" t="s">
@@ -14073,15 +14091,15 @@
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33" s="233" t="s">
+      <c r="B33" s="131" t="s">
         <v>343</v>
       </c>
-      <c r="C33" s="233"/>
-      <c r="D33" s="233"/>
-      <c r="E33" s="233"/>
-      <c r="F33" s="233"/>
-      <c r="G33" s="233"/>
-      <c r="H33" s="233"/>
+      <c r="C33" s="131"/>
+      <c r="D33" s="131"/>
+      <c r="E33" s="131"/>
+      <c r="F33" s="131"/>
+      <c r="G33" s="131"/>
+      <c r="H33" s="131"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
@@ -14100,24 +14118,24 @@
       </c>
     </row>
     <row r="39" spans="2:8" ht="8" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
+      <c r="B39" s="131"/>
+      <c r="C39" s="131"/>
+      <c r="D39" s="131"/>
+      <c r="E39" s="131"/>
+      <c r="F39" s="131"/>
+      <c r="G39" s="131"/>
+      <c r="H39" s="131"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42" s="233" t="s">
+      <c r="B42" s="131" t="s">
         <v>346</v>
       </c>
-      <c r="C42" s="233"/>
-      <c r="D42" s="233"/>
-      <c r="E42" s="233"/>
-      <c r="F42" s="233"/>
-      <c r="G42" s="233"/>
-      <c r="H42" s="233"/>
+      <c r="C42" s="131"/>
+      <c r="D42" s="131"/>
+      <c r="E42" s="131"/>
+      <c r="F42" s="131"/>
+      <c r="G42" s="131"/>
+      <c r="H42" s="131"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="41" t="s">
@@ -14168,24 +14186,24 @@
       </c>
     </row>
     <row r="52" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B52" s="233"/>
-      <c r="C52" s="233"/>
-      <c r="D52" s="233"/>
-      <c r="E52" s="233"/>
-      <c r="F52" s="233"/>
-      <c r="G52" s="233"/>
-      <c r="H52" s="233"/>
+      <c r="B52" s="131"/>
+      <c r="C52" s="131"/>
+      <c r="D52" s="131"/>
+      <c r="E52" s="131"/>
+      <c r="F52" s="131"/>
+      <c r="G52" s="131"/>
+      <c r="H52" s="131"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B55" s="233" t="s">
+      <c r="B55" s="131" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="233"/>
-      <c r="D55" s="233"/>
-      <c r="E55" s="233"/>
-      <c r="F55" s="233"/>
-      <c r="G55" s="233"/>
-      <c r="H55" s="233"/>
+      <c r="C55" s="131"/>
+      <c r="D55" s="131"/>
+      <c r="E55" s="131"/>
+      <c r="F55" s="131"/>
+      <c r="G55" s="131"/>
+      <c r="H55" s="131"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" s="41" t="s">
@@ -14200,22 +14218,16 @@
       </c>
     </row>
     <row r="62" spans="2:8" ht="7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B62" s="233"/>
-      <c r="C62" s="233"/>
-      <c r="D62" s="233"/>
-      <c r="E62" s="233"/>
-      <c r="F62" s="233"/>
-      <c r="G62" s="233"/>
-      <c r="H62" s="233"/>
+      <c r="B62" s="131"/>
+      <c r="C62" s="131"/>
+      <c r="D62" s="131"/>
+      <c r="E62" s="131"/>
+      <c r="F62" s="131"/>
+      <c r="G62" s="131"/>
+      <c r="H62" s="131"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="B55:H55"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="B33:H33"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B42:H42"/>
-    <mergeCell ref="B52:H52"/>
+  <mergeCells count="6">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
@@ -14291,36 +14303,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="235" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="233" t="s">
+      <c r="S2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233"/>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
-      <c r="AA2" s="233" t="s">
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
+      <c r="AA2" s="232" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="233"/>
-      <c r="AC2" s="233"/>
+      <c r="AB2" s="232"/>
+      <c r="AC2" s="232"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14331,32 +14343,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="232"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="244" t="s">
+      <c r="S4" s="242" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="245"/>
-      <c r="U4" s="245"/>
-      <c r="V4" s="245"/>
-      <c r="W4" s="245"/>
-      <c r="X4" s="245"/>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
-      <c r="AA4" s="245"/>
-      <c r="AB4" s="245"/>
-      <c r="AC4" s="245"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
+      <c r="AA4" s="243"/>
+      <c r="AB4" s="243"/>
+      <c r="AC4" s="243"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15050,33 +15062,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="232" t="s">
+      <c r="C13" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="232"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="232"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="232"/>
-      <c r="K13" s="232"/>
-      <c r="L13" s="232"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="244" t="s">
+      <c r="S13" s="242" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="245"/>
-      <c r="U13" s="245"/>
-      <c r="V13" s="245"/>
-      <c r="W13" s="245"/>
-      <c r="X13" s="245"/>
-      <c r="Y13" s="245"/>
-      <c r="Z13" s="245"/>
-      <c r="AA13" s="245"/>
-      <c r="AB13" s="245"/>
-      <c r="AC13" s="245"/>
+      <c r="T13" s="243"/>
+      <c r="U13" s="243"/>
+      <c r="V13" s="243"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="243"/>
+      <c r="Y13" s="243"/>
+      <c r="Z13" s="243"/>
+      <c r="AA13" s="243"/>
+      <c r="AB13" s="243"/>
+      <c r="AC13" s="243"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15713,35 +15725,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="235" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="P2" s="233" t="s">
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
+      <c r="P2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
-      <c r="S2" s="233"/>
-      <c r="T2" s="233"/>
-      <c r="U2" s="233"/>
-      <c r="V2" s="233"/>
-      <c r="W2" s="233"/>
-      <c r="X2" s="233" t="s">
+      <c r="Q2" s="232"/>
+      <c r="R2" s="232"/>
+      <c r="S2" s="232"/>
+      <c r="T2" s="232"/>
+      <c r="U2" s="232"/>
+      <c r="V2" s="232"/>
+      <c r="W2" s="232"/>
+      <c r="X2" s="232" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="233"/>
-      <c r="Z2" s="233"/>
+      <c r="Y2" s="232"/>
+      <c r="Z2" s="232"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15750,31 +15762,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="232"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
-      <c r="P4" s="245" t="s">
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
+      <c r="P4" s="243" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="245"/>
-      <c r="R4" s="245"/>
-      <c r="S4" s="245"/>
-      <c r="T4" s="245"/>
-      <c r="U4" s="245"/>
-      <c r="V4" s="245"/>
-      <c r="W4" s="245"/>
-      <c r="X4" s="245"/>
-      <c r="Y4" s="245"/>
-      <c r="Z4" s="245"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15969,32 +15981,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="232" t="s">
+      <c r="C9" s="241" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="232"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="232"/>
-      <c r="J9" s="232"/>
-      <c r="K9" s="232"/>
-      <c r="L9" s="232"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="245" t="s">
+      <c r="P9" s="243" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="245"/>
-      <c r="R9" s="245"/>
-      <c r="S9" s="245"/>
-      <c r="T9" s="245"/>
-      <c r="U9" s="245"/>
-      <c r="V9" s="245"/>
-      <c r="W9" s="245"/>
-      <c r="X9" s="245"/>
-      <c r="Y9" s="245"/>
-      <c r="Z9" s="245"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
+      <c r="U9" s="243"/>
+      <c r="V9" s="243"/>
+      <c r="W9" s="243"/>
+      <c r="X9" s="243"/>
+      <c r="Y9" s="243"/>
+      <c r="Z9" s="243"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16564,31 +16576,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="232" t="s">
+      <c r="C18" s="241" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="232"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="232"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="232"/>
-      <c r="P18" s="245" t="s">
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
+      <c r="P18" s="243" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="245"/>
-      <c r="R18" s="245"/>
-      <c r="S18" s="245"/>
-      <c r="T18" s="245"/>
-      <c r="U18" s="245"/>
-      <c r="V18" s="245"/>
-      <c r="W18" s="245"/>
-      <c r="X18" s="245"/>
-      <c r="Y18" s="245"/>
-      <c r="Z18" s="245"/>
+      <c r="Q18" s="243"/>
+      <c r="R18" s="243"/>
+      <c r="S18" s="243"/>
+      <c r="T18" s="243"/>
+      <c r="U18" s="243"/>
+      <c r="V18" s="243"/>
+      <c r="W18" s="243"/>
+      <c r="X18" s="243"/>
+      <c r="Y18" s="243"/>
+      <c r="Z18" s="243"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17148,20 +17160,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="234"/>
-      <c r="H3" s="235" t="s">
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -17179,18 +17191,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="241" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
       <c r="P5" s="246"/>
       <c r="Q5" s="246"/>
       <c r="R5" s="246"/>
@@ -17387,18 +17399,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="241" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="232"/>
-      <c r="E11" s="232"/>
-      <c r="F11" s="232"/>
-      <c r="G11" s="232"/>
-      <c r="H11" s="232"/>
-      <c r="I11" s="232"/>
-      <c r="J11" s="232"/>
-      <c r="K11" s="232"/>
-      <c r="L11" s="232"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
       <c r="N11" s="90"/>
       <c r="P11" s="246"/>
       <c r="Q11" s="246"/>
@@ -17652,18 +17664,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="232" t="s">
+      <c r="C18" s="241" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="232"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="232"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="232"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17881,18 +17893,18 @@
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="232" t="s">
+      <c r="C26" s="241" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="232"/>
-      <c r="E26" s="232"/>
-      <c r="F26" s="232"/>
-      <c r="G26" s="232"/>
-      <c r="H26" s="232"/>
-      <c r="I26" s="232"/>
-      <c r="J26" s="232"/>
-      <c r="K26" s="232"/>
-      <c r="L26" s="232"/>
+      <c r="D26" s="241"/>
+      <c r="E26" s="241"/>
+      <c r="F26" s="241"/>
+      <c r="G26" s="241"/>
+      <c r="H26" s="241"/>
+      <c r="I26" s="241"/>
+      <c r="J26" s="241"/>
+      <c r="K26" s="241"/>
+      <c r="L26" s="241"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18084,18 +18096,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="232" t="s">
+      <c r="C33" s="241" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="232"/>
-      <c r="E33" s="232"/>
-      <c r="F33" s="232"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="232"/>
-      <c r="I33" s="232"/>
-      <c r="J33" s="232"/>
-      <c r="K33" s="232"/>
-      <c r="L33" s="232"/>
+      <c r="D33" s="241"/>
+      <c r="E33" s="241"/>
+      <c r="F33" s="241"/>
+      <c r="G33" s="241"/>
+      <c r="H33" s="241"/>
+      <c r="I33" s="241"/>
+      <c r="J33" s="241"/>
+      <c r="K33" s="241"/>
+      <c r="L33" s="241"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18279,18 +18291,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="232" t="s">
+      <c r="C40" s="241" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="232"/>
-      <c r="E40" s="232"/>
-      <c r="F40" s="232"/>
-      <c r="G40" s="232"/>
-      <c r="H40" s="232"/>
-      <c r="I40" s="232"/>
-      <c r="J40" s="232"/>
-      <c r="K40" s="232"/>
-      <c r="L40" s="232"/>
+      <c r="D40" s="241"/>
+      <c r="E40" s="241"/>
+      <c r="F40" s="241"/>
+      <c r="G40" s="241"/>
+      <c r="H40" s="241"/>
+      <c r="I40" s="241"/>
+      <c r="J40" s="241"/>
+      <c r="K40" s="241"/>
+      <c r="L40" s="241"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18554,12 +18566,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18567,6 +18573,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18604,20 +18616,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="235" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -18635,18 +18647,18 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="241" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="232"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
       <c r="S4" s="246"/>
       <c r="T4" s="246"/>
       <c r="U4" s="246"/>
@@ -19020,18 +19032,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="232" t="s">
+      <c r="C13" s="241" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="232"/>
-      <c r="E13" s="232"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="232"/>
-      <c r="I13" s="232"/>
-      <c r="J13" s="232"/>
-      <c r="K13" s="232"/>
-      <c r="L13" s="232"/>
+      <c r="D13" s="241"/>
+      <c r="E13" s="241"/>
+      <c r="F13" s="241"/>
+      <c r="G13" s="241"/>
+      <c r="H13" s="241"/>
+      <c r="I13" s="241"/>
+      <c r="J13" s="241"/>
+      <c r="K13" s="241"/>
+      <c r="L13" s="241"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19124,18 +19136,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="232" t="s">
+      <c r="C18" s="241" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="232"/>
-      <c r="E18" s="232"/>
-      <c r="F18" s="232"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="232"/>
-      <c r="I18" s="232"/>
-      <c r="J18" s="232"/>
-      <c r="K18" s="232"/>
-      <c r="L18" s="232"/>
+      <c r="D18" s="241"/>
+      <c r="E18" s="241"/>
+      <c r="F18" s="241"/>
+      <c r="G18" s="241"/>
+      <c r="H18" s="241"/>
+      <c r="I18" s="241"/>
+      <c r="J18" s="241"/>
+      <c r="K18" s="241"/>
+      <c r="L18" s="241"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19327,18 +19339,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="232" t="s">
+      <c r="C25" s="241" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="232"/>
-      <c r="E25" s="232"/>
-      <c r="F25" s="232"/>
-      <c r="G25" s="232"/>
-      <c r="H25" s="232"/>
-      <c r="I25" s="232"/>
-      <c r="J25" s="232"/>
-      <c r="K25" s="232"/>
-      <c r="L25" s="232"/>
+      <c r="D25" s="241"/>
+      <c r="E25" s="241"/>
+      <c r="F25" s="241"/>
+      <c r="G25" s="241"/>
+      <c r="H25" s="241"/>
+      <c r="I25" s="241"/>
+      <c r="J25" s="241"/>
+      <c r="K25" s="241"/>
+      <c r="L25" s="241"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19476,18 +19488,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="232" t="s">
+      <c r="C31" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="232"/>
-      <c r="E31" s="232"/>
-      <c r="F31" s="232"/>
-      <c r="G31" s="232"/>
-      <c r="H31" s="232"/>
-      <c r="I31" s="232"/>
-      <c r="J31" s="232"/>
-      <c r="K31" s="232"/>
-      <c r="L31" s="232"/>
+      <c r="D31" s="241"/>
+      <c r="E31" s="241"/>
+      <c r="F31" s="241"/>
+      <c r="G31" s="241"/>
+      <c r="H31" s="241"/>
+      <c r="I31" s="241"/>
+      <c r="J31" s="241"/>
+      <c r="K31" s="241"/>
+      <c r="L31" s="241"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19626,16 +19638,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19698,10 +19710,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="232" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="232"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19786,10 +19798,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="232" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="233"/>
+      <c r="C15" s="232"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19878,20 +19890,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="234"/>
-      <c r="H3" s="235" t="s">
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -19909,18 +19921,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="241" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
       <c r="P5" s="246"/>
       <c r="Q5" s="246"/>
       <c r="R5" s="246"/>
@@ -20177,10 +20189,10 @@
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="233" t="s">
+      <c r="B13" s="232" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="233"/>
+      <c r="C13" s="232"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20200,10 +20212,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="232" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="233"/>
+      <c r="C18" s="232"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20317,37 +20329,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="235" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="241" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="232"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20567,18 +20579,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="232" t="s">
+      <c r="C11" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="232"/>
-      <c r="E11" s="232"/>
-      <c r="F11" s="232"/>
-      <c r="G11" s="232"/>
-      <c r="H11" s="232"/>
-      <c r="I11" s="232"/>
-      <c r="J11" s="232"/>
-      <c r="K11" s="232"/>
-      <c r="L11" s="232"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="241"/>
+      <c r="J11" s="241"/>
+      <c r="K11" s="241"/>
+      <c r="L11" s="241"/>
       <c r="N11" s="90"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20772,18 +20784,18 @@
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="232" t="s">
+      <c r="C17" s="241" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="232"/>
-      <c r="E17" s="232"/>
-      <c r="F17" s="232"/>
-      <c r="G17" s="232"/>
-      <c r="H17" s="232"/>
-      <c r="I17" s="232"/>
-      <c r="J17" s="232"/>
-      <c r="K17" s="232"/>
-      <c r="L17" s="232"/>
+      <c r="D17" s="241"/>
+      <c r="E17" s="241"/>
+      <c r="F17" s="241"/>
+      <c r="G17" s="241"/>
+      <c r="H17" s="241"/>
+      <c r="I17" s="241"/>
+      <c r="J17" s="241"/>
+      <c r="K17" s="241"/>
+      <c r="L17" s="241"/>
       <c r="N17" s="90"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20917,18 +20929,18 @@
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="232" t="s">
+      <c r="C22" s="241" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="232"/>
-      <c r="E22" s="232"/>
-      <c r="F22" s="232"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="232"/>
-      <c r="I22" s="232"/>
-      <c r="J22" s="232"/>
-      <c r="K22" s="232"/>
-      <c r="L22" s="232"/>
+      <c r="D22" s="241"/>
+      <c r="E22" s="241"/>
+      <c r="F22" s="241"/>
+      <c r="G22" s="241"/>
+      <c r="H22" s="241"/>
+      <c r="I22" s="241"/>
+      <c r="J22" s="241"/>
+      <c r="K22" s="241"/>
+      <c r="L22" s="241"/>
       <c r="N22" s="90"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21012,18 +21024,18 @@
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="232" t="s">
+      <c r="C27" s="241" t="s">
         <v>195</v>
       </c>
-      <c r="D27" s="232"/>
-      <c r="E27" s="232"/>
-      <c r="F27" s="232"/>
-      <c r="G27" s="232"/>
-      <c r="H27" s="232"/>
-      <c r="I27" s="232"/>
-      <c r="J27" s="232"/>
-      <c r="K27" s="232"/>
-      <c r="L27" s="232"/>
+      <c r="D27" s="241"/>
+      <c r="E27" s="241"/>
+      <c r="F27" s="241"/>
+      <c r="G27" s="241"/>
+      <c r="H27" s="241"/>
+      <c r="I27" s="241"/>
+      <c r="J27" s="241"/>
+      <c r="K27" s="241"/>
+      <c r="L27" s="241"/>
       <c r="N27" s="90"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21324,10 +21336,10 @@
       <c r="N38" s="90"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="233" t="s">
+      <c r="B39" s="232" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="233"/>
+      <c r="C39" s="232"/>
       <c r="N39" s="90"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21429,10 +21441,10 @@
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="233" t="s">
+      <c r="B52" s="232" t="s">
         <v>205</v>
       </c>
-      <c r="C52" s="233"/>
+      <c r="C52" s="232"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21488,10 +21500,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="233" t="s">
+      <c r="B60" s="232" t="s">
         <v>317</v>
       </c>
-      <c r="C60" s="233"/>
+      <c r="C60" s="232"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21592,10 +21604,10 @@
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="233" t="s">
+      <c r="B73" s="232" t="s">
         <v>414</v>
       </c>
-      <c r="C73" s="233"/>
+      <c r="C73" s="232"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21697,17 +21709,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21745,10 +21757,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="232" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="233"/>
+      <c r="C4" s="232"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21876,37 +21888,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="233" t="s">
+      <c r="C2" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="233"/>
-      <c r="E2" s="233"/>
-      <c r="F2" s="233"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="235" t="s">
+      <c r="D2" s="232"/>
+      <c r="E2" s="232"/>
+      <c r="F2" s="232"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="233"/>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
+      <c r="I2" s="232"/>
+      <c r="J2" s="232"/>
+      <c r="K2" s="232"/>
+      <c r="L2" s="232"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="232" t="s">
+      <c r="C4" s="241" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="232"/>
-      <c r="E4" s="232"/>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
-      <c r="H4" s="232"/>
-      <c r="I4" s="232"/>
-      <c r="J4" s="232"/>
-      <c r="K4" s="232"/>
-      <c r="L4" s="232"/>
+      <c r="D4" s="241"/>
+      <c r="E4" s="241"/>
+      <c r="F4" s="241"/>
+      <c r="G4" s="241"/>
+      <c r="H4" s="241"/>
+      <c r="I4" s="241"/>
+      <c r="J4" s="241"/>
+      <c r="K4" s="241"/>
+      <c r="L4" s="241"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22019,18 +22031,18 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="232" t="s">
+      <c r="C9" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="232"/>
-      <c r="E9" s="232"/>
-      <c r="F9" s="232"/>
-      <c r="G9" s="232"/>
-      <c r="H9" s="232"/>
-      <c r="I9" s="232"/>
-      <c r="J9" s="232"/>
-      <c r="K9" s="232"/>
-      <c r="L9" s="232"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="241"/>
+      <c r="J9" s="241"/>
+      <c r="K9" s="241"/>
+      <c r="L9" s="241"/>
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22151,18 +22163,18 @@
       <c r="N13" s="90"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="232" t="s">
+      <c r="C14" s="241" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="232"/>
-      <c r="E14" s="232"/>
-      <c r="F14" s="232"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="232"/>
-      <c r="I14" s="232"/>
-      <c r="J14" s="232"/>
-      <c r="K14" s="232"/>
-      <c r="L14" s="232"/>
+      <c r="D14" s="241"/>
+      <c r="E14" s="241"/>
+      <c r="F14" s="241"/>
+      <c r="G14" s="241"/>
+      <c r="H14" s="241"/>
+      <c r="I14" s="241"/>
+      <c r="J14" s="241"/>
+      <c r="K14" s="241"/>
+      <c r="L14" s="241"/>
       <c r="N14" s="90"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22252,10 +22264,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="233" t="s">
+      <c r="B20" s="232" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="233"/>
+      <c r="C20" s="232"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22356,20 +22368,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="233" t="s">
+      <c r="C3" s="232" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="233"/>
-      <c r="E3" s="233"/>
-      <c r="F3" s="233"/>
-      <c r="G3" s="234"/>
-      <c r="H3" s="235" t="s">
+      <c r="D3" s="232"/>
+      <c r="E3" s="232"/>
+      <c r="F3" s="232"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="233"/>
-      <c r="J3" s="233"/>
-      <c r="K3" s="233"/>
-      <c r="L3" s="233"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="232"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22387,18 +22399,18 @@
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="232" t="s">
+      <c r="C5" s="241" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="232"/>
-      <c r="K5" s="232"/>
-      <c r="L5" s="232"/>
+      <c r="D5" s="241"/>
+      <c r="E5" s="241"/>
+      <c r="F5" s="241"/>
+      <c r="G5" s="241"/>
+      <c r="H5" s="241"/>
+      <c r="I5" s="241"/>
+      <c r="J5" s="241"/>
+      <c r="K5" s="241"/>
+      <c r="L5" s="241"/>
       <c r="P5" s="246"/>
       <c r="Q5" s="246"/>
       <c r="R5" s="246"/>
@@ -22638,10 +22650,10 @@
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="247" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="248"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22668,20 +22680,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="247" t="s">
+      <c r="E17" s="249" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="247" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="248"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22747,10 +22759,10 @@
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="248" t="s">
+      <c r="B28" s="247" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="248"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -22826,16 +22838,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33771,15 +33783,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="233" t="s">
+      <c r="B4" s="232" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="233"/>
-      <c r="E4" s="233" t="s">
+      <c r="C4" s="232"/>
+      <c r="E4" s="232" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="233"/>
-      <c r="G4" s="233"/>
+      <c r="F4" s="232"/>
+      <c r="G4" s="232"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33916,14 +33928,14 @@
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="233" t="s">
+      <c r="B15" s="232" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="233"/>
-      <c r="E15" s="233" t="s">
+      <c r="C15" s="232"/>
+      <c r="E15" s="232" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="233"/>
+      <c r="F15" s="232"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33974,14 +33986,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="232" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="233"/>
-      <c r="E21" s="233" t="s">
+      <c r="C21" s="232"/>
+      <c r="E21" s="232" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="233"/>
+      <c r="F21" s="232"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34050,14 +34062,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="233" t="s">
+      <c r="B29" s="232" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="233"/>
-      <c r="E29" s="233" t="s">
+      <c r="C29" s="232"/>
+      <c r="E29" s="232" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="233"/>
+      <c r="F29" s="232"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34133,14 +34145,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="233" t="s">
+      <c r="B37" s="232" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="E37" s="233" t="s">
+      <c r="C37" s="232"/>
+      <c r="E37" s="232" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="233"/>
+      <c r="F37" s="232"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34209,14 +34221,14 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="233" t="s">
+      <c r="B45" s="232" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="233"/>
-      <c r="E45" s="233" t="s">
+      <c r="C45" s="232"/>
+      <c r="E45" s="232" t="s">
         <v>280</v>
       </c>
-      <c r="F45" s="233"/>
+      <c r="F45" s="232"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34253,14 +34265,14 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="233" t="s">
+      <c r="B51" s="232" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="233"/>
-      <c r="E51" s="233" t="s">
+      <c r="C51" s="232"/>
+      <c r="E51" s="232" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="233"/>
+      <c r="F51" s="232"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -36294,14 +36306,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="236" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="237"/>
+      <c r="F3" s="238" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="237"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36894,18 +36906,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36922,6 +36922,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDDD59E-CFA0-7548-8F8C-76B8FEA2D600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980F10B2-5260-5B4C-A9CE-17F11B4A320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2323,9 +2323,6 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2335,6 +2332,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2342,12 +2348,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2368,14 +2368,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12802,12 +12802,12 @@
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
-    <v>31.21</v>
-    <v>2.2642000000000002</v>
-    <v>-4.3899999999999997</v>
-    <v>-3.4460999999999999E-2</v>
-    <v>-5.2200000000000003E-2</v>
-    <v>-4.2439999999999996E-4</v>
+    <v>32.89</v>
+    <v>2.3532999999999999</v>
+    <v>-3.14</v>
+    <v>-2.6314000000000001E-2</v>
+    <v>0.2177</v>
+    <v>1.874E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12815,25 +12815,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>126.93</v>
+    <v>118.0583</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46290.999997858591</v>
+    <v>46300.892228853903</v>
     <v>0</v>
-    <v>122.84</v>
-    <v>650063487000</v>
+    <v>115.31</v>
+    <v>614072167110</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>126.83</v>
+    <v>115.33499999999999</v>
     <v>0</v>
-    <v>127.39</v>
-    <v>123</v>
-    <v>122.9478</v>
+    <v>119.33</v>
+    <v>116.19</v>
+    <v>116.40770000000001</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>97728428</v>
-    <v>101957193</v>
+    <v>81014393</v>
+    <v>104373065</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -12855,19 +12855,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>52.3</v>
+    <v>53.42</v>
     <v>39.47</v>
-    <v>0.22</v>
-    <v>4.2620000000000002E-3</v>
+    <v>0.4</v>
+    <v>7.6380000000000007E-3</v>
     <v>US</v>
-    <v>52.3</v>
+    <v>52.98</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.62</v>
+    <v>51.57</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.86</v>
-    <v>51.62</v>
-    <v>51.84</v>
+    <v>52.16</v>
+    <v>52.37</v>
+    <v>52.77</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13089,9 +13089,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -13665,18 +13665,18 @@
   <sheetData>
     <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="233" t="s">
+      <c r="B2" s="232" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="234"/>
-      <c r="E2" s="233" t="s">
+      <c r="C2" s="233"/>
+      <c r="E2" s="232" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="234"/>
-      <c r="H2" s="233" t="s">
+      <c r="F2" s="233"/>
+      <c r="H2" s="232" t="s">
         <v>320</v>
       </c>
-      <c r="I2" s="234"/>
+      <c r="I2" s="233"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B3" s="180" t="s">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F3" s="182">
         <f ca="1">Statement!AC153</f>
-        <v>620412</v>
+        <v>586062.36</v>
       </c>
       <c r="H3" s="180" t="str">
         <f>'AVG target price'!B5</f>
@@ -13699,7 +13699,7 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.117821197205226</v>
+        <v>-9.9335819864773587</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="F4" s="183">
         <f ca="1">Statement!AC154</f>
-        <v>648413</v>
+        <v>614063.35999999999</v>
       </c>
       <c r="H4" s="180" t="str">
         <f>'AVG target price'!B6</f>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.914651209075622</v>
+        <v>36.173902272610633</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -13732,7 +13732,7 @@
       </c>
       <c r="C5" s="203" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
       <c r="E5" s="180" t="s">
         <v>238</v>
@@ -13756,14 +13756,14 @@
       </c>
       <c r="C6" s="203" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>122.9478</v>
+        <v>116.40770000000001</v>
       </c>
       <c r="E6" s="180" t="s">
         <v>232</v>
       </c>
       <c r="F6" s="185">
         <f ca="1">Statement!AC150</f>
-        <v>-58.293838862559234</v>
+        <v>-55.066350710900466</v>
       </c>
       <c r="H6" s="180" t="str">
         <f>'AVG target price'!B8</f>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.324314605788395</v>
+        <v>-21.033300890971983</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -13780,14 +13780,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-4.3899999999999997</v>
+        <v>-3.14</v>
       </c>
       <c r="E7" s="181" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="186">
         <f ca="1">Statement!AC151</f>
-        <v>10.544567085145182</v>
+        <v>9.9607581270164118</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="I7" s="206">
         <f ca="1">'AVG target price'!C9</f>
-        <v>41.238480236269488</v>
+        <v>40.421130260648567</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -13804,14 +13804,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-5.2200000000000003E-2</v>
+        <v>0.2177</v>
       </c>
       <c r="E8" s="180" t="s">
         <v>260</v>
       </c>
       <c r="F8" s="187">
         <f ca="1">Statement!AC161</f>
-        <v>-1.8125052384544465E-2</v>
+        <v>-1.9187377943876142E-2</v>
       </c>
       <c r="H8" s="179" t="str">
         <f>'AVG target price'!B10</f>
@@ -13819,7 +13819,7 @@
       </c>
       <c r="I8" s="207">
         <f ca="1">'AVG target price'!C10</f>
-        <v>19.089891296408641</v>
+        <v>18.873322099100314</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -13828,14 +13828,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.4460999999999999E-2</v>
+        <v>-2.6314000000000001E-2</v>
       </c>
       <c r="E9" s="180" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="187">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7154471544715451E-2</v>
+        <v>-1.8159910491436445E-2</v>
       </c>
       <c r="H9" s="179" t="str">
         <f>'AVG target price'!B12</f>
@@ -13843,7 +13843,7 @@
       </c>
       <c r="I9" s="208">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.84479763173651512</v>
+        <v>-0.8375650047413693</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-4.2439999999999996E-4</v>
+        <v>1.874E-3</v>
       </c>
       <c r="E10" s="180" t="s">
         <v>288</v>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="C12" s="204" cm="1">
         <f t="array" aca="1" ref="C12" ca="1">_FV(C3,"52 week low",TRUE)</f>
-        <v>31.21</v>
+        <v>32.89</v>
       </c>
       <c r="E12" s="180" t="s">
         <v>97</v>
@@ -13907,7 +13907,7 @@
       </c>
       <c r="C13" s="204" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.2642000000000002</v>
+        <v>2.3532999999999999</v>
       </c>
       <c r="E13" s="180" t="s">
         <v>99</v>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="C14" s="205" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>101957193</v>
+        <v>104373065</v>
       </c>
       <c r="E14" s="181" t="s">
         <v>100</v>
@@ -13946,7 +13946,7 @@
       </c>
       <c r="F15" s="187">
         <f ca="1">Statement!AC176</f>
-        <v>-1.9986718503188203E-2</v>
+        <v>-2.1158157981686455E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -13959,10 +13959,10 @@
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="234" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="235"/>
+      <c r="C17" s="234"/>
       <c r="E17" s="179" t="s">
         <v>291</v>
       </c>
@@ -14035,14 +14035,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="235" t="s">
+      <c r="B25" s="234" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="235"/>
-      <c r="E25" s="233" t="s">
+      <c r="C25" s="234"/>
+      <c r="E25" s="232" t="s">
         <v>373</v>
       </c>
-      <c r="F25" s="234"/>
+      <c r="F25" s="233"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="179" t="s">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.84</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14303,36 +14303,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="232" t="s">
+      <c r="S2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232"/>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
-      <c r="AA2" s="232" t="s">
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
+      <c r="AA2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="232"/>
-      <c r="AC2" s="232"/>
+      <c r="AB2" s="235"/>
+      <c r="AC2" s="235"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15725,35 +15725,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
-      <c r="P2" s="232" t="s">
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
+      <c r="P2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="232"/>
-      <c r="R2" s="232"/>
-      <c r="S2" s="232"/>
-      <c r="T2" s="232"/>
-      <c r="U2" s="232"/>
-      <c r="V2" s="232"/>
-      <c r="W2" s="232"/>
-      <c r="X2" s="232" t="s">
+      <c r="Q2" s="235"/>
+      <c r="R2" s="235"/>
+      <c r="S2" s="235"/>
+      <c r="T2" s="235"/>
+      <c r="U2" s="235"/>
+      <c r="V2" s="235"/>
+      <c r="W2" s="235"/>
+      <c r="X2" s="235" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="232"/>
-      <c r="Z2" s="232"/>
+      <c r="Y2" s="235"/>
+      <c r="Z2" s="235"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -17160,20 +17160,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -18566,6 +18566,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18573,12 +18579,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18616,20 +18616,20 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
       <c r="S2" s="246"/>
       <c r="T2" s="246"/>
       <c r="U2" s="246"/>
@@ -19638,16 +19638,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19710,10 +19710,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19730,7 +19730,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19739,7 +19739,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>620412</v>
+        <v>586062.36</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>5.1840000000000004E-2</v>
+        <v>5.2770000000000004E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.2642000000000002</v>
+        <v>2.3532999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19798,10 +19798,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="232"/>
+      <c r="C15" s="235"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19809,7 +19809,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.5321671244759289E-2</v>
+        <v>7.9385879370032664E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19818,7 +19818,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9246783287552407</v>
+        <v>0.92061412062996728</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.153729</v>
+        <v>0.15866849999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14548210553708257</v>
+        <v>0.14958449290250619</v>
       </c>
     </row>
   </sheetData>
@@ -19890,20 +19890,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -20096,7 +20096,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-29352.770791278683</v>
+        <v>-28423.520436261952</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20150,23 +20150,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8077.5890975485418</v>
+        <v>-8048.76355261343</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5695.2848855921911</v>
+        <v>-5654.7092232632258</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4169.7328105604902</v>
+        <v>-4125.2518135291557</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3977.0945963992685</v>
+        <v>-3920.6273943655701</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1831.0035370374044</v>
+        <v>-1798.5654427572829</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20185,14 +20185,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-14883.585191565269</v>
+        <v>-14157.070113263129</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="232" t="s">
+      <c r="B13" s="235" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="232"/>
+      <c r="C13" s="235"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20208,14 +20208,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14548210553708257</v>
+        <v>0.14958449290250619</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="232" t="s">
+      <c r="B18" s="235" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="232"/>
+      <c r="C18" s="235"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23750.704927137893</v>
+        <v>-23547.917426528667</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20232,7 +20232,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-14883.585191565269</v>
+        <v>-14157.070113263129</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-38634.29011870316</v>
+        <v>-37704.987539791793</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-51034.29011870316</v>
+        <v>-50104.987539791793</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-10.117821197205226</v>
+        <v>-9.9335819864773587</v>
       </c>
     </row>
   </sheetData>
@@ -20329,20 +20329,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -20555,23 +20555,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8077.5890975485418</v>
+        <v>-8048.76355261343</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5695.2848855921911</v>
+        <v>-5654.7092232632258</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4169.7328105604902</v>
+        <v>-4125.2518135291557</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-3977.0945963992685</v>
+        <v>-3920.6273943655701</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1831.0035370374044</v>
+        <v>-1798.5654427572829</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -21336,10 +21336,10 @@
       <c r="N38" s="90"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="232" t="s">
+      <c r="B39" s="235" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="232"/>
+      <c r="C39" s="235"/>
       <c r="N39" s="90"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21357,7 +21357,7 @@
       </c>
       <c r="C41" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14548210553708257</v>
+        <v>0.14958449290250619</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21383,7 +21383,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>220517.20208867794</v>
+        <v>216610.5150468194</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="C45" s="93">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>198597.50069857744</v>
+        <v>194861.16306304804</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21419,7 +21419,7 @@
       </c>
       <c r="C48" s="107">
         <f ca="1">C45+C46-C47</f>
-        <v>186197.50069857744</v>
+        <v>182461.16306304804</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21437,14 +21437,14 @@
       </c>
       <c r="C50" s="231">
         <f ca="1">C48/C49</f>
-        <v>36.914651209075622</v>
+        <v>36.173902272610633</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="232" t="s">
+      <c r="B52" s="235" t="s">
         <v>205</v>
       </c>
-      <c r="C52" s="232"/>
+      <c r="C52" s="235"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21500,10 +21500,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="232" t="s">
+      <c r="B60" s="235" t="s">
         <v>317</v>
       </c>
-      <c r="C60" s="232"/>
+      <c r="C60" s="235"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21520,7 +21520,7 @@
       </c>
       <c r="C62" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14548210553708257</v>
+        <v>0.14958449290250619</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="C65" s="63">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>-73240.141481496175</v>
+        <v>-71942.617710291306</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="C66" s="93">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>-95159.842871596658</v>
+        <v>-93691.969694062689</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C69" s="93">
         <f ca="1">C66+C67-C68</f>
-        <v>-107559.84287159666</v>
+        <v>-106091.96969406269</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21600,14 +21600,14 @@
       </c>
       <c r="C71" s="231">
         <f ca="1">C69/C70</f>
-        <v>-21.324314605788395</v>
+        <v>-21.033300890971983</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="232" t="s">
+      <c r="B73" s="235" t="s">
         <v>414</v>
       </c>
-      <c r="C73" s="232"/>
+      <c r="C73" s="235"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="C75" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14548210553708257</v>
+        <v>0.14958449290250619</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C78" s="63">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>242326.59570184379</v>
+        <v>238033.53301848276</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="C79" s="93">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>220406.89431174329</v>
+        <v>216284.18103471136</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C82" s="93">
         <f ca="1">C79+C80-C81</f>
-        <v>208006.89431174329</v>
+        <v>203884.18103471136</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21704,22 +21704,22 @@
       </c>
       <c r="C84" s="231">
         <f ca="1">C82/C83</f>
-        <v>41.238480236269488</v>
+        <v>40.421130260648567</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21757,10 +21757,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="232"/>
+      <c r="C4" s="235"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.117821197205226</v>
+        <v>-9.9335819864773587</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21778,7 +21778,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C50</f>
-        <v>36.914651209075622</v>
+        <v>36.173902272610633</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C71</f>
-        <v>-21.324314605788395</v>
+        <v>-21.033300890971983</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C9" s="132">
         <f ca="1">Multiples!C84</f>
-        <v>41.238480236269488</v>
+        <v>40.421130260648567</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21814,7 +21814,7 @@
       </c>
       <c r="C10" s="231">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>19.089891296408641</v>
+        <v>18.873322099100314</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="C11" s="132">
         <f ca="1">Overview!C5</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C12" s="151">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.84479763173651512</v>
+        <v>-0.8375650047413693</v>
       </c>
     </row>
   </sheetData>
@@ -21888,20 +21888,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="232" t="s">
+      <c r="C2" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="232"/>
-      <c r="E2" s="232"/>
-      <c r="F2" s="232"/>
+      <c r="D2" s="235"/>
+      <c r="E2" s="235"/>
+      <c r="F2" s="235"/>
       <c r="G2" s="244"/>
       <c r="H2" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="232"/>
-      <c r="J2" s="232"/>
-      <c r="K2" s="232"/>
-      <c r="L2" s="232"/>
+      <c r="I2" s="235"/>
+      <c r="J2" s="235"/>
+      <c r="K2" s="235"/>
+      <c r="L2" s="235"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -22264,10 +22264,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="232" t="s">
+      <c r="B20" s="235" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="232"/>
+      <c r="C20" s="235"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22368,20 +22368,20 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="232" t="s">
+      <c r="C3" s="235" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="232"/>
-      <c r="E3" s="232"/>
-      <c r="F3" s="232"/>
+      <c r="D3" s="235"/>
+      <c r="E3" s="235"/>
+      <c r="F3" s="235"/>
       <c r="G3" s="244"/>
       <c r="H3" s="245" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="232"/>
-      <c r="J3" s="232"/>
-      <c r="K3" s="232"/>
-      <c r="L3" s="232"/>
+      <c r="I3" s="235"/>
+      <c r="J3" s="235"/>
+      <c r="K3" s="235"/>
+      <c r="L3" s="235"/>
       <c r="P3" s="246"/>
       <c r="Q3" s="246"/>
       <c r="R3" s="246"/>
@@ -22556,7 +22556,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-469618.64092390455</v>
+        <v>-454751.44859292789</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22610,23 +22610,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6804.6041701228451</v>
+        <v>-6780.32137721239</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9801.6344615339112</v>
+        <v>-9731.8033963330709</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-14118.681368617328</v>
+        <v>-13968.069074598561</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20337.135033022507</v>
+        <v>-20048.386278156078</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-29294.453961595143</v>
+        <v>-28775.472845355227</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22645,15 +22645,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-238124.33584003564</v>
+        <v>-226500.7304874415</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="247" t="s">
+      <c r="B14" s="248" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="248"/>
+      <c r="C14" s="249"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22661,7 +22661,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-65.59889865878813</v>
+        <v>-63.08580163741015</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22680,20 +22680,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="249" t="s">
+      <c r="E17" s="247" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="249"/>
-      <c r="G17" s="249"/>
-      <c r="H17" s="249"/>
-      <c r="I17" s="249"/>
+      <c r="F17" s="247"/>
+      <c r="G17" s="247"/>
+      <c r="H17" s="247"/>
+      <c r="I17" s="247"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="247" t="s">
+      <c r="B19" s="248" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="248"/>
+      <c r="C19" s="249"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22709,7 +22709,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14548210553708257</v>
+        <v>0.14958449290250619</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22727,7 +22727,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>620412</v>
+        <v>586062.36</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22754,15 +22754,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>632812</v>
+        <v>598462.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="247" t="s">
+      <c r="B28" s="248" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="248"/>
+      <c r="C28" s="249"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-80356.508994891745</v>
+        <v>-79304.052971655328</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22779,7 +22779,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-238124.33584003564</v>
+        <v>-226500.7304874415</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22788,7 +22788,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-318480.84483492735</v>
+        <v>-305804.7834590968</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22815,7 +22815,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-330880.84483492735</v>
+        <v>-318204.7834590968</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22833,21 +22833,21 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-65.59889865878813</v>
+        <v>-63.08580163741015</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29506,7 +29506,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30883,7 +30883,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-58.293838862559234</v>
+        <v>-55.066350710900466</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30920,7 +30920,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>10.544567085145182</v>
+        <v>9.9607581270164118</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +30981,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>7.0870210870210872</v>
+        <v>6.6946421146421144</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31042,7 +31042,7 @@
       </c>
       <c r="AC153" s="140">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>620412</v>
+        <v>586062.36</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31103,7 +31103,7 @@
       </c>
       <c r="AC154" s="140">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>648413</v>
+        <v>614063.35999999999</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31140,7 +31140,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="178">
         <f ca="1">AC154/AC5</f>
-        <v>11.369283910786926</v>
+        <v>10.766996773741058</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31177,7 +31177,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="178">
         <f ca="1">AC154/AC12</f>
-        <v>-8420.9480519480512</v>
+        <v>-7974.8488311688307</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31274,8 +31274,8 @@
       <c r="Z158" s="49"/>
       <c r="AA158" s="49"/>
       <c r="AC158" s="63">
-        <f>AC109+AC53+AC110+AC55+AC57+AC58</f>
-        <v>-5633</v>
+        <f>AC109+AC53+AC110+AC55+AC57+AC58+AC56</f>
+        <v>-7711</v>
       </c>
     </row>
     <row r="159" spans="2:29" x14ac:dyDescent="0.2">
@@ -31312,7 +31312,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-55.172254335260114</v>
+        <v>-52.117595375722544</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31349,7 +31349,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-115.10971063376532</v>
+        <v>-79.63472441966023</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31386,7 +31386,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-1.8125052384544465E-2</v>
+        <v>-1.9187377943876142E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31423,7 +31423,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-1.7154471544715451E-2</v>
+        <v>-1.8159910491436445E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31534,7 +31534,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="151">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>2.5773195876288659E-3</v>
+        <v>2.728378597799729E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -31571,7 +31571,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="151">
         <f>AC158/AC5</f>
-        <v>-9.8769112077430221E-2</v>
+        <v>-0.13520479730677515</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -32037,7 +32037,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="151">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-1.9986718503188203E-2</v>
+        <v>-2.1158157981686455E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33783,15 +33783,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="232" t="s">
+      <c r="B4" s="235" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="232"/>
-      <c r="E4" s="232" t="s">
+      <c r="C4" s="235"/>
+      <c r="E4" s="235" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="232"/>
-      <c r="G4" s="232"/>
+      <c r="F4" s="235"/>
+      <c r="G4" s="235"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33799,7 +33799,7 @@
       </c>
       <c r="C5" s="167">
         <f ca="1">Overview!C5</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -33815,7 +33815,7 @@
       </c>
       <c r="C6" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>620412</v>
+        <v>586062.36</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33835,7 +33835,7 @@
       </c>
       <c r="C7" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>648413</v>
+        <v>614063.35999999999</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33855,7 +33855,7 @@
       </c>
       <c r="C8" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-58.293838862559234</v>
+        <v>-55.066350710900466</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>238</v>
@@ -33875,7 +33875,7 @@
       </c>
       <c r="C9" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>10.544567085145182</v>
+        <v>9.9607581270164118</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>239</v>
@@ -33895,7 +33895,7 @@
       </c>
       <c r="C10" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>7.0870210870210872</v>
+        <v>6.6946421146421144</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C11" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>11.369283910786926</v>
+        <v>10.766996773741058</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33924,18 +33924,18 @@
       </c>
       <c r="C12" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-8420.9480519480512</v>
+        <v>-7974.8488311688307</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="235" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="232"/>
-      <c r="E15" s="232" t="s">
+      <c r="C15" s="235"/>
+      <c r="E15" s="235" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="232"/>
+      <c r="F15" s="235"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33986,14 +33986,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="232" t="s">
+      <c r="B21" s="235" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="232"/>
-      <c r="E21" s="232" t="s">
+      <c r="C21" s="235"/>
+      <c r="E21" s="235" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="232"/>
+      <c r="F21" s="235"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34062,14 +34062,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="232" t="s">
+      <c r="B29" s="235" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="232"/>
-      <c r="E29" s="232" t="s">
+      <c r="C29" s="235"/>
+      <c r="E29" s="235" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="232"/>
+      <c r="F29" s="235"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34145,14 +34145,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="235" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="232"/>
-      <c r="E37" s="232" t="s">
+      <c r="C37" s="235"/>
+      <c r="E37" s="235" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="232"/>
+      <c r="F37" s="235"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="C38" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7154471544715451E-2</v>
+        <v>-1.8159910491436445E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>265</v>
@@ -34176,7 +34176,7 @@
       </c>
       <c r="C39" s="210">
         <f ca="1">Statement!AC161</f>
-        <v>-1.8125052384544465E-2</v>
+        <v>-1.9187377943876142E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>267</v>
@@ -34217,18 +34217,18 @@
       </c>
       <c r="C42" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>2.5773195876288659E-3</v>
+        <v>2.728378597799729E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="232" t="s">
+      <c r="B45" s="235" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="232"/>
-      <c r="E45" s="232" t="s">
+      <c r="C45" s="235"/>
+      <c r="E45" s="235" t="s">
         <v>280</v>
       </c>
-      <c r="F45" s="232"/>
+      <c r="F45" s="235"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34261,18 +34261,18 @@
       </c>
       <c r="F48" s="170">
         <f ca="1">Statement!AC176</f>
-        <v>-1.9986718503188203E-2</v>
+        <v>-2.1158157981686455E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="235" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="232"/>
-      <c r="E51" s="232" t="s">
+      <c r="C51" s="235"/>
+      <c r="E51" s="235" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="232"/>
+      <c r="F51" s="235"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="I6" s="167">
         <f ca="1">Statement!AC116</f>
-        <v>123</v>
+        <v>116.19</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="I7" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>620412</v>
+        <v>586062.36</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34498,7 +34498,7 @@
       </c>
       <c r="I8" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>648413</v>
+        <v>614063.35999999999</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34527,7 +34527,7 @@
       </c>
       <c r="I9" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-58.293838862559234</v>
+        <v>-55.066350710900466</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34556,7 +34556,7 @@
       </c>
       <c r="I10" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>10.544567085145182</v>
+        <v>9.9607581270164118</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34585,7 +34585,7 @@
       </c>
       <c r="I11" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>7.0870210870210872</v>
+        <v>6.6946421146421144</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34614,7 +34614,7 @@
       </c>
       <c r="I12" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>11.369283910786926</v>
+        <v>10.766996773741058</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="I13" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-8420.9480519480512</v>
+        <v>-7974.8488311688307</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35416,7 +35416,7 @@
       </c>
       <c r="I51" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-1.7154471544715451E-2</v>
+        <v>-1.8159910491436445E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="I52" s="170">
         <f ca="1">Statement!AC161</f>
-        <v>-1.8125052384544465E-2</v>
+        <v>-1.9187377943876142E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35532,7 +35532,7 @@
       </c>
       <c r="I55" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>2.5773195876288659E-3</v>
+        <v>2.728378597799729E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35768,7 +35768,7 @@
       </c>
       <c r="I68" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-1.9986718503188203E-2</v>
+        <v>-2.1158157981686455E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36306,14 +36306,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="236" t="s">
+      <c r="C3" s="238" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="237"/>
-      <c r="F3" s="238" t="s">
+      <c r="D3" s="239"/>
+      <c r="F3" s="240" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="237"/>
+      <c r="G3" s="239"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36380,19 +36380,19 @@
       <c r="B7" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="236">
         <f>Statement!AA89</f>
         <v>0.18789128673491934</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="237"/>
+      <c r="F7" s="236">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.25421883505715842</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="237"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
@@ -36419,19 +36419,19 @@
       <c r="B9" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="236">
         <f>Statement!AA90</f>
         <v>0.16877278250303768</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="237"/>
+      <c r="F9" s="236">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>3.2413867124610925E-2</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="237"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
@@ -36458,19 +36458,19 @@
       <c r="B11" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="236">
         <f>Statement!AA91</f>
         <v>0.21731812231157657</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="237"/>
+      <c r="F11" s="236">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.83766233766233766</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="237"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="202" t="s">
@@ -36497,19 +36497,19 @@
       <c r="B13" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="236">
         <f>Statement!AA95</f>
         <v>-0.44441824826122833</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="237"/>
+      <c r="F13" s="236">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-0.29845192021434952</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="237"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="202" t="s">
@@ -36536,19 +36536,19 @@
       <c r="B15" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="236">
         <f>Statement!AA96</f>
         <v>1.572704081632653</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="237"/>
+      <c r="F15" s="236">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5654911838790933</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="237"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="202" t="s">
@@ -36575,19 +36575,19 @@
       <c r="B17" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="236">
         <f>Statement!AA98</f>
         <v>-1.9594957081545064</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="237"/>
+      <c r="F17" s="236">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-2.781014393420151</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="237"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="202" t="s">
@@ -36614,22 +36614,22 @@
       <c r="B19" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="236">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.1314184536690932E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="237"/>
+      <c r="F19" s="236">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.16823071641107806</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="237"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="202" t="s">
@@ -36656,22 +36656,22 @@
       <c r="B21" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="236">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-1.9589041095890414</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="237"/>
+      <c r="F21" s="236">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.2238805970149254</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="237"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36719,22 +36719,22 @@
       <c r="B25" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="236">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14882878219231266</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="237"/>
+      <c r="F25" s="236">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.12781095159446068</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="237"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36761,22 +36761,22 @@
       <c r="B27" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="236">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.23950910530482977</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="237"/>
+      <c r="F27" s="236">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.58974358974358976</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="237"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36803,22 +36803,22 @@
       <c r="B29" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C29" s="239">
+      <c r="C29" s="236">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18467798732295171</v>
       </c>
-      <c r="D29" s="240"/>
-      <c r="F29" s="239">
+      <c r="D29" s="237"/>
+      <c r="F29" s="236">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28187976291278577</v>
       </c>
-      <c r="G29" s="240"/>
+      <c r="G29" s="237"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36845,22 +36845,22 @@
       <c r="B31" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C31" s="239">
+      <c r="C31" s="236">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>6.3456926766279287E-2</v>
       </c>
-      <c r="D31" s="240"/>
-      <c r="F31" s="239">
+      <c r="D31" s="237"/>
+      <c r="F31" s="236">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.30518451437627347</v>
       </c>
-      <c r="G31" s="240"/>
+      <c r="G31" s="237"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36887,25 +36887,37 @@
       <c r="B33" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C33" s="239">
+      <c r="C33" s="236">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.11624203821656051</v>
       </c>
-      <c r="D33" s="240"/>
-      <c r="F33" s="239">
+      <c r="D33" s="237"/>
+      <c r="F33" s="236">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33428300094966762</v>
       </c>
-      <c r="G33" s="240"/>
+      <c r="G33" s="237"/>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36922,18 +36934,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980F10B2-5260-5B4C-A9CE-17F11B4A320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8647F51-D805-9B42-9ED5-8A00C10CF4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="427">
   <si>
     <t>Ticker</t>
   </si>
@@ -1411,6 +1411,30 @@
   </si>
   <si>
     <t>Reverse DCF rate</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1427,7 +1451,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1593,6 +1617,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2010,11 +2042,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="250">
+  <cellXfs count="254">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2323,6 +2356,14 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2335,12 +2376,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2348,6 +2383,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2368,17 +2409,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -12803,11 +12845,11 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>32.89</v>
-    <v>2.3532999999999999</v>
-    <v>-3.14</v>
-    <v>-2.6314000000000001E-2</v>
-    <v>0.2177</v>
-    <v>1.874E-3</v>
+    <v>2.3353000000000002</v>
+    <v>-3.35</v>
+    <v>-3.1996000000000004E-2</v>
+    <v>0.21</v>
+    <v>2.0720000000000001E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12815,25 +12857,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>118.0583</v>
+    <v>103.19</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46300.892228853903</v>
+    <v>46307.860498553127</v>
     <v>0</v>
-    <v>115.31</v>
-    <v>614072167110</v>
+    <v>100.7103</v>
+    <v>535641743150</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>115.33499999999999</v>
+    <v>102.515</v>
     <v>0</v>
-    <v>119.33</v>
-    <v>116.19</v>
-    <v>116.40770000000001</v>
+    <v>104.7</v>
+    <v>101.35</v>
+    <v>101.56</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>81014393</v>
-    <v>104373065</v>
+    <v>72339596</v>
+    <v>108154739</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -12855,19 +12897,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13648,7 +13690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I62"/>
+  <dimension ref="B1:K62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -13660,25 +13702,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="232" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="236" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="233"/>
-      <c r="E2" s="232" t="s">
+      <c r="C2" s="237"/>
+      <c r="E2" s="236" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="233"/>
-      <c r="H2" s="232" t="s">
+      <c r="F2" s="237"/>
+      <c r="H2" s="236" t="s">
         <v>320</v>
       </c>
-      <c r="I2" s="233"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="237"/>
+      <c r="K2" s="131" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="180" t="s">
         <v>11</v>
       </c>
@@ -13691,7 +13738,7 @@
       </c>
       <c r="F3" s="182">
         <f ca="1">Statement!AC153</f>
-        <v>586062.36</v>
+        <v>511209.39999999997</v>
       </c>
       <c r="H3" s="180" t="str">
         <f>'AVG target price'!B5</f>
@@ -13699,10 +13746,13 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-9.9335819864773587</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-10.033175639822971</v>
+      </c>
+      <c r="K3" s="234" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="180" t="s">
         <v>0</v>
       </c>
@@ -13715,7 +13765,7 @@
       </c>
       <c r="F4" s="183">
         <f ca="1">Statement!AC154</f>
-        <v>614063.35999999999</v>
+        <v>539210.39999999991</v>
       </c>
       <c r="H4" s="180" t="str">
         <f>'AVG target price'!B6</f>
@@ -13723,16 +13773,19 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.173902272610633</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>36.577790878205242</v>
+      </c>
+      <c r="K4" s="234" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="180" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="203" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
       <c r="E5" s="180" t="s">
         <v>238</v>
@@ -13749,21 +13802,24 @@
         <f>'AVG target price'!C7</f>
         <v>48.738460839691712</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="234" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="180" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="203" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>116.40770000000001</v>
+        <v>101.56</v>
       </c>
       <c r="E6" s="180" t="s">
         <v>232</v>
       </c>
       <c r="F6" s="185">
         <f ca="1">Statement!AC150</f>
-        <v>-55.066350710900466</v>
+        <v>-48.033175355450226</v>
       </c>
       <c r="H6" s="180" t="str">
         <f>'AVG target price'!B8</f>
@@ -13771,23 +13827,26 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.033300890971983</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-21.192021040088761</v>
+      </c>
+      <c r="K6" s="235" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="180" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.14</v>
+        <v>-3.35</v>
       </c>
       <c r="E7" s="181" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="186">
         <f ca="1">Statement!AC151</f>
-        <v>9.9607581270164118</v>
+        <v>8.6885518217842606</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13795,23 +13854,23 @@
       </c>
       <c r="I7" s="206">
         <f ca="1">'AVG target price'!C9</f>
-        <v>40.421130260648567</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>40.866788565112962</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="180" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.2177</v>
+        <v>0.21</v>
       </c>
       <c r="E8" s="180" t="s">
         <v>260</v>
       </c>
       <c r="F8" s="187">
         <f ca="1">Statement!AC161</f>
-        <v>-1.9187377943876142E-2</v>
+        <v>-2.1996856865308032E-2</v>
       </c>
       <c r="H8" s="179" t="str">
         <f>'AVG target price'!B10</f>
@@ -13819,23 +13878,23 @@
       </c>
       <c r="I8" s="207">
         <f ca="1">'AVG target price'!C10</f>
-        <v>18.873322099100314</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>18.991568720619636</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="180" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-2.6314000000000001E-2</v>
+        <v>-3.1996000000000004E-2</v>
       </c>
       <c r="E9" s="180" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="187">
         <f ca="1">Statement!AC162</f>
-        <v>-1.8159910491436445E-2</v>
+        <v>-2.0818944252590038E-2</v>
       </c>
       <c r="H9" s="179" t="str">
         <f>'AVG target price'!B12</f>
@@ -13843,16 +13902,16 @@
       </c>
       <c r="I9" s="208">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.8375650047413693</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-0.81261402347686595</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="180" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="72" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.874E-3</v>
+        <v>2.0720000000000001E-3</v>
       </c>
       <c r="E10" s="180" t="s">
         <v>288</v>
@@ -13862,7 +13921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="180" t="s">
         <v>7</v>
       </c>
@@ -13885,7 +13944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="180" t="s">
         <v>8</v>
       </c>
@@ -13901,13 +13960,13 @@
         <v>-5.5285789793468654E-2</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="180" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="204" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3532999999999999</v>
+        <v>2.3353000000000002</v>
       </c>
       <c r="E13" s="180" t="s">
         <v>99</v>
@@ -13924,13 +13983,13 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="181" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="205" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>104373065</v>
+        <v>108154739</v>
       </c>
       <c r="E14" s="181" t="s">
         <v>100</v>
@@ -13940,16 +13999,16 @@
         <v>-6.6641856278614885E-4</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="180" t="s">
         <v>285</v>
       </c>
       <c r="F15" s="187">
         <f ca="1">Statement!AC176</f>
-        <v>-2.1158157981686455E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>-2.425620499153576E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="181" t="s">
         <v>290</v>
       </c>
@@ -13957,12 +14016,16 @@
         <f>Statement!AC175</f>
         <v>-2.4583663758921492</v>
       </c>
+      <c r="H16" s="236" t="s">
+        <v>419</v>
+      </c>
+      <c r="I16" s="237"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="234" t="s">
+      <c r="B17" s="238" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="234"/>
+      <c r="C17" s="238"/>
       <c r="E17" s="179" t="s">
         <v>291</v>
       </c>
@@ -13970,6 +14033,13 @@
         <f>Statement!AC171</f>
         <v>5.947660586835844E-4</v>
       </c>
+      <c r="H17" s="180" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="232">
+        <f ca="1">DCF!C15</f>
+        <v>0.14733660393355438</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="179" t="s">
@@ -13985,6 +14055,13 @@
         <f>Statement!AC144</f>
         <v>64.755312947057305</v>
       </c>
+      <c r="H18" s="181" t="s">
+        <v>420</v>
+      </c>
+      <c r="I18" s="233">
+        <f>Multiples!C54</f>
+        <v>0.12</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="179" t="s">
@@ -14035,14 +14112,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="234" t="s">
+      <c r="B25" s="238" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="234"/>
-      <c r="E25" s="232" t="s">
+      <c r="C25" s="238"/>
+      <c r="E25" s="236" t="s">
         <v>373</v>
       </c>
-      <c r="F25" s="233"/>
+      <c r="F25" s="237"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="179" t="s">
@@ -14056,7 +14133,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14071,7 +14148,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14227,13 +14304,14 @@
       <c r="H62" s="131"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -14246,6 +14324,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{E99C3821-C030-2047-B823-2BDDC88F64EA}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{30EA2D1C-66CA-594E-B123-2EEEF5B0DBA8}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{0BF96B4B-5FDB-1542-8DC8-5FA5787C0496}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{4DC801DF-81C6-624C-853F-E4066817BC6D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14255,18 +14339,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="131" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="234" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="234" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="234" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="234" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="235" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{2FAE08F3-3629-4F42-8CB8-5D64CA33BE2D}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{E720CD94-30E1-DC44-99B8-36930AA2606E}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{80B04D5C-387D-CD4C-A15B-C920D4AEEB39}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{19D37859-49D9-C84F-8095-3F93F53DF271}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{8D9E2D0E-8CBA-914C-BEC1-B8FF8649557A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14303,36 +14426,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="235" t="s">
+      <c r="S2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235"/>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
-      <c r="AA2" s="235" t="s">
+      <c r="T2" s="239"/>
+      <c r="U2" s="239"/>
+      <c r="V2" s="239"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="239"/>
+      <c r="Y2" s="239"/>
+      <c r="Z2" s="239"/>
+      <c r="AA2" s="239" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="235"/>
-      <c r="AC2" s="235"/>
+      <c r="AB2" s="239"/>
+      <c r="AC2" s="239"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14343,32 +14466,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="242" t="s">
+      <c r="S4" s="246" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
-      <c r="AA4" s="243"/>
-      <c r="AB4" s="243"/>
-      <c r="AC4" s="243"/>
+      <c r="T4" s="247"/>
+      <c r="U4" s="247"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="247"/>
+      <c r="X4" s="247"/>
+      <c r="Y4" s="247"/>
+      <c r="Z4" s="247"/>
+      <c r="AA4" s="247"/>
+      <c r="AB4" s="247"/>
+      <c r="AC4" s="247"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15062,33 +15185,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="242" t="s">
+      <c r="S13" s="246" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="243"/>
-      <c r="U13" s="243"/>
-      <c r="V13" s="243"/>
-      <c r="W13" s="243"/>
-      <c r="X13" s="243"/>
-      <c r="Y13" s="243"/>
-      <c r="Z13" s="243"/>
-      <c r="AA13" s="243"/>
-      <c r="AB13" s="243"/>
-      <c r="AC13" s="243"/>
+      <c r="T13" s="247"/>
+      <c r="U13" s="247"/>
+      <c r="V13" s="247"/>
+      <c r="W13" s="247"/>
+      <c r="X13" s="247"/>
+      <c r="Y13" s="247"/>
+      <c r="Z13" s="247"/>
+      <c r="AA13" s="247"/>
+      <c r="AB13" s="247"/>
+      <c r="AC13" s="247"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15725,35 +15848,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="P2" s="235" t="s">
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
+      <c r="P2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="235"/>
-      <c r="R2" s="235"/>
-      <c r="S2" s="235"/>
-      <c r="T2" s="235"/>
-      <c r="U2" s="235"/>
-      <c r="V2" s="235"/>
-      <c r="W2" s="235"/>
-      <c r="X2" s="235" t="s">
+      <c r="Q2" s="239"/>
+      <c r="R2" s="239"/>
+      <c r="S2" s="239"/>
+      <c r="T2" s="239"/>
+      <c r="U2" s="239"/>
+      <c r="V2" s="239"/>
+      <c r="W2" s="239"/>
+      <c r="X2" s="239" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="235"/>
-      <c r="Z2" s="235"/>
+      <c r="Y2" s="239"/>
+      <c r="Z2" s="239"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15762,31 +15885,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="P4" s="243" t="s">
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="P4" s="247" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="243"/>
-      <c r="R4" s="243"/>
-      <c r="S4" s="243"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="243"/>
-      <c r="V4" s="243"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="243"/>
-      <c r="Y4" s="243"/>
-      <c r="Z4" s="243"/>
+      <c r="Q4" s="247"/>
+      <c r="R4" s="247"/>
+      <c r="S4" s="247"/>
+      <c r="T4" s="247"/>
+      <c r="U4" s="247"/>
+      <c r="V4" s="247"/>
+      <c r="W4" s="247"/>
+      <c r="X4" s="247"/>
+      <c r="Y4" s="247"/>
+      <c r="Z4" s="247"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -15981,32 +16104,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="245" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="243" t="s">
+      <c r="P9" s="247" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="243"/>
-      <c r="S9" s="243"/>
-      <c r="T9" s="243"/>
-      <c r="U9" s="243"/>
-      <c r="V9" s="243"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
+      <c r="Q9" s="247"/>
+      <c r="R9" s="247"/>
+      <c r="S9" s="247"/>
+      <c r="T9" s="247"/>
+      <c r="U9" s="247"/>
+      <c r="V9" s="247"/>
+      <c r="W9" s="247"/>
+      <c r="X9" s="247"/>
+      <c r="Y9" s="247"/>
+      <c r="Z9" s="247"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16576,31 +16699,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="245" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
-      <c r="P18" s="243" t="s">
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
+      <c r="P18" s="247" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="243"/>
-      <c r="R18" s="243"/>
-      <c r="S18" s="243"/>
-      <c r="T18" s="243"/>
-      <c r="U18" s="243"/>
-      <c r="V18" s="243"/>
-      <c r="W18" s="243"/>
-      <c r="X18" s="243"/>
-      <c r="Y18" s="243"/>
-      <c r="Z18" s="243"/>
+      <c r="Q18" s="247"/>
+      <c r="R18" s="247"/>
+      <c r="S18" s="247"/>
+      <c r="T18" s="247"/>
+      <c r="U18" s="247"/>
+      <c r="V18" s="247"/>
+      <c r="W18" s="247"/>
+      <c r="X18" s="247"/>
+      <c r="Y18" s="247"/>
+      <c r="Z18" s="247"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17160,60 +17283,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="248"/>
+      <c r="H3" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="239"/>
+      <c r="J3" s="239"/>
+      <c r="K3" s="239"/>
+      <c r="L3" s="239"/>
+      <c r="P3" s="250"/>
+      <c r="Q3" s="250"/>
+      <c r="R3" s="250"/>
+      <c r="S3" s="250"/>
+      <c r="T3" s="250"/>
+      <c r="U3" s="250"/>
+      <c r="V3" s="250"/>
+      <c r="W3" s="250"/>
+      <c r="X3" s="250"/>
+      <c r="Y3" s="250"/>
+      <c r="Z3" s="250"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="245" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="250"/>
+      <c r="Q5" s="250"/>
+      <c r="R5" s="250"/>
+      <c r="S5" s="250"/>
+      <c r="T5" s="250"/>
+      <c r="U5" s="250"/>
+      <c r="V5" s="250"/>
+      <c r="W5" s="250"/>
+      <c r="X5" s="250"/>
+      <c r="Y5" s="250"/>
+      <c r="Z5" s="250"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17399,30 +17522,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="245" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="246"/>
-      <c r="Q11" s="246"/>
-      <c r="R11" s="246"/>
-      <c r="S11" s="246"/>
-      <c r="T11" s="246"/>
-      <c r="U11" s="246"/>
-      <c r="V11" s="246"/>
-      <c r="W11" s="246"/>
-      <c r="X11" s="246"/>
-      <c r="Y11" s="246"/>
-      <c r="Z11" s="246"/>
+      <c r="P11" s="250"/>
+      <c r="Q11" s="250"/>
+      <c r="R11" s="250"/>
+      <c r="S11" s="250"/>
+      <c r="T11" s="250"/>
+      <c r="U11" s="250"/>
+      <c r="V11" s="250"/>
+      <c r="W11" s="250"/>
+      <c r="X11" s="250"/>
+      <c r="Y11" s="250"/>
+      <c r="Z11" s="250"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17664,18 +17787,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="245" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17888,23 +18011,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="246"/>
-      <c r="C25" s="246"/>
+      <c r="B25" s="250"/>
+      <c r="C25" s="250"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="241" t="s">
+      <c r="C26" s="245" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="241"/>
-      <c r="E26" s="241"/>
-      <c r="F26" s="241"/>
-      <c r="G26" s="241"/>
-      <c r="H26" s="241"/>
-      <c r="I26" s="241"/>
-      <c r="J26" s="241"/>
-      <c r="K26" s="241"/>
-      <c r="L26" s="241"/>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="245"/>
+      <c r="G26" s="245"/>
+      <c r="H26" s="245"/>
+      <c r="I26" s="245"/>
+      <c r="J26" s="245"/>
+      <c r="K26" s="245"/>
+      <c r="L26" s="245"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18096,18 +18219,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="241" t="s">
+      <c r="C33" s="245" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="241"/>
-      <c r="E33" s="241"/>
-      <c r="F33" s="241"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="241"/>
-      <c r="I33" s="241"/>
-      <c r="J33" s="241"/>
-      <c r="K33" s="241"/>
-      <c r="L33" s="241"/>
+      <c r="D33" s="245"/>
+      <c r="E33" s="245"/>
+      <c r="F33" s="245"/>
+      <c r="G33" s="245"/>
+      <c r="H33" s="245"/>
+      <c r="I33" s="245"/>
+      <c r="J33" s="245"/>
+      <c r="K33" s="245"/>
+      <c r="L33" s="245"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18291,18 +18414,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="241" t="s">
+      <c r="C40" s="245" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="241"/>
-      <c r="E40" s="241"/>
-      <c r="F40" s="241"/>
-      <c r="G40" s="241"/>
-      <c r="H40" s="241"/>
-      <c r="I40" s="241"/>
-      <c r="J40" s="241"/>
-      <c r="K40" s="241"/>
-      <c r="L40" s="241"/>
+      <c r="D40" s="245"/>
+      <c r="E40" s="245"/>
+      <c r="F40" s="245"/>
+      <c r="G40" s="245"/>
+      <c r="H40" s="245"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18566,12 +18689,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18579,6 +18696,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18616,60 +18739,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
-      <c r="S2" s="246"/>
-      <c r="T2" s="246"/>
-      <c r="U2" s="246"/>
-      <c r="V2" s="246"/>
-      <c r="W2" s="246"/>
-      <c r="X2" s="246"/>
-      <c r="Y2" s="246"/>
-      <c r="Z2" s="246"/>
-      <c r="AA2" s="246"/>
-      <c r="AB2" s="246"/>
-      <c r="AC2" s="246"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
+      <c r="S2" s="250"/>
+      <c r="T2" s="250"/>
+      <c r="U2" s="250"/>
+      <c r="V2" s="250"/>
+      <c r="W2" s="250"/>
+      <c r="X2" s="250"/>
+      <c r="Y2" s="250"/>
+      <c r="Z2" s="250"/>
+      <c r="AA2" s="250"/>
+      <c r="AB2" s="250"/>
+      <c r="AC2" s="250"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="245" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="S4" s="250"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
+      <c r="AA4" s="250"/>
+      <c r="AB4" s="250"/>
+      <c r="AC4" s="250"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19032,18 +19155,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="241" t="s">
+      <c r="C13" s="245" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="241"/>
-      <c r="E13" s="241"/>
-      <c r="F13" s="241"/>
-      <c r="G13" s="241"/>
-      <c r="H13" s="241"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="241"/>
-      <c r="K13" s="241"/>
-      <c r="L13" s="241"/>
+      <c r="D13" s="245"/>
+      <c r="E13" s="245"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="245"/>
+      <c r="J13" s="245"/>
+      <c r="K13" s="245"/>
+      <c r="L13" s="245"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19136,18 +19259,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="241" t="s">
+      <c r="C18" s="245" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
-      <c r="K18" s="241"/>
-      <c r="L18" s="241"/>
+      <c r="D18" s="245"/>
+      <c r="E18" s="245"/>
+      <c r="F18" s="245"/>
+      <c r="G18" s="245"/>
+      <c r="H18" s="245"/>
+      <c r="I18" s="245"/>
+      <c r="J18" s="245"/>
+      <c r="K18" s="245"/>
+      <c r="L18" s="245"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19339,18 +19462,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="241" t="s">
+      <c r="C25" s="245" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="241"/>
-      <c r="E25" s="241"/>
-      <c r="F25" s="241"/>
-      <c r="G25" s="241"/>
-      <c r="H25" s="241"/>
-      <c r="I25" s="241"/>
-      <c r="J25" s="241"/>
-      <c r="K25" s="241"/>
-      <c r="L25" s="241"/>
+      <c r="D25" s="245"/>
+      <c r="E25" s="245"/>
+      <c r="F25" s="245"/>
+      <c r="G25" s="245"/>
+      <c r="H25" s="245"/>
+      <c r="I25" s="245"/>
+      <c r="J25" s="245"/>
+      <c r="K25" s="245"/>
+      <c r="L25" s="245"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19488,18 +19611,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="241" t="s">
+      <c r="C31" s="245" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="241"/>
-      <c r="E31" s="241"/>
-      <c r="F31" s="241"/>
-      <c r="G31" s="241"/>
-      <c r="H31" s="241"/>
-      <c r="I31" s="241"/>
-      <c r="J31" s="241"/>
-      <c r="K31" s="241"/>
-      <c r="L31" s="241"/>
+      <c r="D31" s="245"/>
+      <c r="E31" s="245"/>
+      <c r="F31" s="245"/>
+      <c r="G31" s="245"/>
+      <c r="H31" s="245"/>
+      <c r="I31" s="245"/>
+      <c r="J31" s="245"/>
+      <c r="K31" s="245"/>
+      <c r="L31" s="245"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19638,16 +19761,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19661,18 +19784,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="131" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="234" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="234" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="234" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="234" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="235" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>159</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{31C97374-02FF-8649-AFBE-77050005C08A}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{69356680-499D-B149-B169-0DDFF228A9F2}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{FA7D09B3-DDFB-9C4A-A884-72B097E683E0}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{ADA71856-205A-8446-886B-3A2A502B4298}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{E8D8A197-2855-034F-827F-59357C007C31}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -19710,10 +19872,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="239" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="239"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19730,7 +19892,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19739,7 +19901,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>586062.36</v>
+        <v>511209.39999999997</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19757,7 +19919,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19766,7 +19928,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.3532999999999999</v>
+        <v>2.3353000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19798,10 +19960,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="239" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="235"/>
+      <c r="C15" s="239"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -19809,7 +19971,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.9385879370032664E-2</v>
+        <v>8.9964083436938819E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19818,7 +19980,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92061412062996728</v>
+        <v>0.91003591656306126</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19836,7 +19998,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15866849999999999</v>
+        <v>0.15752850000000002</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19845,7 +20007,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14958449290250619</v>
+        <v>0.14733660393355438</v>
       </c>
     </row>
   </sheetData>
@@ -19890,60 +20052,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="248"/>
+      <c r="H3" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="239"/>
+      <c r="J3" s="239"/>
+      <c r="K3" s="239"/>
+      <c r="L3" s="239"/>
+      <c r="P3" s="250"/>
+      <c r="Q3" s="250"/>
+      <c r="R3" s="250"/>
+      <c r="S3" s="250"/>
+      <c r="T3" s="250"/>
+      <c r="U3" s="250"/>
+      <c r="V3" s="250"/>
+      <c r="W3" s="250"/>
+      <c r="X3" s="250"/>
+      <c r="Y3" s="250"/>
+      <c r="Z3" s="250"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="245" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="250"/>
+      <c r="Q5" s="250"/>
+      <c r="R5" s="250"/>
+      <c r="S5" s="250"/>
+      <c r="T5" s="250"/>
+      <c r="U5" s="250"/>
+      <c r="V5" s="250"/>
+      <c r="W5" s="250"/>
+      <c r="X5" s="250"/>
+      <c r="Y5" s="250"/>
+      <c r="Z5" s="250"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20096,7 +20258,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-28423.520436261952</v>
+        <v>-28925.284391587709</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20150,23 +20312,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8048.76355261343</v>
+        <v>-8064.5328802384638</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5654.7092232632258</v>
+        <v>-5676.8886088819236</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4125.2518135291557</v>
+        <v>-4149.5462219128358</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3920.6273943655701</v>
+        <v>-3951.4433527885344</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1798.5654427572829</v>
+        <v>-1816.2535765596492</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20185,14 +20347,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-14157.070113263129</v>
+        <v>-14548.673286885662</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="239" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="235"/>
+      <c r="C13" s="239"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20208,14 +20370,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14958449290250619</v>
+        <v>0.14733660393355438</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="239" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="235"/>
+      <c r="C18" s="239"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20223,7 +20385,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23547.917426528667</v>
+        <v>-23658.664640381405</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20232,7 +20394,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-14157.070113263129</v>
+        <v>-14548.673286885662</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20241,7 +20403,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-37704.987539791793</v>
+        <v>-38207.337927267065</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20268,7 +20430,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-50104.987539791793</v>
+        <v>-50607.337927267065</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20286,7 +20448,7 @@
       </c>
       <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-9.9335819864773587</v>
+        <v>-10.033175639822971</v>
       </c>
     </row>
   </sheetData>
@@ -20329,37 +20491,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="245" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20555,23 +20717,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8048.76355261343</v>
+        <v>-8064.5328802384638</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5654.7092232632258</v>
+        <v>-5676.8886088819236</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4125.2518135291557</v>
+        <v>-4149.5462219128358</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-3920.6273943655701</v>
+        <v>-3951.4433527885344</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1798.5654427572829</v>
+        <v>-1816.2535765596492</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -20579,18 +20741,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="241" t="s">
+      <c r="C11" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="241"/>
-      <c r="E11" s="241"/>
-      <c r="F11" s="241"/>
-      <c r="G11" s="241"/>
-      <c r="H11" s="241"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="241"/>
-      <c r="K11" s="241"/>
-      <c r="L11" s="241"/>
+      <c r="D11" s="245"/>
+      <c r="E11" s="245"/>
+      <c r="F11" s="245"/>
+      <c r="G11" s="245"/>
+      <c r="H11" s="245"/>
+      <c r="I11" s="245"/>
+      <c r="J11" s="245"/>
+      <c r="K11" s="245"/>
+      <c r="L11" s="245"/>
       <c r="N11" s="90"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20784,18 +20946,18 @@
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="241" t="s">
+      <c r="C17" s="245" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
-      <c r="K17" s="241"/>
-      <c r="L17" s="241"/>
+      <c r="D17" s="245"/>
+      <c r="E17" s="245"/>
+      <c r="F17" s="245"/>
+      <c r="G17" s="245"/>
+      <c r="H17" s="245"/>
+      <c r="I17" s="245"/>
+      <c r="J17" s="245"/>
+      <c r="K17" s="245"/>
+      <c r="L17" s="245"/>
       <c r="N17" s="90"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -20929,18 +21091,18 @@
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="241" t="s">
+      <c r="C22" s="245" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="241"/>
-      <c r="E22" s="241"/>
-      <c r="F22" s="241"/>
-      <c r="G22" s="241"/>
-      <c r="H22" s="241"/>
-      <c r="I22" s="241"/>
-      <c r="J22" s="241"/>
-      <c r="K22" s="241"/>
-      <c r="L22" s="241"/>
+      <c r="D22" s="245"/>
+      <c r="E22" s="245"/>
+      <c r="F22" s="245"/>
+      <c r="G22" s="245"/>
+      <c r="H22" s="245"/>
+      <c r="I22" s="245"/>
+      <c r="J22" s="245"/>
+      <c r="K22" s="245"/>
+      <c r="L22" s="245"/>
       <c r="N22" s="90"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21024,18 +21186,18 @@
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="241" t="s">
+      <c r="C27" s="245" t="s">
         <v>195</v>
       </c>
-      <c r="D27" s="241"/>
-      <c r="E27" s="241"/>
-      <c r="F27" s="241"/>
-      <c r="G27" s="241"/>
-      <c r="H27" s="241"/>
-      <c r="I27" s="241"/>
-      <c r="J27" s="241"/>
-      <c r="K27" s="241"/>
-      <c r="L27" s="241"/>
+      <c r="D27" s="245"/>
+      <c r="E27" s="245"/>
+      <c r="F27" s="245"/>
+      <c r="G27" s="245"/>
+      <c r="H27" s="245"/>
+      <c r="I27" s="245"/>
+      <c r="J27" s="245"/>
+      <c r="K27" s="245"/>
+      <c r="L27" s="245"/>
       <c r="N27" s="90"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21336,10 +21498,10 @@
       <c r="N38" s="90"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="235" t="s">
+      <c r="B39" s="239" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="235"/>
+      <c r="C39" s="239"/>
       <c r="N39" s="90"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21357,7 +21519,7 @@
       </c>
       <c r="C41" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14958449290250619</v>
+        <v>0.14733660393355438</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21383,7 +21545,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>216610.5150468194</v>
+        <v>218740.78825348898</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21392,7 +21554,7 @@
       </c>
       <c r="C45" s="93">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>194861.16306304804</v>
+        <v>196898.37718966723</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21419,7 +21581,7 @@
       </c>
       <c r="C48" s="107">
         <f ca="1">C45+C46-C47</f>
-        <v>182461.16306304804</v>
+        <v>184498.37718966723</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21437,14 +21599,14 @@
       </c>
       <c r="C50" s="231">
         <f ca="1">C48/C49</f>
-        <v>36.173902272610633</v>
+        <v>36.577790878205242</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="235" t="s">
+      <c r="B52" s="239" t="s">
         <v>205</v>
       </c>
-      <c r="C52" s="235"/>
+      <c r="C52" s="239"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21500,10 +21662,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="235" t="s">
+      <c r="B60" s="239" t="s">
         <v>317</v>
       </c>
-      <c r="C60" s="235"/>
+      <c r="C60" s="239"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21520,7 +21682,7 @@
       </c>
       <c r="C62" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14958449290250619</v>
+        <v>0.14733660393355438</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21546,7 +21708,7 @@
       </c>
       <c r="C65" s="63">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>-71942.617710291306</v>
+        <v>-72650.143062385963</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21555,7 +21717,7 @@
       </c>
       <c r="C66" s="93">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>-93691.969694062689</v>
+        <v>-94492.554126207717</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21582,7 +21744,7 @@
       </c>
       <c r="C69" s="93">
         <f ca="1">C66+C67-C68</f>
-        <v>-106091.96969406269</v>
+        <v>-106892.55412620772</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21600,14 +21762,14 @@
       </c>
       <c r="C71" s="231">
         <f ca="1">C69/C70</f>
-        <v>-21.033300890971983</v>
+        <v>-21.192021040088761</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="235" t="s">
+      <c r="B73" s="239" t="s">
         <v>414</v>
       </c>
-      <c r="C73" s="235"/>
+      <c r="C73" s="239"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21624,7 +21786,7 @@
       </c>
       <c r="C75" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14958449290250619</v>
+        <v>0.14733660393355438</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21650,7 +21812,7 @@
       </c>
       <c r="C78" s="63">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>238033.53301848276</v>
+        <v>240374.49258625152</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21659,7 +21821,7 @@
       </c>
       <c r="C79" s="93">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>216284.18103471136</v>
+        <v>218532.08152242977</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21686,7 +21848,7 @@
       </c>
       <c r="C82" s="93">
         <f ca="1">C79+C80-C81</f>
-        <v>203884.18103471136</v>
+        <v>206132.08152242977</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21704,22 +21866,22 @@
       </c>
       <c r="C84" s="231">
         <f ca="1">C82/C83</f>
-        <v>40.421130260648567</v>
+        <v>40.866788565112962</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21757,10 +21919,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="239" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="235"/>
+      <c r="C4" s="239"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21769,7 +21931,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-9.9335819864773587</v>
+        <v>-10.033175639822971</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21778,7 +21940,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C50</f>
-        <v>36.173902272610633</v>
+        <v>36.577790878205242</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21796,7 +21958,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C71</f>
-        <v>-21.033300890971983</v>
+        <v>-21.192021040088761</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21805,7 +21967,7 @@
       </c>
       <c r="C9" s="132">
         <f ca="1">Multiples!C84</f>
-        <v>40.421130260648567</v>
+        <v>40.866788565112962</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21814,7 +21976,7 @@
       </c>
       <c r="C10" s="231">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>18.873322099100314</v>
+        <v>18.991568720619636</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21823,7 +21985,7 @@
       </c>
       <c r="C11" s="132">
         <f ca="1">Overview!C5</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21832,7 +21994,7 @@
       </c>
       <c r="C12" s="151">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.8375650047413693</v>
+        <v>-0.81261402347686595</v>
       </c>
     </row>
   </sheetData>
@@ -21848,18 +22010,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="131" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="234" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="234" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="234" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="234" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="235" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{70104AE7-FBEA-2E4F-A2B6-8CC367FC1CD5}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{D9400C1E-21BA-7643-B47C-411621DEEC8B}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{7E8D648B-3B86-B94A-8E13-9E07062B8D6E}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{32954A4C-9CB8-1142-8495-3DE4B04BEEF7}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{DC12F570-F933-6C45-B8FD-755C80DF2A1F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21888,37 +22089,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="235" t="s">
+      <c r="C2" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="235"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="245" t="s">
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="248"/>
+      <c r="H2" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="235"/>
-      <c r="J2" s="235"/>
-      <c r="K2" s="235"/>
-      <c r="L2" s="235"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="241" t="s">
+      <c r="C4" s="245" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="241"/>
-      <c r="E4" s="241"/>
-      <c r="F4" s="241"/>
-      <c r="G4" s="241"/>
-      <c r="H4" s="241"/>
-      <c r="I4" s="241"/>
-      <c r="J4" s="241"/>
-      <c r="K4" s="241"/>
-      <c r="L4" s="241"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22031,18 +22232,18 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="241" t="s">
+      <c r="C9" s="245" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="241"/>
-      <c r="E9" s="241"/>
-      <c r="F9" s="241"/>
-      <c r="G9" s="241"/>
-      <c r="H9" s="241"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="241"/>
-      <c r="K9" s="241"/>
-      <c r="L9" s="241"/>
+      <c r="D9" s="245"/>
+      <c r="E9" s="245"/>
+      <c r="F9" s="245"/>
+      <c r="G9" s="245"/>
+      <c r="H9" s="245"/>
+      <c r="I9" s="245"/>
+      <c r="J9" s="245"/>
+      <c r="K9" s="245"/>
+      <c r="L9" s="245"/>
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22163,18 +22364,18 @@
       <c r="N13" s="90"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="241" t="s">
+      <c r="C14" s="245" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
-      <c r="K14" s="241"/>
-      <c r="L14" s="241"/>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="245"/>
+      <c r="G14" s="245"/>
+      <c r="H14" s="245"/>
+      <c r="I14" s="245"/>
+      <c r="J14" s="245"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
       <c r="N14" s="90"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22264,10 +22465,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="235" t="s">
+      <c r="B20" s="239" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="235"/>
+      <c r="C20" s="239"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22368,60 +22569,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="235" t="s">
+      <c r="C3" s="239" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="235"/>
-      <c r="E3" s="235"/>
-      <c r="F3" s="235"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="245" t="s">
+      <c r="D3" s="239"/>
+      <c r="E3" s="239"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="248"/>
+      <c r="H3" s="249" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="235"/>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
-      <c r="P3" s="246"/>
-      <c r="Q3" s="246"/>
-      <c r="R3" s="246"/>
-      <c r="S3" s="246"/>
-      <c r="T3" s="246"/>
-      <c r="U3" s="246"/>
-      <c r="V3" s="246"/>
-      <c r="W3" s="246"/>
-      <c r="X3" s="246"/>
-      <c r="Y3" s="246"/>
-      <c r="Z3" s="246"/>
+      <c r="I3" s="239"/>
+      <c r="J3" s="239"/>
+      <c r="K3" s="239"/>
+      <c r="L3" s="239"/>
+      <c r="P3" s="250"/>
+      <c r="Q3" s="250"/>
+      <c r="R3" s="250"/>
+      <c r="S3" s="250"/>
+      <c r="T3" s="250"/>
+      <c r="U3" s="250"/>
+      <c r="V3" s="250"/>
+      <c r="W3" s="250"/>
+      <c r="X3" s="250"/>
+      <c r="Y3" s="250"/>
+      <c r="Z3" s="250"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="241" t="s">
+      <c r="C5" s="245" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="241"/>
-      <c r="E5" s="241"/>
-      <c r="F5" s="241"/>
-      <c r="G5" s="241"/>
-      <c r="H5" s="241"/>
-      <c r="I5" s="241"/>
-      <c r="J5" s="241"/>
-      <c r="K5" s="241"/>
-      <c r="L5" s="241"/>
-      <c r="P5" s="246"/>
-      <c r="Q5" s="246"/>
-      <c r="R5" s="246"/>
-      <c r="S5" s="246"/>
-      <c r="T5" s="246"/>
-      <c r="U5" s="246"/>
-      <c r="V5" s="246"/>
-      <c r="W5" s="246"/>
-      <c r="X5" s="246"/>
-      <c r="Y5" s="246"/>
-      <c r="Z5" s="246"/>
+      <c r="D5" s="245"/>
+      <c r="E5" s="245"/>
+      <c r="F5" s="245"/>
+      <c r="G5" s="245"/>
+      <c r="H5" s="245"/>
+      <c r="I5" s="245"/>
+      <c r="J5" s="245"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="P5" s="250"/>
+      <c r="Q5" s="250"/>
+      <c r="R5" s="250"/>
+      <c r="S5" s="250"/>
+      <c r="T5" s="250"/>
+      <c r="U5" s="250"/>
+      <c r="V5" s="250"/>
+      <c r="W5" s="250"/>
+      <c r="X5" s="250"/>
+      <c r="Y5" s="250"/>
+      <c r="Z5" s="250"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22556,7 +22757,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-454751.44859292789</v>
+        <v>-462779.23269686324</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22610,23 +22811,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6780.32137721239</v>
+        <v>-6793.6055429729267</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9731.8033963330709</v>
+        <v>-9769.9743104809895</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-13968.069074598561</v>
+        <v>-14050.32974370895</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20048.386278156078</v>
+        <v>-20205.965710183475</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-28775.472845355227</v>
+        <v>-29058.46750421774</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22645,15 +22846,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-226500.7304874415</v>
+        <v>-232766.03850506627</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="248" t="s">
+      <c r="B14" s="251" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="249"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22661,7 +22862,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22670,7 +22871,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-63.08580163741015</v>
+        <v>-64.441788524312116</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22680,20 +22881,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="247" t="s">
+      <c r="E17" s="253" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="247"/>
-      <c r="G17" s="247"/>
-      <c r="H17" s="247"/>
-      <c r="I17" s="247"/>
+      <c r="F17" s="253"/>
+      <c r="G17" s="253"/>
+      <c r="H17" s="253"/>
+      <c r="I17" s="253"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="248" t="s">
+      <c r="B19" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="249"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22709,7 +22910,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14958449290250619</v>
+        <v>0.14733660393355438</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22727,7 +22928,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>586062.36</v>
+        <v>511209.39999999997</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22754,15 +22955,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>598462.36</v>
+        <v>523609.39999999991</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="248" t="s">
+      <c r="B28" s="251" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="249"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -22770,7 +22971,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-79304.052971655328</v>
+        <v>-79878.342811564085</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22779,7 +22980,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-226500.7304874415</v>
+        <v>-232766.03850506627</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22788,7 +22989,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-305804.7834590968</v>
+        <v>-312644.38131663034</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -22815,7 +23016,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-318204.7834590968</v>
+        <v>-325044.38131663034</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -22833,21 +23034,21 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-63.08580163741015</v>
+        <v>-64.441788524312116</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29506,7 +29707,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29577,7 +29778,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -30883,7 +31084,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-55.066350710900466</v>
+        <v>-48.033175355450226</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -30920,7 +31121,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>9.9607581270164118</v>
+        <v>8.6885518217842606</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -30981,7 +31182,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>6.6946421146421144</v>
+        <v>5.8395901395901388</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31042,7 +31243,7 @@
       </c>
       <c r="AC153" s="140">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>586062.36</v>
+        <v>511209.39999999997</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31103,7 +31304,7 @@
       </c>
       <c r="AC154" s="140">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>614063.35999999999</v>
+        <v>539210.39999999991</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31140,7 +31341,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="178">
         <f ca="1">AC154/AC5</f>
-        <v>10.766996773741058</v>
+        <v>9.4545237761256828</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31177,7 +31378,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="178">
         <f ca="1">AC154/AC12</f>
-        <v>-7974.8488311688307</v>
+        <v>-7002.7324675324662</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31312,7 +31513,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-52.117595375722544</v>
+        <v>-45.461040462427739</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31349,7 +31550,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-79.63472441966023</v>
+        <v>-69.927428349111651</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31386,7 +31587,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-1.9187377943876142E-2</v>
+        <v>-2.1996856865308032E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31423,7 +31624,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-1.8159910491436445E-2</v>
+        <v>-2.0818944252590038E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31534,7 +31735,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="151">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>2.728378597799729E-3</v>
+        <v>3.1278767565698128E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32037,7 +32238,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="151">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-2.1158157981686455E-2</v>
+        <v>-2.425620499153576E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -33748,18 +33949,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="131" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="234" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="234" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="234" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="234" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="235" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>227</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{2D27DE06-8CB2-534D-BA10-29E499730906}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{A0508156-8678-DD40-B34B-942B35AFC366}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{268ED4EF-1BBB-E84A-A0FC-D2446769C91C}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{BD1CC9A3-E228-2B4F-84C4-3CE291267636}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{A6120D08-6B10-3B4B-9F9C-F630879294C6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33783,15 +34023,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="235" t="s">
+      <c r="B4" s="239" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="235"/>
-      <c r="E4" s="235" t="s">
+      <c r="C4" s="239"/>
+      <c r="E4" s="239" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="235"/>
-      <c r="G4" s="235"/>
+      <c r="F4" s="239"/>
+      <c r="G4" s="239"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -33799,7 +34039,7 @@
       </c>
       <c r="C5" s="167">
         <f ca="1">Overview!C5</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -33815,7 +34055,7 @@
       </c>
       <c r="C6" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>586062.36</v>
+        <v>511209.39999999997</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -33835,7 +34075,7 @@
       </c>
       <c r="C7" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>614063.35999999999</v>
+        <v>539210.39999999991</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -33855,7 +34095,7 @@
       </c>
       <c r="C8" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-55.066350710900466</v>
+        <v>-48.033175355450226</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>238</v>
@@ -33875,7 +34115,7 @@
       </c>
       <c r="C9" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>9.9607581270164118</v>
+        <v>8.6885518217842606</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>239</v>
@@ -33895,7 +34135,7 @@
       </c>
       <c r="C10" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>6.6946421146421144</v>
+        <v>5.8395901395901388</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -33915,7 +34155,7 @@
       </c>
       <c r="C11" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>10.766996773741058</v>
+        <v>9.4545237761256828</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -33924,18 +34164,18 @@
       </c>
       <c r="C12" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-7974.8488311688307</v>
+        <v>-7002.7324675324662</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="239" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="235"/>
-      <c r="E15" s="235" t="s">
+      <c r="C15" s="239"/>
+      <c r="E15" s="239" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="235"/>
+      <c r="F15" s="239"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -33986,14 +34226,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="235" t="s">
+      <c r="B21" s="239" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="235"/>
-      <c r="E21" s="235" t="s">
+      <c r="C21" s="239"/>
+      <c r="E21" s="239" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="235"/>
+      <c r="F21" s="239"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34062,14 +34302,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="235" t="s">
+      <c r="B29" s="239" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="235"/>
-      <c r="E29" s="235" t="s">
+      <c r="C29" s="239"/>
+      <c r="E29" s="239" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="235"/>
+      <c r="F29" s="239"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34145,14 +34385,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="235" t="s">
+      <c r="B37" s="239" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="235"/>
-      <c r="E37" s="235" t="s">
+      <c r="C37" s="239"/>
+      <c r="E37" s="239" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="235"/>
+      <c r="F37" s="239"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34160,7 +34400,7 @@
       </c>
       <c r="C38" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-1.8159910491436445E-2</v>
+        <v>-2.0818944252590038E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>265</v>
@@ -34176,7 +34416,7 @@
       </c>
       <c r="C39" s="210">
         <f ca="1">Statement!AC161</f>
-        <v>-1.9187377943876142E-2</v>
+        <v>-2.1996856865308032E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>267</v>
@@ -34217,18 +34457,18 @@
       </c>
       <c r="C42" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>2.728378597799729E-3</v>
+        <v>3.1278767565698128E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="235" t="s">
+      <c r="B45" s="239" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="235"/>
-      <c r="E45" s="235" t="s">
+      <c r="C45" s="239"/>
+      <c r="E45" s="239" t="s">
         <v>280</v>
       </c>
-      <c r="F45" s="235"/>
+      <c r="F45" s="239"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34261,18 +34501,18 @@
       </c>
       <c r="F48" s="170">
         <f ca="1">Statement!AC176</f>
-        <v>-2.1158157981686455E-2</v>
+        <v>-2.425620499153576E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="235" t="s">
+      <c r="B51" s="239" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="235"/>
-      <c r="E51" s="235" t="s">
+      <c r="C51" s="239"/>
+      <c r="E51" s="239" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="235"/>
+      <c r="F51" s="239"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34440,7 +34680,7 @@
       </c>
       <c r="I6" s="167">
         <f ca="1">Statement!AC116</f>
-        <v>116.19</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34469,7 +34709,7 @@
       </c>
       <c r="I7" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>586062.36</v>
+        <v>511209.39999999997</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34498,7 +34738,7 @@
       </c>
       <c r="I8" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>614063.35999999999</v>
+        <v>539210.39999999991</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34527,7 +34767,7 @@
       </c>
       <c r="I9" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-55.066350710900466</v>
+        <v>-48.033175355450226</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34556,7 +34796,7 @@
       </c>
       <c r="I10" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>9.9607581270164118</v>
+        <v>8.6885518217842606</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34585,7 +34825,7 @@
       </c>
       <c r="I11" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>6.6946421146421144</v>
+        <v>5.8395901395901388</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34614,7 +34854,7 @@
       </c>
       <c r="I12" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>10.766996773741058</v>
+        <v>9.4545237761256828</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34643,7 +34883,7 @@
       </c>
       <c r="I13" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-7974.8488311688307</v>
+        <v>-7002.7324675324662</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35416,7 +35656,7 @@
       </c>
       <c r="I51" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-1.8159910491436445E-2</v>
+        <v>-2.0818944252590038E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35445,7 +35685,7 @@
       </c>
       <c r="I52" s="170">
         <f ca="1">Statement!AC161</f>
-        <v>-1.9187377943876142E-2</v>
+        <v>-2.1996856865308032E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35532,7 +35772,7 @@
       </c>
       <c r="I55" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>2.728378597799729E-3</v>
+        <v>3.1278767565698128E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35768,7 +36008,7 @@
       </c>
       <c r="I68" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-2.1158157981686455E-2</v>
+        <v>-2.425620499153576E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36306,14 +36546,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="240" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="F3" s="240" t="s">
+      <c r="D3" s="241"/>
+      <c r="F3" s="242" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="239"/>
+      <c r="G3" s="241"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36380,19 +36620,19 @@
       <c r="B7" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C7" s="236">
+      <c r="C7" s="243">
         <f>Statement!AA89</f>
         <v>0.18789128673491934</v>
       </c>
-      <c r="D7" s="237"/>
-      <c r="F7" s="236">
+      <c r="D7" s="244"/>
+      <c r="F7" s="243">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.25421883505715842</v>
       </c>
-      <c r="G7" s="237"/>
+      <c r="G7" s="244"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
@@ -36419,19 +36659,19 @@
       <c r="B9" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="236">
+      <c r="C9" s="243">
         <f>Statement!AA90</f>
         <v>0.16877278250303768</v>
       </c>
-      <c r="D9" s="237"/>
-      <c r="F9" s="236">
+      <c r="D9" s="244"/>
+      <c r="F9" s="243">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>3.2413867124610925E-2</v>
       </c>
-      <c r="G9" s="237"/>
+      <c r="G9" s="244"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
@@ -36458,19 +36698,19 @@
       <c r="B11" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C11" s="236">
+      <c r="C11" s="243">
         <f>Statement!AA91</f>
         <v>0.21731812231157657</v>
       </c>
-      <c r="D11" s="237"/>
-      <c r="F11" s="236">
+      <c r="D11" s="244"/>
+      <c r="F11" s="243">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.83766233766233766</v>
       </c>
-      <c r="G11" s="237"/>
+      <c r="G11" s="244"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="202" t="s">
@@ -36497,19 +36737,19 @@
       <c r="B13" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C13" s="236">
+      <c r="C13" s="243">
         <f>Statement!AA95</f>
         <v>-0.44441824826122833</v>
       </c>
-      <c r="D13" s="237"/>
-      <c r="F13" s="236">
+      <c r="D13" s="244"/>
+      <c r="F13" s="243">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-0.29845192021434952</v>
       </c>
-      <c r="G13" s="237"/>
+      <c r="G13" s="244"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="202" t="s">
@@ -36536,19 +36776,19 @@
       <c r="B15" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C15" s="236">
+      <c r="C15" s="243">
         <f>Statement!AA96</f>
         <v>1.572704081632653</v>
       </c>
-      <c r="D15" s="237"/>
-      <c r="F15" s="236">
+      <c r="D15" s="244"/>
+      <c r="F15" s="243">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5654911838790933</v>
       </c>
-      <c r="G15" s="237"/>
+      <c r="G15" s="244"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="202" t="s">
@@ -36575,19 +36815,19 @@
       <c r="B17" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C17" s="236">
+      <c r="C17" s="243">
         <f>Statement!AA98</f>
         <v>-1.9594957081545064</v>
       </c>
-      <c r="D17" s="237"/>
-      <c r="F17" s="236">
+      <c r="D17" s="244"/>
+      <c r="F17" s="243">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-2.781014393420151</v>
       </c>
-      <c r="G17" s="237"/>
+      <c r="G17" s="244"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="202" t="s">
@@ -36614,22 +36854,22 @@
       <c r="B19" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="236">
+      <c r="C19" s="243">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.1314184536690932E-3</v>
       </c>
-      <c r="D19" s="237"/>
-      <c r="F19" s="236">
+      <c r="D19" s="244"/>
+      <c r="F19" s="243">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.16823071641107806</v>
       </c>
-      <c r="G19" s="237"/>
+      <c r="G19" s="244"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="202" t="s">
@@ -36656,22 +36896,22 @@
       <c r="B21" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C21" s="236">
+      <c r="C21" s="243">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-1.9589041095890414</v>
       </c>
-      <c r="D21" s="237"/>
-      <c r="F21" s="236">
+      <c r="D21" s="244"/>
+      <c r="F21" s="243">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.2238805970149254</v>
       </c>
-      <c r="G21" s="237"/>
+      <c r="G21" s="244"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -36719,22 +36959,22 @@
       <c r="B25" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="236">
+      <c r="C25" s="243">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14882878219231266</v>
       </c>
-      <c r="D25" s="237"/>
-      <c r="F25" s="236">
+      <c r="D25" s="244"/>
+      <c r="F25" s="243">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.12781095159446068</v>
       </c>
-      <c r="G25" s="237"/>
+      <c r="G25" s="244"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -36761,22 +37001,22 @@
       <c r="B27" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C27" s="236">
+      <c r="C27" s="243">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.23950910530482977</v>
       </c>
-      <c r="D27" s="237"/>
-      <c r="F27" s="236">
+      <c r="D27" s="244"/>
+      <c r="F27" s="243">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.58974358974358976</v>
       </c>
-      <c r="G27" s="237"/>
+      <c r="G27" s="244"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -36803,22 +37043,22 @@
       <c r="B29" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C29" s="236">
+      <c r="C29" s="243">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18467798732295171</v>
       </c>
-      <c r="D29" s="237"/>
-      <c r="F29" s="236">
+      <c r="D29" s="244"/>
+      <c r="F29" s="243">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28187976291278577</v>
       </c>
-      <c r="G29" s="237"/>
+      <c r="G29" s="244"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -36845,22 +37085,22 @@
       <c r="B31" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C31" s="236">
+      <c r="C31" s="243">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>6.3456926766279287E-2</v>
       </c>
-      <c r="D31" s="237"/>
-      <c r="F31" s="236">
+      <c r="D31" s="244"/>
+      <c r="F31" s="243">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.30518451437627347</v>
       </c>
-      <c r="G31" s="237"/>
+      <c r="G31" s="244"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -36887,37 +37127,25 @@
       <c r="B33" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C33" s="236">
+      <c r="C33" s="243">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.11624203821656051</v>
       </c>
-      <c r="D33" s="237"/>
-      <c r="F33" s="236">
+      <c r="D33" s="244"/>
+      <c r="F33" s="243">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33428300094966762</v>
       </c>
-      <c r="G33" s="237"/>
+      <c r="G33" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -36934,6 +37162,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8647F51-D805-9B42-9ED5-8A00C10CF4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C962BDB8-5AA7-2E4E-ABAA-79B74E68E6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -121,7 +121,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -132,7 +132,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -142,19 +163,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="428">
   <si>
     <t>Ticker</t>
   </si>
@@ -1435,6 +1465,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2047,7 +2080,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2418,6 +2451,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12826,7 +12862,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12845,11 +12881,9 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>32.89</v>
-    <v>2.3353000000000002</v>
-    <v>-3.35</v>
-    <v>-3.1996000000000004E-2</v>
-    <v>0.21</v>
-    <v>2.0720000000000001E-3</v>
+    <v>2.3628999999999998</v>
+    <v>0.58499999999999996</v>
+    <v>6.3570000000000007E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12857,35 +12891,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>103.19</v>
+    <v>93.73</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46307.860498553127</v>
+    <v>46315.719771180469</v>
     <v>0</v>
-    <v>100.7103</v>
-    <v>535641743150</v>
+    <v>88.77</v>
+    <v>489476665435</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>102.515</v>
+    <v>90.8</v>
     <v>0</v>
-    <v>104.7</v>
-    <v>101.35</v>
-    <v>101.56</v>
+    <v>92.03</v>
+    <v>92.614999999999995</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>72339596</v>
-    <v>108154739</v>
+    <v>57381397</v>
+    <v>109100108</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12899,28 +12947,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>52.34</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12942,8 +12990,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -12964,7 +13010,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -12974,6 +13019,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13009,7 +13059,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13020,16 +13070,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13123,19 +13170,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13207,9 +13248,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13217,9 +13255,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13700,7 +13735,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -13738,7 +13773,7 @@
       </c>
       <c r="F3" s="182">
         <f ca="1">Statement!AC153</f>
-        <v>511209.39999999997</v>
+        <v>467150.06</v>
       </c>
       <c r="H3" s="180" t="str">
         <f>'AVG target price'!B5</f>
@@ -13746,7 +13781,7 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.033175639822971</v>
+        <v>-10.065822156934358</v>
       </c>
       <c r="K3" s="234" t="s">
         <v>422</v>
@@ -13765,7 +13800,7 @@
       </c>
       <c r="F4" s="183">
         <f ca="1">Statement!AC154</f>
-        <v>539210.39999999991</v>
+        <v>495151.06</v>
       </c>
       <c r="H4" s="180" t="str">
         <f>'AVG target price'!B6</f>
@@ -13773,7 +13808,7 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.577790878205242</v>
+        <v>36.708403191629159</v>
       </c>
       <c r="K4" s="234" t="s">
         <v>423</v>
@@ -13785,7 +13820,7 @@
       </c>
       <c r="C5" s="203" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
       <c r="E5" s="180" t="s">
         <v>238</v>
@@ -13810,16 +13845,16 @@
       <c r="B6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="203" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>101.56</v>
+      <c r="C6" s="203" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="180" t="s">
         <v>232</v>
       </c>
       <c r="F6" s="185">
         <f ca="1">Statement!AC150</f>
-        <v>-48.033175355450226</v>
+        <v>-43.893364928909946</v>
       </c>
       <c r="H6" s="180" t="str">
         <f>'AVG target price'!B8</f>
@@ -13827,7 +13862,7 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.192021040088761</v>
+        <v>-21.243324996427159</v>
       </c>
       <c r="K6" s="235" t="s">
         <v>425</v>
@@ -13839,14 +13874,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-3.35</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="E7" s="181" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="186">
         <f ca="1">Statement!AC151</f>
-        <v>8.6885518217842606</v>
+        <v>7.9397161023635849</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13854,23 +13889,23 @@
       </c>
       <c r="I7" s="206">
         <f ca="1">'AVG target price'!C9</f>
-        <v>40.866788565112962</v>
+        <v>41.010906867812473</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.21</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="180" t="s">
         <v>260</v>
       </c>
       <c r="F8" s="187">
         <f ca="1">Statement!AC161</f>
-        <v>-2.1996856865308032E-2</v>
+        <v>-2.4071494286011651E-2</v>
       </c>
       <c r="H8" s="179" t="str">
         <f>'AVG target price'!B10</f>
@@ -13878,7 +13913,7 @@
       </c>
       <c r="I8" s="207">
         <f ca="1">'AVG target price'!C10</f>
-        <v>18.991568720619636</v>
+        <v>19.029724749154365</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13887,14 +13922,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-3.1996000000000004E-2</v>
+        <v>6.3570000000000007E-3</v>
       </c>
       <c r="E9" s="180" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="187">
         <f ca="1">Statement!AC162</f>
-        <v>-2.0818944252590038E-2</v>
+        <v>-2.2782486638233554E-2</v>
       </c>
       <c r="H9" s="179" t="str">
         <f>'AVG target price'!B12</f>
@@ -13902,16 +13937,16 @@
       </c>
       <c r="I9" s="208">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.81261402347686595</v>
+        <v>-0.79452869676451576</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>2.0720000000000001E-3</v>
+      <c r="C10" s="72" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="180" t="s">
         <v>288</v>
@@ -13966,7 +14001,7 @@
       </c>
       <c r="C13" s="204" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3353000000000002</v>
+        <v>2.3628999999999998</v>
       </c>
       <c r="E13" s="180" t="s">
         <v>99</v>
@@ -13975,10 +14010,10 @@
         <f>Statement!AC125</f>
         <v>-0.12784720477028169</v>
       </c>
-      <c r="H13" s="179" t="s">
+      <c r="H13" s="256" t="s">
         <v>418</v>
       </c>
-      <c r="I13" s="208">
+      <c r="I13" s="254">
         <f>'Reverse DCF'!C17</f>
         <v>0.65</v>
       </c>
@@ -13989,7 +14024,7 @@
       </c>
       <c r="C14" s="205" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>108154739</v>
+        <v>109100108</v>
       </c>
       <c r="E14" s="181" t="s">
         <v>100</v>
@@ -13998,6 +14033,13 @@
         <f>Statement!AC140</f>
         <v>-6.6641856278614885E-4</v>
       </c>
+      <c r="H14" s="181" t="s">
+        <v>427</v>
+      </c>
+      <c r="I14" s="255">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>-64.887570402808493</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="180" t="s">
@@ -14005,7 +14047,7 @@
       </c>
       <c r="F15" s="187">
         <f ca="1">Statement!AC176</f>
-        <v>-2.425620499153576E-2</v>
+        <v>-2.6543933227794084E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14038,7 +14080,7 @@
       </c>
       <c r="I17" s="232">
         <f ca="1">DCF!C15</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14128,12 +14170,12 @@
       <c r="C26" s="165">
         <v>0.21</v>
       </c>
-      <c r="E26" s="180" t="e" vm="2">
+      <c r="E26" s="180" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14148,7 +14190,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -19892,7 +19934,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19901,7 +19943,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>511209.39999999997</v>
+        <v>467150.06</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19919,7 +19961,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19928,7 +19970,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.3353000000000002</v>
+        <v>2.3628999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19971,7 +20013,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>8.9964083436938819E-2</v>
+        <v>9.7620751810949258E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19980,7 +20022,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.91003591656306126</v>
+        <v>0.90237924818905069</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19998,7 +20040,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15752850000000002</v>
+        <v>0.15769049999999998</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20007,7 +20049,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
   </sheetData>
@@ -20258,7 +20300,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-28925.284391587709</v>
+        <v>-29090.04871693307</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20312,23 +20354,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8064.5328802384638</v>
+        <v>-8069.6055133726877</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5676.8886088819236</v>
+        <v>-5684.0324398624853</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4149.5462219128358</v>
+        <v>-4157.3814066987125</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3951.4433527885344</v>
+        <v>-3961.3946506947227</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1816.2535765596492</v>
+        <v>-1821.9729317837498</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20347,7 +20389,7 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-14548.673286885662</v>
+        <v>-14677.620017164549</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20370,7 +20412,7 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20385,7 +20427,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23658.664640381405</v>
+        <v>-23694.386942412355</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20394,7 +20436,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-14548.673286885662</v>
+        <v>-14677.620017164549</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20403,7 +20445,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-38207.337927267065</v>
+        <v>-38372.006959576902</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20430,7 +20472,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-50607.337927267065</v>
+        <v>-50772.006959576902</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20448,7 +20490,7 @@
       </c>
       <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-10.033175639822971</v>
+        <v>-10.065822156934358</v>
       </c>
     </row>
   </sheetData>
@@ -20717,23 +20759,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8064.5328802384638</v>
+        <v>-8069.6055133726877</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5676.8886088819236</v>
+        <v>-5684.0324398624853</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4149.5462219128358</v>
+        <v>-4157.3814066987125</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-3951.4433527885344</v>
+        <v>-3961.3946506947227</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1816.2535765596492</v>
+        <v>-1821.9729317837498</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -21519,7 +21561,7 @@
       </c>
       <c r="C41" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21545,7 +21587,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>218740.78825348898</v>
+        <v>219429.59970920609</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21554,7 +21596,7 @@
       </c>
       <c r="C45" s="93">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>196898.37718966723</v>
+        <v>197557.18569857749</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21581,7 +21623,7 @@
       </c>
       <c r="C48" s="107">
         <f ca="1">C45+C46-C47</f>
-        <v>184498.37718966723</v>
+        <v>185157.18569857749</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21599,7 +21641,7 @@
       </c>
       <c r="C50" s="231">
         <f ca="1">C48/C49</f>
-        <v>36.577790878205242</v>
+        <v>36.708403191629159</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21682,7 +21724,7 @@
       </c>
       <c r="C62" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21708,7 +21750,7 @@
       </c>
       <c r="C65" s="63">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>-72650.143062385963</v>
+        <v>-72878.917271349987</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21717,7 +21759,7 @@
       </c>
       <c r="C66" s="93">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>-94492.554126207717</v>
+        <v>-94751.331281978593</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21744,7 +21786,7 @@
       </c>
       <c r="C69" s="93">
         <f ca="1">C66+C67-C68</f>
-        <v>-106892.55412620772</v>
+        <v>-107151.33128197859</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21762,7 +21804,7 @@
       </c>
       <c r="C71" s="231">
         <f ca="1">C69/C70</f>
-        <v>-21.192021040088761</v>
+        <v>-21.243324996427159</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21786,7 +21828,7 @@
       </c>
       <c r="C75" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21812,7 +21854,7 @@
       </c>
       <c r="C78" s="63">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>240374.49258625152</v>
+        <v>241131.42825187472</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21821,7 +21863,7 @@
       </c>
       <c r="C79" s="93">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>218532.08152242977</v>
+        <v>219259.0142412461</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21848,7 +21890,7 @@
       </c>
       <c r="C82" s="93">
         <f ca="1">C79+C80-C81</f>
-        <v>206132.08152242977</v>
+        <v>206859.0142412461</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21866,7 +21908,7 @@
       </c>
       <c r="C84" s="231">
         <f ca="1">C82/C83</f>
-        <v>40.866788565112962</v>
+        <v>41.010906867812473</v>
       </c>
     </row>
   </sheetData>
@@ -21931,7 +21973,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.033175639822971</v>
+        <v>-10.065822156934358</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21940,7 +21982,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C50</f>
-        <v>36.577790878205242</v>
+        <v>36.708403191629159</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21958,7 +22000,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C71</f>
-        <v>-21.192021040088761</v>
+        <v>-21.243324996427159</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -21967,7 +22009,7 @@
       </c>
       <c r="C9" s="132">
         <f ca="1">Multiples!C84</f>
-        <v>40.866788565112962</v>
+        <v>41.010906867812473</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -21976,7 +22018,7 @@
       </c>
       <c r="C10" s="231">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>18.991568720619636</v>
+        <v>19.029724749154365</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -21985,7 +22027,7 @@
       </c>
       <c r="C11" s="132">
         <f ca="1">Overview!C5</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -21994,7 +22036,7 @@
       </c>
       <c r="C12" s="151">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.81261402347686595</v>
+        <v>-0.79452869676451576</v>
       </c>
     </row>
   </sheetData>
@@ -22757,7 +22799,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-462779.23269686324</v>
+        <v>-465415.31768834975</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22811,23 +22853,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6793.6055429729267</v>
+        <v>-6797.8787562005118</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9769.9743104809895</v>
+        <v>-9782.2689052787991</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-14050.32974370895</v>
+        <v>-14076.85961564124</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20205.965710183475</v>
+        <v>-20256.852327126209</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-29058.46750421774</v>
+        <v>-29149.972181796635</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22846,7 +22888,7 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-232766.03850506627</v>
+        <v>-234829.07332572262</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22862,7 +22904,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22871,7 +22913,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-64.441788524312116</v>
+        <v>-64.887570402808493</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22910,7 +22952,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14733660393355438</v>
+        <v>0.14661537689667187</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22928,7 +22970,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>511209.39999999997</v>
+        <v>467150.06</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22955,7 +22997,7 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>523609.39999999991</v>
+        <v>479550.06</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -22971,7 +23013,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-79878.342811564085</v>
+        <v>-80063.831786043389</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -22980,7 +23022,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-232766.03850506627</v>
+        <v>-234829.07332572262</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -22989,7 +23031,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-312644.38131663034</v>
+        <v>-314892.90511176601</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23016,7 +23058,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-325044.38131663034</v>
+        <v>-327292.90511176601</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23034,7 +23076,7 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-64.441788524312116</v>
+        <v>-64.887570402808493</v>
       </c>
     </row>
   </sheetData>
@@ -29707,7 +29749,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29778,7 +29820,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31084,7 +31126,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-48.033175355450226</v>
+        <v>-43.893364928909946</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31121,7 +31163,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>8.6885518217842606</v>
+        <v>7.9397161023635849</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31182,7 +31224,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.8395901395901388</v>
+        <v>5.3362964062964062</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31243,7 +31285,7 @@
       </c>
       <c r="AC153" s="140">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>511209.39999999997</v>
+        <v>467150.06</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31304,7 +31346,7 @@
       </c>
       <c r="AC154" s="140">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>539210.39999999991</v>
+        <v>495151.06</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31341,7 +31383,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="178">
         <f ca="1">AC154/AC5</f>
-        <v>9.4545237761256828</v>
+        <v>8.681986604011783</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31378,7 +31420,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="178">
         <f ca="1">AC154/AC12</f>
-        <v>-7002.7324675324662</v>
+        <v>-6430.5332467532471</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31513,7 +31555,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-45.461040462427739</v>
+        <v>-41.542913294797685</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31550,7 +31592,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-69.927428349111651</v>
+        <v>-64.213598755025288</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31587,7 +31629,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-2.1996856865308032E-2</v>
+        <v>-2.4071494286011651E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31624,7 +31666,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-2.0818944252590038E-2</v>
+        <v>-2.2782486638233554E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31735,7 +31777,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="151">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.1278767565698128E-3</v>
+        <v>3.422883002519576E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32238,7 +32280,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="151">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-2.425620499153576E-2</v>
+        <v>-2.6543933227794084E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34039,7 +34081,7 @@
       </c>
       <c r="C5" s="167">
         <f ca="1">Overview!C5</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -34055,7 +34097,7 @@
       </c>
       <c r="C6" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>511209.39999999997</v>
+        <v>467150.06</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34075,7 +34117,7 @@
       </c>
       <c r="C7" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>539210.39999999991</v>
+        <v>495151.06</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -34095,7 +34137,7 @@
       </c>
       <c r="C8" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-48.033175355450226</v>
+        <v>-43.893364928909946</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>238</v>
@@ -34115,7 +34157,7 @@
       </c>
       <c r="C9" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>8.6885518217842606</v>
+        <v>7.9397161023635849</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>239</v>
@@ -34135,7 +34177,7 @@
       </c>
       <c r="C10" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>5.8395901395901388</v>
+        <v>5.3362964062964062</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34155,7 +34197,7 @@
       </c>
       <c r="C11" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>9.4545237761256828</v>
+        <v>8.681986604011783</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34164,7 +34206,7 @@
       </c>
       <c r="C12" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-7002.7324675324662</v>
+        <v>-6430.5332467532471</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34400,7 +34442,7 @@
       </c>
       <c r="C38" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-2.0818944252590038E-2</v>
+        <v>-2.2782486638233554E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>265</v>
@@ -34416,7 +34458,7 @@
       </c>
       <c r="C39" s="210">
         <f ca="1">Statement!AC161</f>
-        <v>-2.1996856865308032E-2</v>
+        <v>-2.4071494286011651E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>267</v>
@@ -34457,7 +34499,7 @@
       </c>
       <c r="C42" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>3.1278767565698128E-3</v>
+        <v>3.422883002519576E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34501,7 +34543,7 @@
       </c>
       <c r="F48" s="170">
         <f ca="1">Statement!AC176</f>
-        <v>-2.425620499153576E-2</v>
+        <v>-2.6543933227794084E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34680,7 +34722,7 @@
       </c>
       <c r="I6" s="167">
         <f ca="1">Statement!AC116</f>
-        <v>101.35</v>
+        <v>92.614999999999995</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34709,7 +34751,7 @@
       </c>
       <c r="I7" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>511209.39999999997</v>
+        <v>467150.06</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34738,7 +34780,7 @@
       </c>
       <c r="I8" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>539210.39999999991</v>
+        <v>495151.06</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34767,7 +34809,7 @@
       </c>
       <c r="I9" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-48.033175355450226</v>
+        <v>-43.893364928909946</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34796,7 +34838,7 @@
       </c>
       <c r="I10" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>8.6885518217842606</v>
+        <v>7.9397161023635849</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34825,7 +34867,7 @@
       </c>
       <c r="I11" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>5.8395901395901388</v>
+        <v>5.3362964062964062</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34854,7 +34896,7 @@
       </c>
       <c r="I12" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>9.4545237761256828</v>
+        <v>8.681986604011783</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34883,7 +34925,7 @@
       </c>
       <c r="I13" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-7002.7324675324662</v>
+        <v>-6430.5332467532471</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35656,7 +35698,7 @@
       </c>
       <c r="I51" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-2.0818944252590038E-2</v>
+        <v>-2.2782486638233554E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35685,7 +35727,7 @@
       </c>
       <c r="I52" s="170">
         <f ca="1">Statement!AC161</f>
-        <v>-2.1996856865308032E-2</v>
+        <v>-2.4071494286011651E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35772,7 +35814,7 @@
       </c>
       <c r="I55" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>3.1278767565698128E-3</v>
+        <v>3.422883002519576E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36008,7 +36050,7 @@
       </c>
       <c r="I68" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-2.425620499153576E-2</v>
+        <v>-2.6543933227794084E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C962BDB8-5AA7-2E4E-ABAA-79B74E68E6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2B25B5-4A7B-B049-8806-86948AA59711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2397,6 +2397,9 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2409,6 +2412,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2416,12 +2425,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2442,18 +2445,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -12881,9 +12881,9 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>32.89</v>
-    <v>2.3628999999999998</v>
-    <v>0.58499999999999996</v>
-    <v>6.3570000000000007E-3</v>
+    <v>2.3437000000000001</v>
+    <v>-7.47</v>
+    <v>-8.0356999999999998E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12891,24 +12891,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>93.73</v>
+    <v>89.185000000000002</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46315.719771180469</v>
+    <v>46317.999979849221</v>
     <v>0</v>
-    <v>88.77</v>
-    <v>489476665435</v>
+    <v>84.644999999999996</v>
+    <v>451820548810</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>90.8</v>
+    <v>87.92</v>
     <v>0</v>
-    <v>92.03</v>
-    <v>92.614999999999995</v>
+    <v>92.96</v>
+    <v>85.49</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>57381397</v>
-    <v>109100108</v>
+    <v>1265141</v>
+    <v>107288207</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -12947,17 +12947,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
     <v>6</v>
-    <v>50.9</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -13744,18 +13744,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="236" t="s">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="E2" s="236" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>282</v>
       </c>
-      <c r="F2" s="237"/>
-      <c r="H2" s="236" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>320</v>
       </c>
-      <c r="I2" s="237"/>
+      <c r="I2" s="240"/>
       <c r="K2" s="131" t="s">
         <v>421</v>
       </c>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="F3" s="182">
         <f ca="1">Statement!AC153</f>
-        <v>467150.06</v>
+        <v>431211.56</v>
       </c>
       <c r="H3" s="180" t="str">
         <f>'AVG target price'!B5</f>
@@ -13781,7 +13781,7 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.065822156934358</v>
+        <v>-10.216721006760988</v>
       </c>
       <c r="K3" s="234" t="s">
         <v>422</v>
@@ -13800,7 +13800,7 @@
       </c>
       <c r="F4" s="183">
         <f ca="1">Statement!AC154</f>
-        <v>495151.06</v>
+        <v>459212.56</v>
       </c>
       <c r="H4" s="180" t="str">
         <f>'AVG target price'!B6</f>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>36.708403191629159</v>
+        <v>37.300943672630481</v>
       </c>
       <c r="K4" s="234" t="s">
         <v>423</v>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="C5" s="203" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
       <c r="E5" s="180" t="s">
         <v>238</v>
@@ -13834,8 +13834,8 @@
         <v>PS price</v>
       </c>
       <c r="I5" s="206">
-        <f>'AVG target price'!C7</f>
-        <v>48.738460839691712</v>
+        <f ca="1">'AVG target price'!C7</f>
+        <v>41.78867320720358</v>
       </c>
       <c r="K5" s="234" t="s">
         <v>424</v>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="F6" s="185">
         <f ca="1">Statement!AC150</f>
-        <v>-43.893364928909946</v>
+        <v>-40.516587677725113</v>
       </c>
       <c r="H6" s="180" t="str">
         <f>'AVG target price'!B8</f>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.243324996427159</v>
+        <v>-21.475926743674265</v>
       </c>
       <c r="K6" s="235" t="s">
         <v>425</v>
@@ -13874,14 +13874,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.58499999999999996</v>
+        <v>-7.47</v>
       </c>
       <c r="E7" s="181" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="186">
         <f ca="1">Statement!AC151</f>
-        <v>7.9397161023635849</v>
+        <v>7.3289027651143215</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13889,7 +13889,7 @@
       </c>
       <c r="I7" s="206">
         <f ca="1">'AVG target price'!C9</f>
-        <v>41.010906867812473</v>
+        <v>41.66470829100507</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="F8" s="187">
         <f ca="1">Statement!AC161</f>
-        <v>-2.4071494286011651E-2</v>
+        <v>-2.6077686785576898E-2</v>
       </c>
       <c r="H8" s="179" t="str">
         <f>'AVG target price'!B10</f>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="I8" s="207">
         <f ca="1">'AVG target price'!C10</f>
-        <v>19.029724749154365</v>
+        <v>17.812335484080776</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13922,14 +13922,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.3570000000000007E-3</v>
+        <v>-8.0356999999999998E-2</v>
       </c>
       <c r="E9" s="180" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="187">
         <f ca="1">Statement!AC162</f>
-        <v>-2.2782486638233554E-2</v>
+        <v>-2.4681249268920347E-2</v>
       </c>
       <c r="H9" s="179" t="str">
         <f>'AVG target price'!B12</f>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="I9" s="208">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.79452869676451576</v>
+        <v>-0.79164422173259119</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -13975,7 +13975,7 @@
         <v>401</v>
       </c>
       <c r="I11" s="207">
-        <f>DDM!C26</f>
+        <f ca="1">DDM!C26</f>
         <v>0</v>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="C13" s="204" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3628999999999998</v>
+        <v>2.3437000000000001</v>
       </c>
       <c r="E13" s="180" t="s">
         <v>99</v>
@@ -14010,10 +14010,10 @@
         <f>Statement!AC125</f>
         <v>-0.12784720477028169</v>
       </c>
-      <c r="H13" s="256" t="s">
+      <c r="H13" s="238" t="s">
         <v>418</v>
       </c>
-      <c r="I13" s="254">
+      <c r="I13" s="236">
         <f>'Reverse DCF'!C17</f>
         <v>0.65</v>
       </c>
@@ -14024,7 +14024,7 @@
       </c>
       <c r="C14" s="205" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>109100108</v>
+        <v>107288207</v>
       </c>
       <c r="E14" s="181" t="s">
         <v>100</v>
@@ -14036,9 +14036,9 @@
       <c r="H14" s="181" t="s">
         <v>427</v>
       </c>
-      <c r="I14" s="255">
+      <c r="I14" s="237">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>-64.887570402808493</v>
+        <v>-66.956102438761761</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14047,7 +14047,7 @@
       </c>
       <c r="F15" s="187">
         <f ca="1">Statement!AC176</f>
-        <v>-2.6543933227794084E-2</v>
+        <v>-2.875618640650543E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14058,16 +14058,16 @@
         <f>Statement!AC175</f>
         <v>-2.4583663758921492</v>
       </c>
-      <c r="H16" s="236" t="s">
+      <c r="H16" s="239" t="s">
         <v>419</v>
       </c>
-      <c r="I16" s="237"/>
+      <c r="I16" s="240"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="238" t="s">
+      <c r="B17" s="241" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="238"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="179" t="s">
         <v>291</v>
       </c>
@@ -14080,7 +14080,7 @@
       </c>
       <c r="I17" s="232">
         <f ca="1">DCF!C15</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14101,8 +14101,8 @@
         <v>420</v>
       </c>
       <c r="I18" s="233">
-        <f>Multiples!C54</f>
-        <v>0.12</v>
+        <f ca="1">Multiples!C54</f>
+        <v>0.15499650000000001</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14154,14 +14154,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="238" t="s">
+      <c r="B25" s="241" t="s">
         <v>102</v>
       </c>
-      <c r="C25" s="238"/>
-      <c r="E25" s="236" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>373</v>
       </c>
-      <c r="F25" s="237"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="179" t="s">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -14206,7 +14206,7 @@
         <v>391</v>
       </c>
       <c r="C29" s="213">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -14468,36 +14468,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="239" t="s">
+      <c r="C2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="239" t="s">
+      <c r="S2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="T2" s="239"/>
-      <c r="U2" s="239"/>
-      <c r="V2" s="239"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="239"/>
-      <c r="Y2" s="239"/>
-      <c r="Z2" s="239"/>
-      <c r="AA2" s="239" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="AB2" s="239"/>
-      <c r="AC2" s="239"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="84" t="s">
         <v>110</v>
       </c>
@@ -14508,32 +14508,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="248" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="246" t="s">
+      <c r="S4" s="249" t="s">
         <v>111</v>
       </c>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
-      <c r="AA4" s="247"/>
-      <c r="AB4" s="247"/>
-      <c r="AC4" s="247"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
+      <c r="AA4" s="250"/>
+      <c r="AB4" s="250"/>
+      <c r="AC4" s="250"/>
       <c r="AE4" s="86"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -15227,33 +15227,33 @@
       <c r="Q12" s="90"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="245" t="s">
+      <c r="C13" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="E13" s="245"/>
-      <c r="F13" s="245"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="245"/>
-      <c r="I13" s="245"/>
-      <c r="J13" s="245"/>
-      <c r="K13" s="245"/>
-      <c r="L13" s="245"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="248"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
       <c r="O13" s="5"/>
       <c r="Q13" s="90"/>
-      <c r="S13" s="246" t="s">
+      <c r="S13" s="249" t="s">
         <v>117</v>
       </c>
-      <c r="T13" s="247"/>
-      <c r="U13" s="247"/>
-      <c r="V13" s="247"/>
-      <c r="W13" s="247"/>
-      <c r="X13" s="247"/>
-      <c r="Y13" s="247"/>
-      <c r="Z13" s="247"/>
-      <c r="AA13" s="247"/>
-      <c r="AB13" s="247"/>
-      <c r="AC13" s="247"/>
+      <c r="T13" s="250"/>
+      <c r="U13" s="250"/>
+      <c r="V13" s="250"/>
+      <c r="W13" s="250"/>
+      <c r="X13" s="250"/>
+      <c r="Y13" s="250"/>
+      <c r="Z13" s="250"/>
+      <c r="AA13" s="250"/>
+      <c r="AB13" s="250"/>
+      <c r="AC13" s="250"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B14" s="16" t="s">
@@ -15890,35 +15890,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="239" t="s">
+      <c r="C2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="P2" s="239" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="Q2" s="239"/>
-      <c r="R2" s="239"/>
-      <c r="S2" s="239"/>
-      <c r="T2" s="239"/>
-      <c r="U2" s="239"/>
-      <c r="V2" s="239"/>
-      <c r="W2" s="239"/>
-      <c r="X2" s="239" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>109</v>
       </c>
-      <c r="Y2" s="239"/>
-      <c r="Z2" s="239"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="84" t="s">
         <v>110</v>
       </c>
@@ -15927,31 +15927,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="248" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
-      <c r="P4" s="247" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="P4" s="250" t="s">
         <v>111</v>
       </c>
-      <c r="Q4" s="247"/>
-      <c r="R4" s="247"/>
-      <c r="S4" s="247"/>
-      <c r="T4" s="247"/>
-      <c r="U4" s="247"/>
-      <c r="V4" s="247"/>
-      <c r="W4" s="247"/>
-      <c r="X4" s="247"/>
-      <c r="Y4" s="247"/>
-      <c r="Z4" s="247"/>
+      <c r="Q4" s="250"/>
+      <c r="R4" s="250"/>
+      <c r="S4" s="250"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
       <c r="AB4" s="86"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -16146,32 +16146,32 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="245" t="s">
+      <c r="C9" s="248" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="245"/>
-      <c r="H9" s="245"/>
-      <c r="I9" s="245"/>
-      <c r="J9" s="245"/>
-      <c r="K9" s="245"/>
-      <c r="L9" s="245"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="90"/>
-      <c r="P9" s="247" t="s">
+      <c r="P9" s="250" t="s">
         <v>121</v>
       </c>
-      <c r="Q9" s="247"/>
-      <c r="R9" s="247"/>
-      <c r="S9" s="247"/>
-      <c r="T9" s="247"/>
-      <c r="U9" s="247"/>
-      <c r="V9" s="247"/>
-      <c r="W9" s="247"/>
-      <c r="X9" s="247"/>
-      <c r="Y9" s="247"/>
-      <c r="Z9" s="247"/>
+      <c r="Q9" s="250"/>
+      <c r="R9" s="250"/>
+      <c r="S9" s="250"/>
+      <c r="T9" s="250"/>
+      <c r="U9" s="250"/>
+      <c r="V9" s="250"/>
+      <c r="W9" s="250"/>
+      <c r="X9" s="250"/>
+      <c r="Y9" s="250"/>
+      <c r="Z9" s="250"/>
       <c r="AB9" s="86">
         <f>AB4</f>
         <v>0</v>
@@ -16741,31 +16741,31 @@
       </c>
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
-      <c r="C18" s="245" t="s">
+      <c r="C18" s="248" t="s">
         <v>123</v>
       </c>
-      <c r="D18" s="245"/>
-      <c r="E18" s="245"/>
-      <c r="F18" s="245"/>
-      <c r="G18" s="245"/>
-      <c r="H18" s="245"/>
-      <c r="I18" s="245"/>
-      <c r="J18" s="245"/>
-      <c r="K18" s="245"/>
-      <c r="L18" s="245"/>
-      <c r="P18" s="247" t="s">
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
+      <c r="P18" s="250" t="s">
         <v>123</v>
       </c>
-      <c r="Q18" s="247"/>
-      <c r="R18" s="247"/>
-      <c r="S18" s="247"/>
-      <c r="T18" s="247"/>
-      <c r="U18" s="247"/>
-      <c r="V18" s="247"/>
-      <c r="W18" s="247"/>
-      <c r="X18" s="247"/>
-      <c r="Y18" s="247"/>
-      <c r="Z18" s="247"/>
+      <c r="Q18" s="250"/>
+      <c r="R18" s="250"/>
+      <c r="S18" s="250"/>
+      <c r="T18" s="250"/>
+      <c r="U18" s="250"/>
+      <c r="V18" s="250"/>
+      <c r="W18" s="250"/>
+      <c r="X18" s="250"/>
+      <c r="Y18" s="250"/>
+      <c r="Z18" s="250"/>
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -17325,60 +17325,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="249" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="239"/>
-      <c r="J3" s="239"/>
-      <c r="K3" s="239"/>
-      <c r="L3" s="239"/>
-      <c r="P3" s="250"/>
-      <c r="Q3" s="250"/>
-      <c r="R3" s="250"/>
-      <c r="S3" s="250"/>
-      <c r="T3" s="250"/>
-      <c r="U3" s="250"/>
-      <c r="V3" s="250"/>
-      <c r="W3" s="250"/>
-      <c r="X3" s="250"/>
-      <c r="Y3" s="250"/>
-      <c r="Z3" s="250"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="248" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
-      <c r="P5" s="250"/>
-      <c r="Q5" s="250"/>
-      <c r="R5" s="250"/>
-      <c r="S5" s="250"/>
-      <c r="T5" s="250"/>
-      <c r="U5" s="250"/>
-      <c r="V5" s="250"/>
-      <c r="W5" s="250"/>
-      <c r="X5" s="250"/>
-      <c r="Y5" s="250"/>
-      <c r="Z5" s="250"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -17564,30 +17564,30 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="245" t="s">
+      <c r="C11" s="248" t="s">
         <v>127</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="245"/>
-      <c r="G11" s="245"/>
-      <c r="H11" s="245"/>
-      <c r="I11" s="245"/>
-      <c r="J11" s="245"/>
-      <c r="K11" s="245"/>
-      <c r="L11" s="245"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="90"/>
-      <c r="P11" s="250"/>
-      <c r="Q11" s="250"/>
-      <c r="R11" s="250"/>
-      <c r="S11" s="250"/>
-      <c r="T11" s="250"/>
-      <c r="U11" s="250"/>
-      <c r="V11" s="250"/>
-      <c r="W11" s="250"/>
-      <c r="X11" s="250"/>
-      <c r="Y11" s="250"/>
-      <c r="Z11" s="250"/>
+      <c r="P11" s="253"/>
+      <c r="Q11" s="253"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
       <c r="AB11" s="109"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -17829,18 +17829,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="245" t="s">
+      <c r="C18" s="248" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="245"/>
-      <c r="E18" s="245"/>
-      <c r="F18" s="245"/>
-      <c r="G18" s="245"/>
-      <c r="H18" s="245"/>
-      <c r="I18" s="245"/>
-      <c r="J18" s="245"/>
-      <c r="K18" s="245"/>
-      <c r="L18" s="245"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -18053,23 +18053,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="250"/>
-      <c r="C25" s="250"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="253"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="108"/>
-      <c r="C26" s="245" t="s">
+      <c r="C26" s="248" t="s">
         <v>138</v>
       </c>
-      <c r="D26" s="245"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="245"/>
-      <c r="G26" s="245"/>
-      <c r="H26" s="245"/>
-      <c r="I26" s="245"/>
-      <c r="J26" s="245"/>
-      <c r="K26" s="245"/>
-      <c r="L26" s="245"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -18261,18 +18261,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="108"/>
-      <c r="C33" s="245" t="s">
+      <c r="C33" s="248" t="s">
         <v>142</v>
       </c>
-      <c r="D33" s="245"/>
-      <c r="E33" s="245"/>
-      <c r="F33" s="245"/>
-      <c r="G33" s="245"/>
-      <c r="H33" s="245"/>
-      <c r="I33" s="245"/>
-      <c r="J33" s="245"/>
-      <c r="K33" s="245"/>
-      <c r="L33" s="245"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -18456,18 +18456,18 @@
       <c r="C39" s="124"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="245" t="s">
+      <c r="C40" s="248" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="245"/>
-      <c r="E40" s="245"/>
-      <c r="F40" s="245"/>
-      <c r="G40" s="245"/>
-      <c r="H40" s="245"/>
-      <c r="I40" s="245"/>
-      <c r="J40" s="245"/>
-      <c r="K40" s="245"/>
-      <c r="L40" s="245"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
+      <c r="I40" s="248"/>
+      <c r="J40" s="248"/>
+      <c r="K40" s="248"/>
+      <c r="L40" s="248"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -18731,6 +18731,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18738,12 +18744,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -18781,60 +18781,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="239" t="s">
+      <c r="C2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
-      <c r="S2" s="250"/>
-      <c r="T2" s="250"/>
-      <c r="U2" s="250"/>
-      <c r="V2" s="250"/>
-      <c r="W2" s="250"/>
-      <c r="X2" s="250"/>
-      <c r="Y2" s="250"/>
-      <c r="Z2" s="250"/>
-      <c r="AA2" s="250"/>
-      <c r="AB2" s="250"/>
-      <c r="AC2" s="250"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="108"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="109"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -19197,18 +19197,18 @@
       <c r="AE10" s="63"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="245" t="s">
+      <c r="C13" s="248" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="245"/>
-      <c r="E13" s="245"/>
-      <c r="F13" s="245"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="245"/>
-      <c r="I13" s="245"/>
-      <c r="J13" s="245"/>
-      <c r="K13" s="245"/>
-      <c r="L13" s="245"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="248"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -19301,18 +19301,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="245" t="s">
+      <c r="C18" s="248" t="s">
         <v>154</v>
       </c>
-      <c r="D18" s="245"/>
-      <c r="E18" s="245"/>
-      <c r="F18" s="245"/>
-      <c r="G18" s="245"/>
-      <c r="H18" s="245"/>
-      <c r="I18" s="245"/>
-      <c r="J18" s="245"/>
-      <c r="K18" s="245"/>
-      <c r="L18" s="245"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -19504,18 +19504,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="245" t="s">
+      <c r="C25" s="248" t="s">
         <v>257</v>
       </c>
-      <c r="D25" s="245"/>
-      <c r="E25" s="245"/>
-      <c r="F25" s="245"/>
-      <c r="G25" s="245"/>
-      <c r="H25" s="245"/>
-      <c r="I25" s="245"/>
-      <c r="J25" s="245"/>
-      <c r="K25" s="245"/>
-      <c r="L25" s="245"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="248"/>
+      <c r="K25" s="248"/>
+      <c r="L25" s="248"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -19653,18 +19653,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="245" t="s">
+      <c r="C31" s="248" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="245"/>
-      <c r="E31" s="245"/>
-      <c r="F31" s="245"/>
-      <c r="G31" s="245"/>
-      <c r="H31" s="245"/>
-      <c r="I31" s="245"/>
-      <c r="J31" s="245"/>
-      <c r="K31" s="245"/>
-      <c r="L31" s="245"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -19803,16 +19803,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19914,10 +19914,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="239" t="s">
+      <c r="B4" s="242" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="239"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>467150.06</v>
+        <v>431211.56</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19961,7 +19961,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.3628999999999998</v>
+        <v>2.3437000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20002,10 +20002,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="239" t="s">
+      <c r="B15" s="242" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="239"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -20013,7 +20013,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>9.7620751810949258E-2</v>
+        <v>0.10490327153235289</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20022,7 +20022,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.90237924818905069</v>
+        <v>0.8950967284676471</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20040,7 +20040,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15769049999999998</v>
+        <v>0.15499650000000001</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20049,7 +20049,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
   </sheetData>
@@ -20094,60 +20094,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="249" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="239"/>
-      <c r="J3" s="239"/>
-      <c r="K3" s="239"/>
-      <c r="L3" s="239"/>
-      <c r="P3" s="250"/>
-      <c r="Q3" s="250"/>
-      <c r="R3" s="250"/>
-      <c r="S3" s="250"/>
-      <c r="T3" s="250"/>
-      <c r="U3" s="250"/>
-      <c r="V3" s="250"/>
-      <c r="W3" s="250"/>
-      <c r="X3" s="250"/>
-      <c r="Y3" s="250"/>
-      <c r="Z3" s="250"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="248" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
-      <c r="P5" s="250"/>
-      <c r="Q5" s="250"/>
-      <c r="R5" s="250"/>
-      <c r="S5" s="250"/>
-      <c r="T5" s="250"/>
-      <c r="U5" s="250"/>
-      <c r="V5" s="250"/>
-      <c r="W5" s="250"/>
-      <c r="X5" s="250"/>
-      <c r="Y5" s="250"/>
-      <c r="Z5" s="250"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-29090.04871693307</v>
+        <v>-29853.410056166082</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20354,23 +20354,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8069.6055133726877</v>
+        <v>-8092.4554617429258</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5684.0324398624853</v>
+        <v>-5716.2679021507702</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4157.3814066987125</v>
+        <v>-4192.7977087948966</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-3961.3946506947227</v>
+        <v>-4006.4540306097533</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1821.9729317837498</v>
+        <v>-1847.9149847948663</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20389,14 +20389,14 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-14677.620017164549</v>
+        <v>-15277.250670009211</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="239" t="s">
+      <c r="B13" s="242" t="s">
         <v>179</v>
       </c>
-      <c r="C13" s="239"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -20412,14 +20412,14 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="239" t="s">
+      <c r="B18" s="242" t="s">
         <v>181</v>
       </c>
-      <c r="C18" s="239"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -20427,7 +20427,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23694.386942412355</v>
+        <v>-23855.890088093212</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20436,7 +20436,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-14677.620017164549</v>
+        <v>-15277.250670009211</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-38372.006959576902</v>
+        <v>-39133.140758102425</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-50772.006959576902</v>
+        <v>-51533.140758102425</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20490,7 +20490,7 @@
       </c>
       <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-10.065822156934358</v>
+        <v>-10.216721006760988</v>
       </c>
     </row>
   </sheetData>
@@ -20533,37 +20533,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="239" t="s">
+      <c r="C2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="248" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -20759,23 +20759,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8069.6055133726877</v>
+        <v>-8092.4554617429258</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5684.0324398624853</v>
+        <v>-5716.2679021507702</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4157.3814066987125</v>
+        <v>-4192.7977087948966</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-3961.3946506947227</v>
+        <v>-4006.4540306097533</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1821.9729317837498</v>
+        <v>-1847.9149847948663</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -20783,18 +20783,18 @@
       <c r="N10" s="90"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="245" t="s">
+      <c r="C11" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="245"/>
-      <c r="E11" s="245"/>
-      <c r="F11" s="245"/>
-      <c r="G11" s="245"/>
-      <c r="H11" s="245"/>
-      <c r="I11" s="245"/>
-      <c r="J11" s="245"/>
-      <c r="K11" s="245"/>
-      <c r="L11" s="245"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="90"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -20988,18 +20988,18 @@
       <c r="N16" s="90"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="245" t="s">
+      <c r="C17" s="248" t="s">
         <v>191</v>
       </c>
-      <c r="D17" s="245"/>
-      <c r="E17" s="245"/>
-      <c r="F17" s="245"/>
-      <c r="G17" s="245"/>
-      <c r="H17" s="245"/>
-      <c r="I17" s="245"/>
-      <c r="J17" s="245"/>
-      <c r="K17" s="245"/>
-      <c r="L17" s="245"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
       <c r="N17" s="90"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -21133,18 +21133,18 @@
       <c r="N21" s="90"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="245" t="s">
+      <c r="C22" s="248" t="s">
         <v>194</v>
       </c>
-      <c r="D22" s="245"/>
-      <c r="E22" s="245"/>
-      <c r="F22" s="245"/>
-      <c r="G22" s="245"/>
-      <c r="H22" s="245"/>
-      <c r="I22" s="245"/>
-      <c r="J22" s="245"/>
-      <c r="K22" s="245"/>
-      <c r="L22" s="245"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+      <c r="K22" s="248"/>
+      <c r="L22" s="248"/>
       <c r="N22" s="90"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -21228,18 +21228,18 @@
       <c r="N26" s="90"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="245" t="s">
+      <c r="C27" s="248" t="s">
         <v>195</v>
       </c>
-      <c r="D27" s="245"/>
-      <c r="E27" s="245"/>
-      <c r="F27" s="245"/>
-      <c r="G27" s="245"/>
-      <c r="H27" s="245"/>
-      <c r="I27" s="245"/>
-      <c r="J27" s="245"/>
-      <c r="K27" s="245"/>
-      <c r="L27" s="245"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
       <c r="N27" s="90"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -21540,10 +21540,10 @@
       <c r="N38" s="90"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="239" t="s">
+      <c r="B39" s="242" t="s">
         <v>200</v>
       </c>
-      <c r="C39" s="239"/>
+      <c r="C39" s="242"/>
       <c r="N39" s="90"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="C41" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21587,7 +21587,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>219429.59970920609</v>
+        <v>222553.9349880465</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="C45" s="93">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>197557.18569857749</v>
+        <v>200545.95988474815</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21623,7 +21623,7 @@
       </c>
       <c r="C48" s="107">
         <f ca="1">C45+C46-C47</f>
-        <v>185157.18569857749</v>
+        <v>188145.95988474815</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21641,14 +21641,14 @@
       </c>
       <c r="C50" s="231">
         <f ca="1">C48/C49</f>
-        <v>36.708403191629159</v>
+        <v>37.300943672630481</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="239" t="s">
+      <c r="B52" s="242" t="s">
         <v>205</v>
       </c>
-      <c r="C52" s="239"/>
+      <c r="C52" s="242"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -21664,8 +21664,8 @@
         <v>379</v>
       </c>
       <c r="C54" s="134">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.15499650000000001</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21699,15 +21699,15 @@
         <v>204</v>
       </c>
       <c r="C58" s="231">
-        <f>C57/(1+C54)^5</f>
-        <v>48.738460839691712</v>
+        <f ca="1">C57/(1+C54)^5</f>
+        <v>41.78867320720358</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="239" t="s">
+      <c r="B60" s="242" t="s">
         <v>317</v>
       </c>
-      <c r="C60" s="239"/>
+      <c r="C60" s="242"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="C62" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21750,7 +21750,7 @@
       </c>
       <c r="C65" s="63">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>-72878.917271349987</v>
+        <v>-73916.599391794647</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21759,7 +21759,7 @@
       </c>
       <c r="C66" s="93">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>-94751.331281978593</v>
+        <v>-95924.574495092995</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C69" s="93">
         <f ca="1">C66+C67-C68</f>
-        <v>-107151.33128197859</v>
+        <v>-108324.57449509299</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21804,14 +21804,14 @@
       </c>
       <c r="C71" s="231">
         <f ca="1">C69/C70</f>
-        <v>-21.243324996427159</v>
+        <v>-21.475926743674265</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="239" t="s">
+      <c r="B73" s="242" t="s">
         <v>414</v>
       </c>
-      <c r="C73" s="239"/>
+      <c r="C73" s="242"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="C75" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C78" s="63">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>241131.42825187472</v>
+        <v>244564.76372312792</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21863,7 +21863,7 @@
       </c>
       <c r="C79" s="93">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>219259.0142412461</v>
+        <v>222556.78861982957</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="C82" s="93">
         <f ca="1">C79+C80-C81</f>
-        <v>206859.0142412461</v>
+        <v>210156.78861982957</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21908,22 +21908,22 @@
       </c>
       <c r="C84" s="231">
         <f ca="1">C82/C83</f>
-        <v>41.010906867812473</v>
+        <v>41.66470829100507</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21961,10 +21961,10 @@
       <c r="N3" s="90"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="239" t="s">
+      <c r="B4" s="242" t="s">
         <v>209</v>
       </c>
-      <c r="C4" s="239"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="90"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.065822156934358</v>
+        <v>-10.216721006760988</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C50</f>
-        <v>36.708403191629159</v>
+        <v>37.300943672630481</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21990,8 +21990,8 @@
         <v>212</v>
       </c>
       <c r="C7" s="132">
-        <f>Multiples!C58</f>
-        <v>48.738460839691712</v>
+        <f ca="1">Multiples!C58</f>
+        <v>41.78867320720358</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C71</f>
-        <v>-21.243324996427159</v>
+        <v>-21.475926743674265</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22009,7 +22009,7 @@
       </c>
       <c r="C9" s="132">
         <f ca="1">Multiples!C84</f>
-        <v>41.010906867812473</v>
+        <v>41.66470829100507</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="C10" s="231">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>19.029724749154365</v>
+        <v>17.812335484080776</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="C11" s="132">
         <f ca="1">Overview!C5</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="C12" s="151">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.79452869676451576</v>
+        <v>-0.79164422173259119</v>
       </c>
     </row>
   </sheetData>
@@ -22131,37 +22131,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="239" t="s">
+      <c r="C2" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="239"/>
-      <c r="E2" s="239"/>
-      <c r="F2" s="239"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="239"/>
-      <c r="J2" s="239"/>
-      <c r="K2" s="239"/>
-      <c r="L2" s="239"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="85"/>
       <c r="B4" s="59"/>
-      <c r="C4" s="245" t="s">
+      <c r="C4" s="248" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
-      <c r="J4" s="245"/>
-      <c r="K4" s="245"/>
-      <c r="L4" s="245"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -22274,18 +22274,18 @@
       <c r="N8" s="90"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="245" t="s">
+      <c r="C9" s="248" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="245"/>
-      <c r="E9" s="245"/>
-      <c r="F9" s="245"/>
-      <c r="G9" s="245"/>
-      <c r="H9" s="245"/>
-      <c r="I9" s="245"/>
-      <c r="J9" s="245"/>
-      <c r="K9" s="245"/>
-      <c r="L9" s="245"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="90"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22406,18 +22406,18 @@
       <c r="N13" s="90"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="245" t="s">
+      <c r="C14" s="248" t="s">
         <v>394</v>
       </c>
-      <c r="D14" s="245"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="245"/>
-      <c r="G14" s="245"/>
-      <c r="H14" s="245"/>
-      <c r="I14" s="245"/>
-      <c r="J14" s="245"/>
-      <c r="K14" s="245"/>
-      <c r="L14" s="245"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="248"/>
+      <c r="I14" s="248"/>
+      <c r="J14" s="248"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
       <c r="N14" s="90"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -22507,10 +22507,10 @@
       <c r="N19" s="90"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="239" t="s">
+      <c r="B20" s="242" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="239"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="90"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -22544,8 +22544,8 @@
         <v>379</v>
       </c>
       <c r="C24" s="134">
-        <f>IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.12</v>
+        <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
+        <v>0.15499650000000001</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22561,7 +22561,7 @@
         <v>204</v>
       </c>
       <c r="C26" s="231">
-        <f>C23/(C24-C25)</f>
+        <f ca="1">C23/(C24-C25)</f>
         <v>0</v>
       </c>
     </row>
@@ -22611,60 +22611,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="242" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="239"/>
-      <c r="E3" s="239"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="248"/>
-      <c r="H3" s="249" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="239"/>
-      <c r="J3" s="239"/>
-      <c r="K3" s="239"/>
-      <c r="L3" s="239"/>
-      <c r="P3" s="250"/>
-      <c r="Q3" s="250"/>
-      <c r="R3" s="250"/>
-      <c r="S3" s="250"/>
-      <c r="T3" s="250"/>
-      <c r="U3" s="250"/>
-      <c r="V3" s="250"/>
-      <c r="W3" s="250"/>
-      <c r="X3" s="250"/>
-      <c r="Y3" s="250"/>
-      <c r="Z3" s="250"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="108"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="85"/>
       <c r="B5" s="59"/>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="248" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="245"/>
-      <c r="E5" s="245"/>
-      <c r="F5" s="245"/>
-      <c r="G5" s="245"/>
-      <c r="H5" s="245"/>
-      <c r="I5" s="245"/>
-      <c r="J5" s="245"/>
-      <c r="K5" s="245"/>
-      <c r="L5" s="245"/>
-      <c r="P5" s="250"/>
-      <c r="Q5" s="250"/>
-      <c r="R5" s="250"/>
-      <c r="S5" s="250"/>
-      <c r="T5" s="250"/>
-      <c r="U5" s="250"/>
-      <c r="V5" s="250"/>
-      <c r="W5" s="250"/>
-      <c r="X5" s="250"/>
-      <c r="Y5" s="250"/>
-      <c r="Z5" s="250"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="109"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -22799,7 +22799,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-465415.31768834975</v>
+        <v>-477628.43096523924</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22853,23 +22853,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6797.8787562005118</v>
+        <v>-6817.1276746698113</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9782.2689052787991</v>
+        <v>-9837.7464141998444</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-14076.85961564124</v>
+        <v>-14196.778926366451</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20256.852327126209</v>
+        <v>-20487.266432605596</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-29149.972181796635</v>
+        <v>-29565.022323552799</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22888,15 +22888,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-234829.07332572262</v>
+        <v>-244422.63892971983</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="255" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22913,7 +22913,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-64.887570402808493</v>
+        <v>-66.956102438761761</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22923,20 +22923,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="253" t="s">
+      <c r="E17" s="254" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="253"/>
-      <c r="G17" s="253"/>
-      <c r="H17" s="253"/>
-      <c r="I17" s="253"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="255" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14661537689667187</v>
+        <v>0.14337778080652697</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>467150.06</v>
+        <v>431211.56</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22997,15 +22997,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>479550.06</v>
+        <v>443611.56</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="255" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-80063.831786043389</v>
+        <v>-80903.9417713945</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23022,7 +23022,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-234829.07332572262</v>
+        <v>-244422.63892971983</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23031,7 +23031,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-314892.90511176601</v>
+        <v>-325326.58070111432</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-327292.90511176601</v>
+        <v>-337726.58070111432</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23076,21 +23076,21 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-64.887570402808493</v>
+        <v>-66.956102438761761</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29749,7 +29749,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29820,7 +29820,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31126,7 +31126,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-43.893364928909946</v>
+        <v>-40.516587677725113</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31163,7 +31163,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.9397161023635849</v>
+        <v>7.3289027651143215</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31224,7 +31224,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>5.3362964062964062</v>
+        <v>4.9257677457677449</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31285,7 +31285,7 @@
       </c>
       <c r="AC153" s="140">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>467150.06</v>
+        <v>431211.56</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="AC154" s="140">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>495151.06</v>
+        <v>459212.56</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31383,7 +31383,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="178">
         <f ca="1">AC154/AC5</f>
-        <v>8.681986604011783</v>
+        <v>8.051840370318418</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31420,7 +31420,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="178">
         <f ca="1">AC154/AC12</f>
-        <v>-6430.5332467532471</v>
+        <v>-5963.7994805194803</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31555,7 +31555,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-41.542913294797685</v>
+        <v>-38.346959537572253</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31592,7 +31592,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-64.213598755025288</v>
+        <v>-59.552919206328625</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31629,7 +31629,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-2.4071494286011651E-2</v>
+        <v>-2.6077686785576898E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31666,7 +31666,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-2.2782486638233554E-2</v>
+        <v>-2.4681249268920347E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31777,7 +31777,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="151">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.422883002519576E-3</v>
+        <v>3.7081566180646921E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32280,7 +32280,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="151">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-2.6543933227794084E-2</v>
+        <v>-2.875618640650543E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34065,15 +34065,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="239" t="s">
+      <c r="B4" s="242" t="s">
         <v>228</v>
       </c>
-      <c r="C4" s="239"/>
-      <c r="E4" s="239" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>235</v>
       </c>
-      <c r="F4" s="239"/>
-      <c r="G4" s="239"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -34081,7 +34081,7 @@
       </c>
       <c r="C5" s="167">
         <f ca="1">Overview!C5</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -34097,7 +34097,7 @@
       </c>
       <c r="C6" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>467150.06</v>
+        <v>431211.56</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34117,7 +34117,7 @@
       </c>
       <c r="C7" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>495151.06</v>
+        <v>459212.56</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -34137,7 +34137,7 @@
       </c>
       <c r="C8" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-43.893364928909946</v>
+        <v>-40.516587677725113</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>238</v>
@@ -34157,7 +34157,7 @@
       </c>
       <c r="C9" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>7.9397161023635849</v>
+        <v>7.3289027651143215</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>239</v>
@@ -34177,7 +34177,7 @@
       </c>
       <c r="C10" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>5.3362964062964062</v>
+        <v>4.9257677457677449</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34197,7 +34197,7 @@
       </c>
       <c r="C11" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>8.681986604011783</v>
+        <v>8.051840370318418</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34206,18 +34206,18 @@
       </c>
       <c r="C12" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-6430.5332467532471</v>
+        <v>-5963.7994805194803</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="239" t="s">
+      <c r="B15" s="242" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="239"/>
-      <c r="E15" s="239" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>241</v>
       </c>
-      <c r="F15" s="239"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -34268,14 +34268,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="239" t="s">
+      <c r="B21" s="242" t="s">
         <v>240</v>
       </c>
-      <c r="C21" s="239"/>
-      <c r="E21" s="239" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>244</v>
       </c>
-      <c r="F21" s="239"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -34344,14 +34344,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="239" t="s">
+      <c r="B29" s="242" t="s">
         <v>245</v>
       </c>
-      <c r="C29" s="239"/>
-      <c r="E29" s="239" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>251</v>
       </c>
-      <c r="F29" s="239"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -34427,14 +34427,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="239" t="s">
+      <c r="B37" s="242" t="s">
         <v>263</v>
       </c>
-      <c r="C37" s="239"/>
-      <c r="E37" s="239" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>266</v>
       </c>
-      <c r="F37" s="239"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -34442,7 +34442,7 @@
       </c>
       <c r="C38" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-2.2782486638233554E-2</v>
+        <v>-2.4681249268920347E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>265</v>
@@ -34458,7 +34458,7 @@
       </c>
       <c r="C39" s="210">
         <f ca="1">Statement!AC161</f>
-        <v>-2.4071494286011651E-2</v>
+        <v>-2.6077686785576898E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>267</v>
@@ -34499,18 +34499,18 @@
       </c>
       <c r="C42" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>3.422883002519576E-3</v>
+        <v>3.7081566180646921E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="239" t="s">
+      <c r="B45" s="242" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="239"/>
-      <c r="E45" s="239" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>280</v>
       </c>
-      <c r="F45" s="239"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -34543,18 +34543,18 @@
       </c>
       <c r="F48" s="170">
         <f ca="1">Statement!AC176</f>
-        <v>-2.6543933227794084E-2</v>
+        <v>-2.875618640650543E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="239" t="s">
+      <c r="B51" s="242" t="s">
         <v>277</v>
       </c>
-      <c r="C51" s="239"/>
-      <c r="E51" s="239" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>298</v>
       </c>
-      <c r="F51" s="239"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -34722,7 +34722,7 @@
       </c>
       <c r="I6" s="167">
         <f ca="1">Statement!AC116</f>
-        <v>92.614999999999995</v>
+        <v>85.49</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34751,7 +34751,7 @@
       </c>
       <c r="I7" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>467150.06</v>
+        <v>431211.56</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34780,7 +34780,7 @@
       </c>
       <c r="I8" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>495151.06</v>
+        <v>459212.56</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="I9" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-43.893364928909946</v>
+        <v>-40.516587677725113</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="I10" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>7.9397161023635849</v>
+        <v>7.3289027651143215</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34867,7 +34867,7 @@
       </c>
       <c r="I11" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>5.3362964062964062</v>
+        <v>4.9257677457677449</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="I12" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>8.681986604011783</v>
+        <v>8.051840370318418</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34925,7 +34925,7 @@
       </c>
       <c r="I13" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-6430.5332467532471</v>
+        <v>-5963.7994805194803</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35698,7 +35698,7 @@
       </c>
       <c r="I51" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-2.2782486638233554E-2</v>
+        <v>-2.4681249268920347E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35727,7 +35727,7 @@
       </c>
       <c r="I52" s="170">
         <f ca="1">Statement!AC161</f>
-        <v>-2.4071494286011651E-2</v>
+        <v>-2.6077686785576898E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35814,7 +35814,7 @@
       </c>
       <c r="I55" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>3.422883002519576E-3</v>
+        <v>3.7081566180646921E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36050,7 +36050,7 @@
       </c>
       <c r="I68" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-2.6543933227794084E-2</v>
+        <v>-2.875618640650543E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36588,14 +36588,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="240" t="s">
+      <c r="C3" s="245" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="241"/>
-      <c r="F3" s="242" t="s">
+      <c r="D3" s="246"/>
+      <c r="F3" s="247" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="241"/>
+      <c r="G3" s="246"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -37188,6 +37188,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -37204,18 +37216,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/INTC.xlsx
+++ b/INTC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2B25B5-4A7B-B049-8806-86948AA59711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86124CCD-0966-FE44-BB5F-2F6CCDA2FCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -121,7 +121,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -132,28 +132,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -163,28 +142,19 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="432">
   <si>
     <t>Ticker</t>
   </si>
@@ -1468,6 +1438,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2412,12 +2394,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2425,6 +2401,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2445,14 +2427,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -12862,7 +12844,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -12881,9 +12863,11 @@
     <v>Powered by Refinitiv</v>
     <v>142.35</v>
     <v>32.89</v>
-    <v>2.3437000000000001</v>
-    <v>-7.47</v>
-    <v>-8.0356999999999998E-2</v>
+    <v>2.3673000000000002</v>
+    <v>3.27</v>
+    <v>3.6145000000000004E-2</v>
+    <v>-0.15</v>
+    <v>-1.6000000000000001E-3</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
     <v>82300</v>
@@ -12891,49 +12875,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>89.185000000000002</v>
+    <v>94.98</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46317.999979849221</v>
+    <v>46322.903575474222</v>
     <v>0</v>
-    <v>84.644999999999996</v>
-    <v>451820548810</v>
+    <v>91.86</v>
+    <v>495422368060</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>87.92</v>
+    <v>92.465000000000003</v>
     <v>0</v>
-    <v>92.96</v>
-    <v>85.49</v>
+    <v>90.47</v>
+    <v>93.74</v>
+    <v>93.59</v>
     <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>1265141</v>
-    <v>107288207</v>
+    <v>90004459</v>
+    <v>98832404</v>
     <v>1989</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -12947,28 +12917,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
-    <v>6</v>
-    <v>49.39</v>
+    <v>3</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
-    <v>49.53</v>
+    <v>50.03</v>
+    <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -12990,6 +12960,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -13010,6 +12982,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -13019,11 +12992,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -13059,7 +13027,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -13070,13 +13038,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -13170,13 +13141,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -13248,6 +13225,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -13255,6 +13235,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -13773,7 +13756,7 @@
       </c>
       <c r="F3" s="182">
         <f ca="1">Statement!AC153</f>
-        <v>431211.56</v>
+        <v>472824.56</v>
       </c>
       <c r="H3" s="180" t="str">
         <f>'AVG target price'!B5</f>
@@ -13781,7 +13764,7 @@
       </c>
       <c r="I3" s="206">
         <f ca="1">'AVG target price'!C5</f>
-        <v>-10.216721006760988</v>
+        <v>-10.114257077363854</v>
       </c>
       <c r="K3" s="234" t="s">
         <v>422</v>
@@ -13800,7 +13783,7 @@
       </c>
       <c r="F4" s="183">
         <f ca="1">Statement!AC154</f>
-        <v>459212.56</v>
+        <v>500825.56</v>
       </c>
       <c r="H4" s="180" t="str">
         <f>'AVG target price'!B6</f>
@@ -13808,7 +13791,7 @@
       </c>
       <c r="I4" s="206">
         <f ca="1">'AVG target price'!C6</f>
-        <v>37.300943672630481</v>
+        <v>36.900584306209062</v>
       </c>
       <c r="K4" s="234" t="s">
         <v>423</v>
@@ -13820,7 +13803,7 @@
       </c>
       <c r="C5" s="203" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
       <c r="E5" s="180" t="s">
         <v>238</v>
@@ -13835,7 +13818,7 @@
       </c>
       <c r="I5" s="206">
         <f ca="1">'AVG target price'!C7</f>
-        <v>41.78867320720358</v>
+        <v>41.537762903381562</v>
       </c>
       <c r="K5" s="234" t="s">
         <v>424</v>
@@ -13845,16 +13828,16 @@
       <c r="B6" s="180" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="203" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="203" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>93.59</v>
       </c>
       <c r="E6" s="180" t="s">
         <v>232</v>
       </c>
       <c r="F6" s="185">
         <f ca="1">Statement!AC150</f>
-        <v>-40.516587677725113</v>
+        <v>-44.426540284360179</v>
       </c>
       <c r="H6" s="180" t="str">
         <f>'AVG target price'!B8</f>
@@ -13862,7 +13845,7 @@
       </c>
       <c r="I6" s="206">
         <f ca="1">'AVG target price'!C8</f>
-        <v>-21.475926743674265</v>
+        <v>-21.31879172435843</v>
       </c>
       <c r="K6" s="235" t="s">
         <v>425</v>
@@ -13874,14 +13857,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-7.47</v>
+        <v>3.27</v>
       </c>
       <c r="E7" s="181" t="s">
         <v>196</v>
       </c>
       <c r="F7" s="186">
         <f ca="1">Statement!AC151</f>
-        <v>7.3289027651143215</v>
+        <v>8.0361603135082067</v>
       </c>
       <c r="H7" s="180" t="str">
         <f>'AVG target price'!B9</f>
@@ -13889,23 +13872,23 @@
       </c>
       <c r="I7" s="206">
         <f ca="1">'AVG target price'!C9</f>
-        <v>41.66470829100507</v>
+        <v>41.22295893123777</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="180" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>-0.15</v>
       </c>
       <c r="E8" s="180" t="s">
         <v>260</v>
       </c>
       <c r="F8" s="187">
         <f ca="1">Statement!AC161</f>
-        <v>-2.6077686785576898E-2</v>
+        <v>-2.3782605539779914E-2</v>
       </c>
       <c r="H8" s="179" t="str">
         <f>'AVG target price'!B10</f>
@@ -13913,7 +13896,7 @@
       </c>
       <c r="I8" s="207">
         <f ca="1">'AVG target price'!C10</f>
-        <v>17.812335484080776</v>
+        <v>17.645651467821221</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -13922,14 +13905,14 @@
       </c>
       <c r="C9" s="72" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-8.0356999999999998E-2</v>
+        <v>3.6145000000000004E-2</v>
       </c>
       <c r="E9" s="180" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="187">
         <f ca="1">Statement!AC162</f>
-        <v>-2.4681249268920347E-2</v>
+        <v>-2.2509067633880952E-2</v>
       </c>
       <c r="H9" s="179" t="str">
         <f>'AVG target price'!B12</f>
@@ -13937,16 +13920,16 @@
       </c>
       <c r="I9" s="208">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-0.79164422173259119</v>
+        <v>-0.81175963870470214</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="180" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="72" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="72" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>-1.6000000000000001E-3</v>
       </c>
       <c r="E10" s="180" t="s">
         <v>288</v>
@@ -14001,7 +13984,7 @@
       </c>
       <c r="C13" s="204" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>2.3437000000000001</v>
+        <v>2.3673000000000002</v>
       </c>
       <c r="E13" s="180" t="s">
         <v>99</v>
@@ -14024,7 +14007,7 @@
       </c>
       <c r="C14" s="205" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>107288207</v>
+        <v>98832404</v>
       </c>
       <c r="E14" s="181" t="s">
         <v>100</v>
@@ -14038,7 +14021,7 @@
       </c>
       <c r="I14" s="237">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>-66.956102438761761</v>
+        <v>-65.550092584457488</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -14047,7 +14030,7 @@
       </c>
       <c r="F15" s="187">
         <f ca="1">Statement!AC176</f>
-        <v>-2.875618640650543E-2</v>
+        <v>-2.6225372049201504E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -14080,7 +14063,7 @@
       </c>
       <c r="I17" s="232">
         <f ca="1">DCF!C15</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -14102,7 +14085,7 @@
       </c>
       <c r="I18" s="233">
         <f ca="1">Multiples!C54</f>
-        <v>0.15499650000000001</v>
+        <v>0.15638849999999999</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -14170,12 +14153,12 @@
       <c r="C26" s="165">
         <v>0.21</v>
       </c>
-      <c r="E26" s="180" t="e" vm="5">
+      <c r="E26" s="180" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="218" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -14190,7 +14173,7 @@
       </c>
       <c r="F27" s="219">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -18731,12 +18714,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -18744,6 +18721,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -19803,16 +19786,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -19934,7 +19917,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Overview!C5</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19943,7 +19926,7 @@
       </c>
       <c r="C7" s="133">
         <f ca="1">C5*C6</f>
-        <v>431211.56</v>
+        <v>472824.56</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19961,7 +19944,7 @@
       </c>
       <c r="C9" s="134">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -19970,7 +19953,7 @@
       </c>
       <c r="C10" s="132">
         <f ca="1">Overview!C13</f>
-        <v>2.3437000000000001</v>
+        <v>2.3673000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20013,7 +19996,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>0.10490327153235289</v>
+        <v>9.6562307709416026E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20022,7 +20005,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.8950967284676471</v>
+        <v>0.90343769229058402</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20040,7 +20023,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.15499650000000001</v>
+        <v>0.15638849999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -20049,7 +20032,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
   </sheetData>
@@ -20300,7 +20283,7 @@
       </c>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>-29853.410056166082</v>
+        <v>-29334.752127041003</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -20354,23 +20337,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>-8092.4554617429258</v>
+        <v>-8077.0456142613084</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>-5716.2679021507702</v>
+        <v>-5694.5185212763245</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4192.7977087948966</v>
+        <v>-4168.8912125555371</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-4006.4540306097533</v>
+        <v>-3976.0243432421489</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="0"/>
-        <v>-1847.9149847948663</v>
+        <v>-1830.3876441582149</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -20389,7 +20372,7 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>-15277.250670009211</v>
+        <v>-14869.445362729744</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -20412,7 +20395,7 @@
       </c>
       <c r="C15" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -20427,7 +20410,7 @@
       </c>
       <c r="C19" s="63">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-23855.890088093212</v>
+        <v>-23746.867335493531</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -20436,7 +20419,7 @@
       </c>
       <c r="C20" s="63">
         <f ca="1">L11</f>
-        <v>-15277.250670009211</v>
+        <v>-14869.445362729744</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -20445,7 +20428,7 @@
       </c>
       <c r="C21" s="93">
         <f ca="1">C19+C20</f>
-        <v>-39133.140758102425</v>
+        <v>-38616.312698223279</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -20472,7 +20455,7 @@
       </c>
       <c r="C24" s="93">
         <f ca="1">C21+C22-C23</f>
-        <v>-51533.140758102425</v>
+        <v>-51016.312698223279</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -20490,7 +20473,7 @@
       </c>
       <c r="C26" s="231">
         <f ca="1">C24/C25</f>
-        <v>-10.216721006760988</v>
+        <v>-10.114257077363854</v>
       </c>
     </row>
   </sheetData>
@@ -20759,23 +20742,23 @@
       <c r="G9" s="137"/>
       <c r="H9" s="91">
         <f ca="1">DCF!H10</f>
-        <v>-8092.4554617429258</v>
+        <v>-8077.0456142613084</v>
       </c>
       <c r="I9" s="91">
         <f ca="1">DCF!I10</f>
-        <v>-5716.2679021507702</v>
+        <v>-5694.5185212763245</v>
       </c>
       <c r="J9" s="91">
         <f ca="1">DCF!J10</f>
-        <v>-4192.7977087948966</v>
+        <v>-4168.8912125555371</v>
       </c>
       <c r="K9" s="91">
         <f ca="1">DCF!K10</f>
-        <v>-4006.4540306097533</v>
+        <v>-3976.0243432421489</v>
       </c>
       <c r="L9" s="91">
         <f ca="1">DCF!L10</f>
-        <v>-1847.9149847948663</v>
+        <v>-1830.3876441582149</v>
       </c>
       <c r="N9" s="90"/>
     </row>
@@ -21561,7 +21544,7 @@
       </c>
       <c r="C41" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -21587,7 +21570,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>222553.9349880465</v>
+        <v>220443.02693185382</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -21596,7 +21579,7 @@
       </c>
       <c r="C45" s="93">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>200545.95988474815</v>
+        <v>198526.5472405185</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -21623,7 +21606,7 @@
       </c>
       <c r="C48" s="107">
         <f ca="1">C45+C46-C47</f>
-        <v>188145.95988474815</v>
+        <v>186126.5472405185</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -21641,7 +21624,7 @@
       </c>
       <c r="C50" s="231">
         <f ca="1">C48/C49</f>
-        <v>37.300943672630481</v>
+        <v>36.900584306209062</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -21665,7 +21648,7 @@
       </c>
       <c r="C54" s="134">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15499650000000001</v>
+        <v>0.15638849999999999</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -21700,7 +21683,7 @@
       </c>
       <c r="C58" s="231">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>41.78867320720358</v>
+        <v>41.537762903381562</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -21724,7 +21707,7 @@
       </c>
       <c r="C62" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -21750,7 +21733,7 @@
       </c>
       <c r="C65" s="63">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>-73916.599391794647</v>
+        <v>-73215.505766328599</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -21759,7 +21742,7 @@
       </c>
       <c r="C66" s="93">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>-95924.574495092995</v>
+        <v>-95131.985457663919</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -21786,7 +21769,7 @@
       </c>
       <c r="C69" s="93">
         <f ca="1">C66+C67-C68</f>
-        <v>-108324.57449509299</v>
+        <v>-107531.98545766392</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -21804,7 +21787,7 @@
       </c>
       <c r="C71" s="231">
         <f ca="1">C69/C70</f>
-        <v>-21.475926743674265</v>
+        <v>-21.31879172435843</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -21828,7 +21811,7 @@
       </c>
       <c r="C75" s="134">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -21854,7 +21837,7 @@
       </c>
       <c r="C78" s="63">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>244564.76372312792</v>
+        <v>242245.08454049862</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -21863,7 +21846,7 @@
       </c>
       <c r="C79" s="93">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>222556.78861982957</v>
+        <v>220328.6048491633</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -21890,7 +21873,7 @@
       </c>
       <c r="C82" s="93">
         <f ca="1">C79+C80-C81</f>
-        <v>210156.78861982957</v>
+        <v>207928.6048491633</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -21908,22 +21891,22 @@
       </c>
       <c r="C84" s="231">
         <f ca="1">C82/C83</f>
-        <v>41.66470829100507</v>
+        <v>41.22295893123777</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -21973,7 +21956,7 @@
       </c>
       <c r="C5" s="132">
         <f ca="1">DCF!C26</f>
-        <v>-10.216721006760988</v>
+        <v>-10.114257077363854</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -21982,7 +21965,7 @@
       </c>
       <c r="C6" s="132">
         <f ca="1">Multiples!C50</f>
-        <v>37.300943672630481</v>
+        <v>36.900584306209062</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -21991,7 +21974,7 @@
       </c>
       <c r="C7" s="132">
         <f ca="1">Multiples!C58</f>
-        <v>41.78867320720358</v>
+        <v>41.537762903381562</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -22000,7 +21983,7 @@
       </c>
       <c r="C8" s="132">
         <f ca="1">Multiples!C71</f>
-        <v>-21.475926743674265</v>
+        <v>-21.31879172435843</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -22009,7 +21992,7 @@
       </c>
       <c r="C9" s="132">
         <f ca="1">Multiples!C84</f>
-        <v>41.66470829100507</v>
+        <v>41.22295893123777</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -22018,7 +22001,7 @@
       </c>
       <c r="C10" s="231">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>17.812335484080776</v>
+        <v>17.645651467821221</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -22027,7 +22010,7 @@
       </c>
       <c r="C11" s="132">
         <f ca="1">Overview!C5</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -22036,7 +22019,7 @@
       </c>
       <c r="C12" s="151">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-0.79164422173259119</v>
+        <v>-0.81175963870470214</v>
       </c>
     </row>
   </sheetData>
@@ -22545,7 +22528,7 @@
       </c>
       <c r="C24" s="134">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.15499650000000001</v>
+        <v>0.15638849999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -22799,7 +22782,7 @@
       <c r="K8" s="136"/>
       <c r="L8" s="125">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>-477628.43096523924</v>
+        <v>-469330.35806738189</v>
       </c>
       <c r="N8" s="90"/>
       <c r="O8" s="16"/>
@@ -22853,23 +22836,23 @@
       <c r="G10" s="137"/>
       <c r="H10" s="125">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>-6817.1276746698113</v>
+        <v>-6804.1463369008234</v>
       </c>
       <c r="I10" s="125">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>-9837.7464141998444</v>
+        <v>-9800.3155419294708</v>
       </c>
       <c r="J10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-14196.778926366451</v>
+        <v>-14115.831724620401</v>
       </c>
       <c r="K10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-20487.266432605596</v>
+        <v>-20331.662223048217</v>
       </c>
       <c r="L10" s="125">
         <f t="shared" ca="1" si="1"/>
-        <v>-29565.022323552799</v>
+        <v>-29284.600214603543</v>
       </c>
       <c r="N10" s="90"/>
     </row>
@@ -22888,15 +22871,15 @@
       <c r="K11" s="136"/>
       <c r="L11" s="125">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>-244422.63892971983</v>
+        <v>-237898.11095490112</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="254" t="s">
         <v>217</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="255"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="152" t="s">
@@ -22904,7 +22887,7 @@
       </c>
       <c r="C15" s="153">
         <f ca="1">Overview!C5</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -22913,7 +22896,7 @@
       </c>
       <c r="C16" s="153">
         <f ca="1">C36</f>
-        <v>-66.956102438761761</v>
+        <v>-65.550092584457488</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -22923,20 +22906,20 @@
       <c r="C17" s="155">
         <v>0.65</v>
       </c>
-      <c r="E17" s="254" t="s">
+      <c r="E17" s="256" t="s">
         <v>220</v>
       </c>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
+      <c r="F17" s="256"/>
+      <c r="G17" s="256"/>
+      <c r="H17" s="256"/>
+      <c r="I17" s="256"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="254" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="255"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="156" t="s">
@@ -22952,7 +22935,7 @@
       </c>
       <c r="C21" s="221">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.14337778080652697</v>
+        <v>0.14555918203385057</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -22970,7 +22953,7 @@
       </c>
       <c r="C23" s="158">
         <f ca="1">C15*C22</f>
-        <v>431211.56</v>
+        <v>472824.56</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -22997,15 +22980,15 @@
       </c>
       <c r="C26" s="159">
         <f ca="1">C23+C25-C24</f>
-        <v>443611.56</v>
+        <v>485224.56</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="254" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="255"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="156" t="s">
@@ -23013,7 +22996,7 @@
       </c>
       <c r="C29" s="158">
         <f ca="1">SUM(H10:L10)</f>
-        <v>-80903.9417713945</v>
+        <v>-80336.556041102449</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -23022,7 +23005,7 @@
       </c>
       <c r="C30" s="158">
         <f ca="1">L11</f>
-        <v>-244422.63892971983</v>
+        <v>-237898.11095490112</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -23031,7 +23014,7 @@
       </c>
       <c r="C31" s="161">
         <f ca="1">C29+C30</f>
-        <v>-325326.58070111432</v>
+        <v>-318234.66699600359</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -23058,7 +23041,7 @@
       </c>
       <c r="C34" s="161">
         <f ca="1">C31+C32-C33</f>
-        <v>-337726.58070111432</v>
+        <v>-330634.66699600359</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -23076,21 +23059,21 @@
       </c>
       <c r="C36" s="164">
         <f ca="1">C34/C35</f>
-        <v>-66.956102438761761</v>
+        <v>-65.550092584457488</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -29749,7 +29732,7 @@
       </c>
       <c r="AC116" s="62">
         <f ca="1">Overview!C5</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="117" spans="1:31" x14ac:dyDescent="0.2">
@@ -29820,7 +29803,7 @@
       </c>
       <c r="AC117" s="64">
         <f ca="1">AC116/AC85</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="119" spans="1:31" x14ac:dyDescent="0.2">
@@ -31126,7 +31109,7 @@
       <c r="AA150" s="49"/>
       <c r="AC150" s="71">
         <f ca="1">AC117/Statement!AC26</f>
-        <v>-40.516587677725113</v>
+        <v>-44.426540284360179</v>
       </c>
     </row>
     <row r="151" spans="2:29" x14ac:dyDescent="0.2">
@@ -31163,7 +31146,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="71">
         <f ca="1">AC117/(Statement!AC5/Statement!AC22)</f>
-        <v>7.3289027651143215</v>
+        <v>8.0361603135082067</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -31224,7 +31207,7 @@
       </c>
       <c r="AC152" s="71">
         <f ca="1">AC117/(Statement!AC49/Statement!AC75)</f>
-        <v>4.9257677457677449</v>
+        <v>5.401116721116721</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -31285,7 +31268,7 @@
       </c>
       <c r="AC153" s="140">
         <f ca="1">Statement!AC117*Statement!AC78</f>
-        <v>431211.56</v>
+        <v>472824.56</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -31346,7 +31329,7 @@
       </c>
       <c r="AC154" s="140">
         <f ca="1">AC153+AC108-AC107+AC48+AC45</f>
-        <v>459212.56</v>
+        <v>500825.56</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -31383,7 +31366,7 @@
       <c r="AA155" s="49"/>
       <c r="AC155" s="178">
         <f ca="1">AC154/AC5</f>
-        <v>8.051840370318418</v>
+        <v>8.7814833777528403</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -31420,7 +31403,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="178">
         <f ca="1">AC154/AC12</f>
-        <v>-5963.7994805194803</v>
+        <v>-6504.2280519480519</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -31555,7 +31538,7 @@
       <c r="AA159" s="49"/>
       <c r="AC159" s="71">
         <f t="shared" ref="AC159:AC160" ca="1" si="161">AC153/AC157</f>
-        <v>-38.346959537572253</v>
+        <v>-42.047537572254335</v>
       </c>
     </row>
     <row r="160" spans="2:29" x14ac:dyDescent="0.2">
@@ -31592,7 +31575,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="71">
         <f t="shared" ca="1" si="161"/>
-        <v>-59.552919206328625</v>
+        <v>-64.949495525872123</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -31629,7 +31612,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="73">
         <f t="shared" ref="AC161" ca="1" si="164">AC157/AC153</f>
-        <v>-2.6077686785576898E-2</v>
+        <v>-2.3782605539779914E-2</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -31666,7 +31649,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="73">
         <f ca="1">AC26/AC117</f>
-        <v>-2.4681249268920347E-2</v>
+        <v>-2.2509067633880952E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -31777,7 +31760,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="151">
         <f ca="1">-(AC63+AC64)/AC153</f>
-        <v>3.7081566180646921E-3</v>
+        <v>3.3818040247317101E-3</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -32280,7 +32263,7 @@
       <c r="AA176" s="49"/>
       <c r="AC176" s="151">
         <f ca="1">(AC107-AC108)/AC153</f>
-        <v>-2.875618640650543E-2</v>
+        <v>-2.6225372049201504E-2</v>
       </c>
     </row>
     <row r="177" spans="1:31" x14ac:dyDescent="0.2">
@@ -34048,7 +34031,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -34081,7 +34064,7 @@
       </c>
       <c r="C5" s="167">
         <f ca="1">Overview!C5</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="131" t="s">
@@ -34097,7 +34080,7 @@
       </c>
       <c r="C6" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>431211.56</v>
+        <v>472824.56</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -34117,7 +34100,7 @@
       </c>
       <c r="C7" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>459212.56</v>
+        <v>500825.56</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>29</v>
@@ -34137,7 +34120,7 @@
       </c>
       <c r="C8" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-40.516587677725113</v>
+        <v>-44.426540284360179</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>238</v>
@@ -34157,7 +34140,7 @@
       </c>
       <c r="C9" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>7.3289027651143215</v>
+        <v>8.0361603135082067</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>239</v>
@@ -34177,7 +34160,7 @@
       </c>
       <c r="C10" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>4.9257677457677449</v>
+        <v>5.401116721116721</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -34197,7 +34180,7 @@
       </c>
       <c r="C11" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>8.051840370318418</v>
+        <v>8.7814833777528403</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -34206,7 +34189,7 @@
       </c>
       <c r="C12" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-5963.7994805194803</v>
+        <v>-6504.2280519480519</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -34442,7 +34425,7 @@
       </c>
       <c r="C38" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-2.4681249268920347E-2</v>
+        <v>-2.2509067633880952E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>265</v>
@@ -34458,7 +34441,7 @@
       </c>
       <c r="C39" s="210">
         <f ca="1">Statement!AC161</f>
-        <v>-2.6077686785576898E-2</v>
+        <v>-2.3782605539779914E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>267</v>
@@ -34499,7 +34482,7 @@
       </c>
       <c r="C42" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>3.7081566180646921E-3</v>
+        <v>3.3818040247317101E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -34543,7 +34526,7 @@
       </c>
       <c r="F48" s="170">
         <f ca="1">Statement!AC176</f>
-        <v>-2.875618640650543E-2</v>
+        <v>-2.6225372049201504E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -34597,8 +34580,51 @@
         <v>1.7758878194490542</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="242" t="s">
+        <v>428</v>
+      </c>
+      <c r="C57" s="242"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C58" s="169">
+        <f ca="1">Statement!AC159</f>
+        <v>-42.047537572254335</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="C59" s="169">
+        <f ca="1">Statement!AC160</f>
+        <v>-64.949495525872123</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="C60" s="170">
+        <f>Statement!AC166</f>
+        <v>-0.13520479730677515</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="C61" s="170">
+        <f>Statement!AC167</f>
+        <v>-0.19717000981904895</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -34623,7 +34649,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I96"/>
+  <dimension ref="B1:I102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -34722,7 +34748,7 @@
       </c>
       <c r="I6" s="167">
         <f ca="1">Statement!AC116</f>
-        <v>85.49</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -34751,7 +34777,7 @@
       </c>
       <c r="I7" s="168">
         <f ca="1">Statement!AC153</f>
-        <v>431211.56</v>
+        <v>472824.56</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -34780,7 +34806,7 @@
       </c>
       <c r="I8" s="168">
         <f ca="1">Statement!AC154</f>
-        <v>459212.56</v>
+        <v>500825.56</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -34809,7 +34835,7 @@
       </c>
       <c r="I9" s="169">
         <f ca="1">Statement!AC150</f>
-        <v>-40.516587677725113</v>
+        <v>-44.426540284360179</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -34838,7 +34864,7 @@
       </c>
       <c r="I10" s="169">
         <f ca="1">Statement!AC151</f>
-        <v>7.3289027651143215</v>
+        <v>8.0361603135082067</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -34867,7 +34893,7 @@
       </c>
       <c r="I11" s="169">
         <f ca="1">Statement!AC152</f>
-        <v>4.9257677457677449</v>
+        <v>5.401116721116721</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -34896,7 +34922,7 @@
       </c>
       <c r="I12" s="169">
         <f ca="1">Statement!AC155</f>
-        <v>8.051840370318418</v>
+        <v>8.7814833777528403</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -34925,7 +34951,7 @@
       </c>
       <c r="I13" s="169">
         <f ca="1">Statement!AC156</f>
-        <v>-5963.7994805194803</v>
+        <v>-6504.2280519480519</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -35698,7 +35724,7 @@
       </c>
       <c r="I51" s="170">
         <f ca="1">Statement!AC162</f>
-        <v>-2.4681249268920347E-2</v>
+        <v>-2.2509067633880952E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -35727,7 +35753,7 @@
       </c>
       <c r="I52" s="170">
         <f ca="1">Statement!AC161</f>
-        <v>-2.6077686785576898E-2</v>
+        <v>-2.3782605539779914E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -35814,7 +35840,7 @@
       </c>
       <c r="I55" s="170">
         <f ca="1">Statement!AC165</f>
-        <v>3.7081566180646921E-3</v>
+        <v>3.3818040247317101E-3</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36050,7 +36076,7 @@
       </c>
       <c r="I68" s="191">
         <f ca="1">Statement!AC176</f>
-        <v>-2.875618640650543E-2</v>
+        <v>-2.6225372049201504E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -36387,183 +36413,310 @@
       </c>
       <c r="I85" s="192"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C88" s="169">
+        <f>Statement!M159</f>
+        <v>24.234480257856571</v>
+      </c>
+      <c r="D88" s="169">
+        <f>Statement!N159</f>
+        <v>-8.7516835473323233</v>
+      </c>
+      <c r="E88" s="169">
+        <f>Statement!O159</f>
+        <v>-12.197995202193283</v>
+      </c>
+      <c r="F88" s="169">
+        <f>Statement!P159</f>
+        <v>-4.6102486100912623</v>
+      </c>
+      <c r="G88" s="169">
+        <f>Statement!Q159</f>
+        <v>-24.491263713937425</v>
+      </c>
+      <c r="I88" s="169">
+        <f ca="1">Statement!AC159</f>
+        <v>-42.047537572254335</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="C89" s="169">
+        <f>Statement!M160</f>
+        <v>39.164320117414455</v>
+      </c>
+      <c r="D89" s="169">
+        <f>Statement!N160</f>
+        <v>-8.5390374025602505</v>
+      </c>
+      <c r="E89" s="169">
+        <f>Statement!O160</f>
+        <v>-14.216825072184793</v>
+      </c>
+      <c r="F89" s="169">
+        <f>Statement!P160</f>
+        <v>-5.0227744165946415</v>
+      </c>
+      <c r="G89" s="169">
+        <f>Statement!Q160</f>
+        <v>-28.047384437038112</v>
+      </c>
+      <c r="I89" s="169">
+        <f ca="1">Statement!AC160</f>
+        <v>-64.949495525872123</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="C90" s="170">
+        <f>Statement!M166</f>
+        <v>6.9118053061243856E-2</v>
+      </c>
+      <c r="D90" s="170">
+        <f>Statement!N166</f>
+        <v>-0.22176229898182509</v>
+      </c>
+      <c r="E90" s="170">
+        <f>Statement!O166</f>
+        <v>-0.30655749797152765</v>
+      </c>
+      <c r="F90" s="170">
+        <f>Statement!P166</f>
+        <v>-0.43577333760192838</v>
+      </c>
+      <c r="G90" s="170">
+        <f>Statement!Q166</f>
+        <v>-0.1305696933002857</v>
+      </c>
+      <c r="I90" s="170">
+        <f>Statement!AC166</f>
+        <v>-0.13520479730677515</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="C91" s="170">
+        <f>Statement!M167</f>
+        <v>0.10992862927718161</v>
+      </c>
+      <c r="D91" s="170">
+        <f>Statement!N167</f>
+        <v>-0.19886129349446507</v>
+      </c>
+      <c r="E91" s="170">
+        <f>Statement!O167</f>
+        <v>-0.3228590396105333</v>
+      </c>
+      <c r="F91" s="170">
+        <f>Statement!P167</f>
+        <v>-0.35905161861358542</v>
+      </c>
+      <c r="G91" s="170">
+        <f>Statement!Q167</f>
+        <v>-0.13968932700130551</v>
+      </c>
+      <c r="I91" s="170">
+        <f>Statement!AC167</f>
+        <v>-0.19717000981904895</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="C94" s="170">
+        <f>Statement!M209</f>
+        <v>-1</v>
+      </c>
+      <c r="D94" s="170">
+        <f>Statement!N209</f>
+        <v>6.2544294826364283E-2</v>
+      </c>
+      <c r="E94" s="170">
+        <f>Statement!O209</f>
+        <v>-0.48507587126896784</v>
+      </c>
+      <c r="F94" s="170">
+        <f>Statement!P209</f>
+        <v>-0.48218911917098445</v>
+      </c>
+      <c r="G94" s="170">
+        <f>Statement!Q209</f>
+        <v>-1</v>
+      </c>
+      <c r="I94" s="192"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="211" t="s">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="211" t="s">
         <v>348</v>
       </c>
-      <c r="C89" s="170">
+      <c r="C98" s="170">
         <f>Statement!M201</f>
         <v>1</v>
       </c>
-      <c r="D89" s="170">
+      <c r="D98" s="170">
         <f>Statement!N201</f>
         <v>-0.22657676298045326</v>
       </c>
-      <c r="E89" s="170">
+      <c r="E98" s="170">
         <f>Statement!O201</f>
         <v>-7.9155257608661447E-2</v>
       </c>
-      <c r="F89" s="170">
+      <c r="F98" s="170">
         <f>Statement!P201</f>
         <v>0.139722469068289</v>
       </c>
-      <c r="G89" s="170">
+      <c r="G98" s="170">
         <f>Statement!Q201</f>
         <v>-3.3527259641336293E-2</v>
       </c>
-      <c r="I89" s="192"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="211" t="s">
+      <c r="I98" s="192"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="211" t="s">
         <v>349</v>
       </c>
-      <c r="C90" s="170">
+      <c r="C99" s="170">
         <f>Statement!M202</f>
         <v>1</v>
       </c>
-      <c r="D90" s="170">
+      <c r="D99" s="170">
         <f>Statement!N202</f>
         <v>-8.4923946253162061E-2</v>
       </c>
-      <c r="E90" s="170">
+      <c r="E99" s="170">
         <f>Statement!O202</f>
         <v>-0.23547784878293962</v>
       </c>
-      <c r="F90" s="170">
+      <c r="F99" s="170">
         <f>Statement!P202</f>
         <v>-0.242779995304062</v>
       </c>
-      <c r="G90" s="170">
+      <c r="G99" s="170">
         <f>Statement!Q202</f>
         <v>4.9240310077519382E-2</v>
       </c>
-      <c r="I90" s="192"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B91" s="20" t="s">
+      <c r="I99" s="192"/>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B100" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="C91" s="170">
+      <c r="C100" s="170">
         <f>Statement!M203</f>
         <v>1</v>
       </c>
-      <c r="D91" s="170">
+      <c r="D100" s="170">
         <f>Statement!N203</f>
         <v>-0.16628914988814317</v>
       </c>
-      <c r="E91" s="170">
+      <c r="E100" s="170">
         <f>Statement!O203</f>
         <v>-0.1521793818236705</v>
       </c>
-      <c r="F91" s="170">
+      <c r="F100" s="170">
         <f>Statement!P203</f>
         <v>-2.1403279726227919E-2</v>
       </c>
-      <c r="G91" s="170">
+      <c r="G100" s="170">
         <f>Statement!Q203</f>
         <v>-6.5492915041135214E-3</v>
       </c>
-      <c r="I91" s="192"/>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B92" s="20" t="s">
+      <c r="I100" s="192"/>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B101" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="C92" s="170">
+      <c r="C101" s="170">
         <f>Statement!M204</f>
         <v>1</v>
       </c>
-      <c r="D92" s="170">
+      <c r="D101" s="170">
         <f>Statement!N204</f>
         <v>0.35158501440922191</v>
       </c>
-      <c r="E92" s="170">
+      <c r="E101" s="170">
         <f>Statement!O204</f>
         <v>1.0298507462686568</v>
       </c>
-      <c r="F92" s="170">
+      <c r="F101" s="170">
         <f>Statement!P204</f>
         <v>17.190126050420169</v>
       </c>
-      <c r="G92" s="170">
+      <c r="G101" s="170">
         <f>Statement!Q204</f>
         <v>2.9393081942599757E-2</v>
       </c>
-      <c r="I92" s="192"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="s">
+      <c r="I101" s="192"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B102" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="C93" s="170">
+      <c r="C102" s="170">
         <f>Statement!M205</f>
         <v>1</v>
       </c>
-      <c r="D93" s="170">
+      <c r="D102" s="170">
         <f>Statement!N205</f>
         <v>-0.58669833729216148</v>
       </c>
-      <c r="E93" s="170">
+      <c r="E102" s="170">
         <f>Statement!O205</f>
         <v>-7.9445571331981074E-2</v>
       </c>
-      <c r="F93" s="170">
+      <c r="F102" s="170">
         <f>Statement!P205</f>
         <v>0.32243848696290855</v>
       </c>
-      <c r="G93" s="170">
+      <c r="G102" s="170">
         <f>Statement!Q205</f>
         <v>-1.0552624271035824E-2</v>
       </c>
-      <c r="I93" s="192"/>
-    </row>
-    <row r="95" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="C95" s="14"/>
-      <c r="D95" s="14"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
-      <c r="I95" s="14"/>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B96" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="C96" s="170">
-        <f>Statement!M209</f>
-        <v>-1</v>
-      </c>
-      <c r="D96" s="170">
-        <f>Statement!N209</f>
-        <v>6.2544294826364283E-2</v>
-      </c>
-      <c r="E96" s="170">
-        <f>Statement!O209</f>
-        <v>-0.48507587126896784</v>
-      </c>
-      <c r="F96" s="170">
-        <f>Statement!P209</f>
-        <v>-0.48218911917098445</v>
-      </c>
-      <c r="G96" s="170">
-        <f>Statement!Q209</f>
-        <v>-1</v>
-      </c>
-      <c r="I96" s="192"/>
+      <c r="I102" s="192"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36588,14 +36741,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="243" t="s">
         <v>308</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="F3" s="247" t="s">
+      <c r="D3" s="244"/>
+      <c r="F3" s="245" t="s">
         <v>309</v>
       </c>
-      <c r="G3" s="246"/>
+      <c r="G3" s="244"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -36662,19 +36815,19 @@
       <c r="B7" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C7" s="243">
+      <c r="C7" s="246">
         <f>Statement!AA89</f>
         <v>0.18789128673491934</v>
       </c>
-      <c r="D7" s="244"/>
-      <c r="F7" s="243">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.25421883505715842</v>
       </c>
-      <c r="G7" s="244"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="202" t="s">
@@ -36701,19 +36854,19 @@
       <c r="B9" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="243">
+      <c r="C9" s="246">
         <f>Statement!AA90</f>
         <v>0.16877278250303768</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="F9" s="243">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>3.2413867124610925E-2</v>
       </c>
-      <c r="G9" s="244"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="202" t="s">
@@ -36740,19 +36893,19 @@
       <c r="B11" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C11" s="243">
+      <c r="C11" s="246">
         <f>Statement!AA91</f>
         <v>0.21731812231157657</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="F11" s="243">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.83766233766233766</v>
       </c>
-      <c r="G11" s="244"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="202" t="s">
@@ -36779,19 +36932,19 @@
       <c r="B13" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C13" s="243">
+      <c r="C13" s="246">
         <f>Statement!AA95</f>
         <v>-0.44441824826122833</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="F13" s="243">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>-0.29845192021434952</v>
       </c>
-      <c r="G13" s="244"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="202" t="s">
@@ -36818,19 +36971,19 @@
       <c r="B15" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C15" s="243">
+      <c r="C15" s="246">
         <f>Statement!AA96</f>
         <v>1.572704081632653</v>
       </c>
-      <c r="D15" s="244"/>
-      <c r="F15" s="243">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>1.5654911838790933</v>
       </c>
-      <c r="G15" s="244"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="202" t="s">
@@ -36857,19 +37010,19 @@
       <c r="B17" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C17" s="243">
+      <c r="C17" s="246">
         <f>Statement!AA98</f>
         <v>-1.9594957081545064</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="F17" s="243">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>-2.781014393420151</v>
       </c>
-      <c r="G17" s="244"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="202" t="s">
@@ -36896,22 +37049,22 @@
       <c r="B19" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="243">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>4.1314184536690932E-3</v>
       </c>
-      <c r="D19" s="244"/>
-      <c r="F19" s="243">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>0.16823071641107806</v>
       </c>
-      <c r="G19" s="244"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="202" t="s">
@@ -36938,22 +37091,22 @@
       <c r="B21" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C21" s="243">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>-1.9589041095890414</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="F21" s="243">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>-2.2238805970149254</v>
       </c>
-      <c r="G21" s="244"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -37001,22 +37154,22 @@
       <c r="B25" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C25" s="243">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>0.14882878219231266</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="F25" s="243">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.12781095159446068</v>
       </c>
-      <c r="G25" s="244"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="s">
@@ -37043,22 +37196,22 @@
       <c r="B27" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C27" s="243">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>0.23950910530482977</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="F27" s="243">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>0.58974358974358976</v>
       </c>
-      <c r="G27" s="244"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="20" t="s">
@@ -37085,22 +37238,22 @@
       <c r="B29" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C29" s="243">
+      <c r="C29" s="246">
         <f>IF(C28=0,
 IF(D28=0,0,IF(D28&gt;0,1,-1)),
 (D28-C28)/ABS(C28)
 )</f>
         <v>0.18467798732295171</v>
       </c>
-      <c r="D29" s="244"/>
-      <c r="F29" s="243">
+      <c r="D29" s="247"/>
+      <c r="F29" s="246">
         <f>IF(F28=0,
 IF(G28=0,0,IF(G28&gt;0,1,-1)),
 (G28-F28)/ABS(F28)
 )</f>
         <v>0.28187976291278577</v>
       </c>
-      <c r="G29" s="244"/>
+      <c r="G29" s="247"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37127,22 +37280,22 @@
       <c r="B31" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C31" s="243">
+      <c r="C31" s="246">
         <f>IF(C30=0,
 IF(D30=0,0,IF(D30&gt;0,1,-1)),
 (D30-C30)/ABS(C30)
 )</f>
         <v>6.3456926766279287E-2</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="F31" s="243">
+      <c r="D31" s="247"/>
+      <c r="F31" s="246">
         <f>IF(F30=0,
 IF(G30=0,0,IF(G30&gt;0,1,-1)),
 (G30-F30)/ABS(F30)
 )</f>
         <v>0.30518451437627347</v>
       </c>
-      <c r="G31" s="244"/>
+      <c r="G31" s="247"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="20" t="s">
@@ -37169,37 +37322,25 @@
       <c r="B33" s="201" t="s">
         <v>310</v>
       </c>
-      <c r="C33" s="243">
+      <c r="C33" s="246">
         <f>IF(C32=0,
 IF(D32=0,0,IF(D32&gt;0,1,-1)),
 (D32-C32)/ABS(C32)
 )</f>
         <v>0.11624203821656051</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="F33" s="243">
+      <c r="D33" s="247"/>
+      <c r="F33" s="246">
         <f>IF(F32=0,
 IF(G32=0,0,IF(G32&gt;0,1,-1)),
 (G32-F32)/ABS(F32)
 )</f>
         <v>-0.33428300094966762</v>
       </c>
-      <c r="G33" s="244"/>
+      <c r="G33" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="C33:D33"/>
@@ -37216,6 +37357,18 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
